--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -13,6 +13,7 @@
     <sheet name="NEW THIS WEEK" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="TEXAS - HOUSTON" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="CLOSING SOON" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SOURCE HEALTH" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$188</definedName>
@@ -20,6 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SOURCE HEALTH'!$A$1:$F$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +51,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +61,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0016324F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -79,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -90,6 +107,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -543,6 +569,53 @@
         <is>
           <t>2026-09-26</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SOURCE HEALTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sources OK</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unknown / unverified</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -632,7 +705,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -670,7 +743,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -708,7 +781,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -746,7 +819,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -784,7 +857,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -822,7 +895,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -860,7 +933,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -898,7 +971,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -936,7 +1009,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -974,7 +1047,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1012,7 +1085,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1050,7 +1123,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1088,7 +1161,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1126,7 +1199,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1164,7 +1237,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1202,7 +1275,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1240,7 +1313,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1278,7 +1351,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1316,7 +1389,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1354,7 +1427,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1392,7 +1465,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1430,7 +1503,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1468,7 +1541,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1506,7 +1579,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1544,7 +1617,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1582,7 +1655,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1620,7 +1693,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1658,7 +1731,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1696,7 +1769,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1734,7 +1807,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1772,7 +1845,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1810,7 +1883,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1848,7 +1921,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1886,7 +1959,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1924,7 +1997,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1962,7 +2035,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -2000,7 +2073,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -2038,7 +2111,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2076,7 +2149,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -2114,7 +2187,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2152,7 +2225,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -2190,7 +2263,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -2228,7 +2301,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -2266,7 +2339,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2304,7 +2377,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -2342,7 +2415,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2380,7 +2453,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -2418,7 +2491,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2456,7 +2529,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -2494,7 +2567,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -2532,7 +2605,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -2570,7 +2643,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2608,7 +2681,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2646,7 +2719,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -2684,7 +2757,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -2722,7 +2795,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -2760,7 +2833,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -2798,7 +2871,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -2836,7 +2909,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -2874,7 +2947,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -2912,7 +2985,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -2950,7 +3023,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -2988,7 +3061,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -3026,7 +3099,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3064,7 +3137,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -3102,7 +3175,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3140,7 +3213,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -3178,7 +3251,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3216,7 +3289,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -3254,7 +3327,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -3292,7 +3365,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -3330,7 +3403,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -3368,7 +3441,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -3406,7 +3479,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -3444,7 +3517,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -3482,7 +3555,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -3520,7 +3593,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -3558,7 +3631,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -3596,7 +3669,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -3634,7 +3707,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -3672,7 +3745,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -3710,7 +3783,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -3748,7 +3821,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -3786,7 +3859,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -3824,7 +3897,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -3858,7 +3931,7 @@
       <c r="C87" s="4" t="inlineStr"/>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3892,7 +3965,7 @@
       <c r="C88" s="4" t="inlineStr"/>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -3926,7 +3999,7 @@
       <c r="C89" s="4" t="inlineStr"/>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3960,7 +4033,7 @@
       <c r="C90" s="4" t="inlineStr"/>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -3994,7 +4067,7 @@
       <c r="C91" s="4" t="inlineStr"/>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -4028,7 +4101,7 @@
       <c r="C92" s="4" t="inlineStr"/>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -4062,7 +4135,7 @@
       <c r="C93" s="4" t="inlineStr"/>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -4100,7 +4173,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -4138,7 +4211,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -4176,7 +4249,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -4214,7 +4287,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -4252,7 +4325,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -4290,7 +4363,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -4328,7 +4401,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -4366,7 +4439,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -4404,7 +4477,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -4442,7 +4515,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -4480,7 +4553,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -4518,7 +4591,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -4556,7 +4629,7 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -4594,7 +4667,7 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -4632,7 +4705,7 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -4670,7 +4743,7 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -4708,7 +4781,7 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -4746,7 +4819,7 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -4784,7 +4857,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -4822,7 +4895,7 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -4860,7 +4933,7 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -4898,7 +4971,7 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -4932,7 +5005,7 @@
       <c r="C116" s="4" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -4966,7 +5039,7 @@
       <c r="C117" s="4" t="inlineStr"/>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -5000,7 +5073,7 @@
       <c r="C118" s="4" t="inlineStr"/>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -5038,7 +5111,7 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -5076,7 +5149,7 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -5114,7 +5187,7 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -5152,7 +5225,7 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -5190,7 +5263,7 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -5228,7 +5301,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -5266,7 +5339,7 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -5304,7 +5377,7 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -5342,7 +5415,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -5380,7 +5453,7 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -5418,7 +5491,7 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -5456,7 +5529,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -5494,7 +5567,7 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -5532,7 +5605,7 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -5570,7 +5643,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -5608,7 +5681,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -5646,7 +5719,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -5679,12 +5752,12 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -5700,7 +5773,7 @@
       <c r="G136" s="4" t="inlineStr"/>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -5717,12 +5790,12 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Silver Spring, MD</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -5738,7 +5811,7 @@
       <c r="G137" s="4" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5833,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -5798,7 +5871,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -5836,7 +5909,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -5874,7 +5947,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -5912,7 +5985,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -5950,7 +6023,7 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -5988,7 +6061,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -6026,7 +6099,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -6064,7 +6137,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -6102,7 +6175,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -6140,7 +6213,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -6178,7 +6251,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -6216,7 +6289,7 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -6254,7 +6327,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -6287,12 +6360,12 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -6308,7 +6381,7 @@
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6398,12 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -6346,7 +6419,7 @@
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6441,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -6406,7 +6479,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -6444,7 +6517,7 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -6482,7 +6555,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -6520,7 +6593,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -6558,7 +6631,7 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -6596,7 +6669,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -6634,7 +6707,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -6672,7 +6745,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -6710,7 +6783,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -6748,7 +6821,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
@@ -6786,7 +6859,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
@@ -6824,7 +6897,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
@@ -6862,7 +6935,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
@@ -6900,7 +6973,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -6938,7 +7011,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -6976,7 +7049,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
@@ -7014,7 +7087,7 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -7052,7 +7125,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
@@ -7090,7 +7163,7 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -7128,7 +7201,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
@@ -7166,7 +7239,7 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -7204,7 +7277,7 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
@@ -7242,7 +7315,7 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -7276,7 +7349,7 @@
       <c r="C178" s="4" t="inlineStr"/>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
@@ -7310,7 +7383,7 @@
       <c r="C179" s="4" t="inlineStr"/>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -7344,7 +7417,7 @@
       <c r="C180" s="4" t="inlineStr"/>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
@@ -7378,7 +7451,7 @@
       <c r="C181" s="4" t="inlineStr"/>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -7412,7 +7485,7 @@
       <c r="C182" s="4" t="inlineStr"/>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
@@ -7446,7 +7519,7 @@
       <c r="C183" s="4" t="inlineStr"/>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -7480,7 +7553,7 @@
       <c r="C184" s="4" t="inlineStr"/>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -7514,7 +7587,7 @@
       <c r="C185" s="4" t="inlineStr"/>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -7548,7 +7621,7 @@
       <c r="C186" s="4" t="inlineStr"/>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
@@ -7582,7 +7655,7 @@
       <c r="C187" s="4" t="inlineStr"/>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -7616,7 +7689,7 @@
       <c r="C188" s="4" t="inlineStr"/>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
@@ -7721,7 +7794,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -7759,7 +7832,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -7797,7 +7870,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -7835,7 +7908,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -7873,7 +7946,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -7911,7 +7984,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -7949,7 +8022,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -7987,7 +8060,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -8025,7 +8098,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -8063,7 +8136,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -8101,7 +8174,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -8139,7 +8212,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -8177,7 +8250,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -8215,7 +8288,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -8253,7 +8326,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -8291,7 +8364,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -8329,7 +8402,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -8367,7 +8440,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -8405,7 +8478,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -8443,7 +8516,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -8481,7 +8554,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -8519,7 +8592,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -8557,7 +8630,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -8595,7 +8668,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -8633,7 +8706,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -8671,7 +8744,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -8709,7 +8782,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -8747,7 +8820,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -8785,7 +8858,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -8823,7 +8896,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -8861,7 +8934,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -8899,7 +8972,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -8937,7 +9010,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -8975,7 +9048,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -9013,7 +9086,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -9051,7 +9124,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -9089,7 +9162,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -9127,7 +9200,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -9165,7 +9238,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -9203,7 +9276,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -9241,7 +9314,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -9279,7 +9352,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -9317,7 +9390,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -9355,7 +9428,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -9393,7 +9466,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -9431,7 +9504,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -9469,7 +9542,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -9507,7 +9580,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -9545,7 +9618,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -9583,7 +9656,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -9621,7 +9694,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -9659,7 +9732,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -9697,7 +9770,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -9735,7 +9808,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -9773,7 +9846,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -9811,7 +9884,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -9849,7 +9922,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -9887,7 +9960,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -9925,7 +9998,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -9963,7 +10036,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -10001,7 +10074,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -10039,7 +10112,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -10077,7 +10150,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -10115,7 +10188,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -10153,7 +10226,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -10191,7 +10264,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -10229,7 +10302,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -10267,7 +10340,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -10305,7 +10378,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -10343,7 +10416,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -10381,7 +10454,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -10419,7 +10492,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -10457,7 +10530,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -10495,7 +10568,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -10533,7 +10606,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -10571,7 +10644,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -10609,7 +10682,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -10647,7 +10720,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -10685,7 +10758,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -10723,7 +10796,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -10761,7 +10834,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -10799,7 +10872,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -10837,7 +10910,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -10875,7 +10948,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -10913,7 +10986,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -10947,7 +11020,7 @@
       <c r="C87" s="4" t="inlineStr"/>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -10981,7 +11054,7 @@
       <c r="C88" s="4" t="inlineStr"/>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -11015,7 +11088,7 @@
       <c r="C89" s="4" t="inlineStr"/>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -11049,7 +11122,7 @@
       <c r="C90" s="4" t="inlineStr"/>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -11083,7 +11156,7 @@
       <c r="C91" s="4" t="inlineStr"/>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -11117,7 +11190,7 @@
       <c r="C92" s="4" t="inlineStr"/>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -11151,7 +11224,7 @@
       <c r="C93" s="4" t="inlineStr"/>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -11189,7 +11262,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -11227,7 +11300,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -11265,7 +11338,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -11303,7 +11376,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -11341,7 +11414,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -11379,7 +11452,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -11417,7 +11490,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -11455,7 +11528,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -11493,7 +11566,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -11531,7 +11604,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -11569,7 +11642,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -11607,7 +11680,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -11645,7 +11718,7 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -11683,7 +11756,7 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -11721,7 +11794,7 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -11759,7 +11832,7 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -11797,7 +11870,7 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -11835,7 +11908,7 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -11873,7 +11946,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -11911,7 +11984,7 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -11949,7 +12022,7 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -11987,7 +12060,7 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -12021,7 +12094,7 @@
       <c r="C116" s="4" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -12055,7 +12128,7 @@
       <c r="C117" s="4" t="inlineStr"/>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -12089,7 +12162,7 @@
       <c r="C118" s="4" t="inlineStr"/>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -12127,7 +12200,7 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -12165,7 +12238,7 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -12203,7 +12276,7 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -12241,7 +12314,7 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -12279,7 +12352,7 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -12317,7 +12390,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -12355,7 +12428,7 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -12393,7 +12466,7 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -12431,7 +12504,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -12469,7 +12542,7 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -12507,7 +12580,7 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -12545,7 +12618,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -12583,7 +12656,7 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -12621,7 +12694,7 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -12659,7 +12732,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -12697,7 +12770,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -12735,7 +12808,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12768,12 +12841,12 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -12789,7 +12862,7 @@
       <c r="G136" s="4" t="inlineStr"/>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12879,12 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Silver Spring, MD</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -12827,7 +12900,7 @@
       <c r="G137" s="4" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -12849,7 +12922,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -12887,7 +12960,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -12925,7 +12998,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -12963,7 +13036,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -13001,7 +13074,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -13039,7 +13112,7 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -13077,7 +13150,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -13115,7 +13188,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -13153,7 +13226,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -13191,7 +13264,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -13229,7 +13302,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -13267,7 +13340,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -13305,7 +13378,7 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -13343,7 +13416,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -13376,12 +13449,12 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -13397,7 +13470,7 @@
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -13414,12 +13487,12 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -13435,7 +13508,7 @@
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -13457,7 +13530,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -13495,7 +13568,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -13533,7 +13606,7 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -13571,7 +13644,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -13609,7 +13682,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -13647,7 +13720,7 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -13685,7 +13758,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -13723,7 +13796,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -13761,7 +13834,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -13799,7 +13872,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -13837,7 +13910,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
@@ -13875,7 +13948,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
@@ -13913,7 +13986,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
@@ -13951,7 +14024,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
@@ -13989,7 +14062,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -14027,7 +14100,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -14065,7 +14138,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
@@ -14103,7 +14176,7 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -14141,7 +14214,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
@@ -14179,7 +14252,7 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -14217,7 +14290,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
@@ -14255,7 +14328,7 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -14293,7 +14366,7 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
@@ -14331,7 +14404,7 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -14365,7 +14438,7 @@
       <c r="C178" s="4" t="inlineStr"/>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
@@ -14399,7 +14472,7 @@
       <c r="C179" s="4" t="inlineStr"/>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -14433,7 +14506,7 @@
       <c r="C180" s="4" t="inlineStr"/>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
@@ -14467,7 +14540,7 @@
       <c r="C181" s="4" t="inlineStr"/>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -14501,7 +14574,7 @@
       <c r="C182" s="4" t="inlineStr"/>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
@@ -14535,7 +14608,7 @@
       <c r="C183" s="4" t="inlineStr"/>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -14569,7 +14642,7 @@
       <c r="C184" s="4" t="inlineStr"/>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -14603,7 +14676,7 @@
       <c r="C185" s="4" t="inlineStr"/>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -14637,7 +14710,7 @@
       <c r="C186" s="4" t="inlineStr"/>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
@@ -14671,7 +14744,7 @@
       <c r="C187" s="4" t="inlineStr"/>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -14705,7 +14778,7 @@
       <c r="C188" s="4" t="inlineStr"/>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
@@ -14806,7 +14879,7 @@
       <c r="C2" s="4" t="inlineStr"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -14840,7 +14913,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -14874,7 +14947,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -14908,7 +14981,7 @@
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -14942,7 +15015,7 @@
       <c r="C6" s="4" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -14976,7 +15049,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -15010,7 +15083,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -15044,7 +15117,7 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -15078,7 +15151,7 @@
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -15112,7 +15185,7 @@
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -15146,7 +15219,7 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -15184,7 +15257,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -15222,7 +15295,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -15260,7 +15333,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -15298,7 +15371,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -15336,7 +15409,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -15374,7 +15447,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -15412,7 +15485,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -15450,7 +15523,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -15488,7 +15561,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -15526,7 +15599,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -15564,7 +15637,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -15602,7 +15675,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -15640,7 +15713,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -15678,7 +15751,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -15716,7 +15789,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -15754,7 +15827,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -15792,7 +15865,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -15830,7 +15903,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -15868,7 +15941,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -15906,7 +15979,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -15944,7 +16017,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -15982,7 +16055,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -16015,12 +16088,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -16036,7 +16109,7 @@
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -16053,12 +16126,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -16074,7 +16147,7 @@
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -16096,7 +16169,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -16134,7 +16207,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -16172,7 +16245,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -16210,7 +16283,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -16248,7 +16321,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -16286,7 +16359,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -16324,7 +16397,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -16362,7 +16435,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -16400,7 +16473,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -16438,7 +16511,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -16476,7 +16549,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -16514,7 +16587,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -16552,7 +16625,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -16590,7 +16663,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -16628,7 +16701,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -16666,7 +16739,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -16704,7 +16777,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -16737,12 +16810,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -16758,7 +16831,7 @@
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -16775,12 +16848,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Silver Spring, MD</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -16796,7 +16869,7 @@
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -16818,7 +16891,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -16856,7 +16929,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -16894,7 +16967,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -16932,7 +17005,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -16970,7 +17043,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -17008,7 +17081,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -17046,7 +17119,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -17084,7 +17157,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -17122,7 +17195,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -17160,7 +17233,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -17198,7 +17271,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -17236,7 +17309,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -17274,7 +17347,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -17312,7 +17385,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -17350,7 +17423,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -17388,7 +17461,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -17422,7 +17495,7 @@
       <c r="C72" s="4" t="inlineStr"/>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -17456,7 +17529,7 @@
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -17490,7 +17563,7 @@
       <c r="C74" s="4" t="inlineStr"/>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -17528,7 +17601,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -17566,7 +17639,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -17604,7 +17677,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -17642,7 +17715,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -17680,7 +17753,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -17718,7 +17791,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -17756,7 +17829,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -17794,7 +17867,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -17832,7 +17905,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -17870,7 +17943,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -17908,7 +17981,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -17946,7 +18019,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -17984,7 +18057,7 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -18022,7 +18095,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -18060,7 +18133,7 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -18098,7 +18171,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -18136,7 +18209,7 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -18174,7 +18247,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -18212,7 +18285,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -18250,7 +18323,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -18288,7 +18361,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -18326,7 +18399,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -18360,7 +18433,7 @@
       <c r="C97" s="4" t="inlineStr"/>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -18394,7 +18467,7 @@
       <c r="C98" s="4" t="inlineStr"/>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -18428,7 +18501,7 @@
       <c r="C99" s="4" t="inlineStr"/>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -18462,7 +18535,7 @@
       <c r="C100" s="4" t="inlineStr"/>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -18496,7 +18569,7 @@
       <c r="C101" s="4" t="inlineStr"/>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -18530,7 +18603,7 @@
       <c r="C102" s="4" t="inlineStr"/>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -18564,7 +18637,7 @@
       <c r="C103" s="4" t="inlineStr"/>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -18602,7 +18675,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -18640,7 +18713,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -18678,7 +18751,7 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -18716,7 +18789,7 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -18754,7 +18827,7 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -18792,7 +18865,7 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -18830,7 +18903,7 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -18868,7 +18941,7 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -18906,7 +18979,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -18944,7 +19017,7 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -18982,7 +19055,7 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -19020,7 +19093,7 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -19058,7 +19131,7 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -19096,7 +19169,7 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -19134,7 +19207,7 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -19172,7 +19245,7 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -19210,7 +19283,7 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -19248,7 +19321,7 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -19286,7 +19359,7 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -19324,7 +19397,7 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -19362,7 +19435,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -19400,7 +19473,7 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -19438,7 +19511,7 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -19476,7 +19549,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -19514,7 +19587,7 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -19552,7 +19625,7 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -19590,7 +19663,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -19628,7 +19701,7 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -19666,7 +19739,7 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -19704,7 +19777,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -19742,7 +19815,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -19780,7 +19853,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -19818,7 +19891,7 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -19856,7 +19929,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -19894,7 +19967,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -19932,7 +20005,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -19970,7 +20043,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -20008,7 +20081,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -20046,7 +20119,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -20084,7 +20157,7 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -20122,7 +20195,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -20160,7 +20233,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -20198,7 +20271,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -20236,7 +20309,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -20274,7 +20347,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -20312,7 +20385,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -20350,7 +20423,7 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -20388,7 +20461,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -20426,7 +20499,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -20464,7 +20537,7 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -20502,7 +20575,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -20540,7 +20613,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -20578,7 +20651,7 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -20616,7 +20689,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -20654,7 +20727,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -20692,7 +20765,7 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -20730,7 +20803,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -20768,7 +20841,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -20806,7 +20879,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -20844,7 +20917,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -20882,7 +20955,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
@@ -20920,7 +20993,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
@@ -20958,7 +21031,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
@@ -20996,7 +21069,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
@@ -21034,7 +21107,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -21072,7 +21145,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -21110,7 +21183,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
@@ -21148,7 +21221,7 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -21186,7 +21259,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
@@ -21224,7 +21297,7 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -21262,7 +21335,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
@@ -21300,7 +21373,7 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -21338,7 +21411,7 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
@@ -21376,7 +21449,7 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -21414,7 +21487,7 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
@@ -21452,7 +21525,7 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -21490,7 +21563,7 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
@@ -21528,7 +21601,7 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -21566,7 +21639,7 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
@@ -21604,7 +21677,7 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -21642,7 +21715,7 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -21680,7 +21753,7 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -21718,7 +21791,7 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
@@ -21756,7 +21829,7 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -21794,7 +21867,7 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
@@ -21899,7 +21972,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -21937,7 +22010,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -21975,7 +22048,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -22013,7 +22086,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -22051,7 +22124,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -22089,7 +22162,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -22127,7 +22200,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -22165,7 +22238,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -22203,7 +22276,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -22241,7 +22314,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -22279,7 +22352,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -22317,7 +22390,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -22355,7 +22428,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -22393,7 +22466,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -22484,4 +22557,2729 @@
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Last Checked</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Astranis</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>BETA Technologies</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CesiumAstro</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>E-Space</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Gulfstream Aerospace</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hermeus</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>K2 Space</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Loft Orbital</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>MIT Lincoln Laboratory</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Relativity Space</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Rocket Lab</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Shield AI</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Star Catcher</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Stoke Space</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>United Launch Alliance</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Varda Space Industries</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Vast</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Successful source check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.blueorigin.com/careers/search?search=intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Honda Aircraft Company</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.hondajet.com/en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://careers.leidos.com/search/jobs?q=intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Parker Aerospace</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://parkercareers.ttcportals.com/search/jobs?q=intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://jobs.saic.com/search/intern/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Apex Space</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/apexspace/jobs?content=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Boom Supersonic</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://api.lever.co/v0/postings/boomsupersonic?mode=json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Crane Aerospace &amp; Electronics</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='jobs.craneco.com', port=443): Max retries exceeded with url: /search/?q=intern (Caused by NameResolutionError("HTTPSConnection(host='jobs.craneco.com', port=443): Failed to resolve 'jobs.craneco.com' ([Errno -2] Name or service not known)"))</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Hadrian</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/hadrian/jobs?content=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Howmet Aerospace</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>500 Server Error: Internal Server Error for url: https://howmet.wd5.myworkdayjobs.com/Howmet_Careers?q=intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Impulse Space</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/impulsespace/jobs?content=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Kratos Defense</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='careers.kratosdefense.com', port=443): Max retries exceeded with url: /search/jobs?q=intern (Caused by NameResolutionError("HTTPSConnection(host='careers.kratosdefense.com', port=443): Failed to resolve 'careers.kratosdefense.com' ([Errno -2] Name or service not known)"))</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>NASA JPL / Caltech</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.jpl.jobs/internships</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Parsons</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://jobs.parsons.com/jobs/search?q=intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Peraton</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.careers.peraton.com/jobs/search?query=intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RTX / Raytheon / Collins / Pratt &amp; Whitney</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>422 Client Error: Unprocessable Entity for url: https://globalhr.wd5.myworkdayjobs.com/wday/cxs/RTX/REC_RTX_Ext_Gateway/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Relativity Space Internships</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/rsinternboard/jobs?content=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Sierra Nevada Corporation</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.sncorp.com/careers/open-positions</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>StandardAero</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>500 Server Error: Internal Server Error for url: https://standardaero.wd1.myworkdayjobs.com/External?q=intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Venturi Astrolab</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.astrolab.space/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>AeroVironment</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Airbus Americas</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Archer Aviation</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Axiom Space</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>BAE Systems</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Barrios Technology</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Bell / Textron</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>BlackSky</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Bombardier</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>CACI</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Capella Space</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Curtiss-Wright</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Eaton Aerospace</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Embraer</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Firefly Aerospace</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>GKN Aerospace</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>General Atomics Aeronautical Systems</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>General Dynamics Mission Systems</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Intuitive Machines</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Joby Aviation</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Johns Hopkins APL</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>L3Harris</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Lunar Outpost</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Maxar Space Systems</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Moog</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Muon Space</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>NASA</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>NASA / USAJobs Pathways</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Northrop Grumman</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Oceaneering</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Planet Labs</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Redwire</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Safran</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Scaled Composites</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Sierra Space</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Southwest Research Institute</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Stratolaunch</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Terran Orbital</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>The Aerospace Corporation</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Ursa Major</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Virgin Galactic</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Wisk Aero</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Woodward</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>York Space Systems</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F90"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -65,11 +65,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
@@ -81,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -690,27 +690,27 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Intern to Intern Conversion - Engineering (Summer 2026 Intern Program)</t>
+          <t>2027 Electrical Engineer Intern</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -721,34 +721,34 @@
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Intern-to-Intern-Conversion---Engineering--Summer-2026-Intern-Program-_JR2026516288</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
+          <t>2027 Flight Software Engineer Intern</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Costa Mesa, California, United States</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -759,34 +759,34 @@
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Internship - Summer 2027</t>
+          <t>2027 Manufacturing Engineer Intern</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -797,7 +797,7 @@
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
         </is>
       </c>
     </row>
@@ -809,15 +809,15 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2027 Electrical Engineer Intern</t>
+          <t>2027 Manufacturing Optimization Engineer Intern</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+          <t>Ashville, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -835,7 +835,7 @@
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
         </is>
       </c>
     </row>
@@ -847,15 +847,15 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2027 Flight Software Engineer Intern</t>
+          <t>2027 Mechanical Engineer Intern</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -873,7 +873,7 @@
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
         </is>
       </c>
     </row>
@@ -885,15 +885,15 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Engineer Intern</t>
+          <t>2027 Software Engineer Intern</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -911,7 +911,7 @@
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
         </is>
       </c>
     </row>
@@ -923,15 +923,15 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Optimization Engineer Intern</t>
+          <t>Winter 2027 Manufacturing Engineer Co-op</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
+          <t>Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -949,27 +949,27 @@
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2027 Mechanical Engineer Intern</t>
+          <t>Antenna Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -987,27 +987,27 @@
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2027 Software Engineer Intern</t>
+          <t>Antenna Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1025,27 +1025,27 @@
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Winter 2027 Manufacturing Engineer Co-op</t>
+          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1063,7 +1063,7 @@
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Antenna Associate (Summer 2027)</t>
+          <t>Avionics Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1083,7 +1083,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1101,7 +1101,7 @@
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Antenna Intern (Summer 2027)</t>
+          <t>Avionics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1121,7 +1121,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1139,7 +1139,7 @@
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
+          <t>CAD Engineer Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1177,7 +1177,7 @@
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Avionics Associate Engineer (Summer 2027)</t>
+          <t>CAD Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1197,7 +1197,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1215,7 +1215,7 @@
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
         </is>
       </c>
     </row>
@@ -1227,15 +1227,15 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Avionics Intern (Summer 2027)</t>
+          <t>Electrical Integration Associate - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1253,7 +1253,7 @@
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Associate (Summer 2027)</t>
+          <t>Electrical Integration Intern - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1273,7 +1273,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1291,7 +1291,7 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Intern (Summer 2027)</t>
+          <t>Electrical Reliability Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1311,7 +1311,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1329,7 +1329,7 @@
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
         </is>
       </c>
     </row>
@@ -1341,15 +1341,15 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Associate - RF (Summer 2027)</t>
+          <t>Electrical Reliability Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1367,7 +1367,7 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Intern - RF (Summer 2027)</t>
+          <t>FPGA Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1387,7 +1387,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1405,7 +1405,7 @@
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Associate (Summer 2027)</t>
+          <t>FPGA Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1425,7 +1425,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1443,7 +1443,7 @@
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Intern (Summer 2027)</t>
+          <t>Flight Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1463,7 +1463,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1481,7 +1481,7 @@
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>FPGA Associate (Summer 2027)</t>
+          <t>Flight Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1501,7 +1501,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1519,7 +1519,7 @@
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>FPGA Intern (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1539,7 +1539,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1557,7 +1557,7 @@
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Associate (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1595,7 +1595,7 @@
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Intern (Summer 2027)</t>
+          <t>Harness Design Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1615,7 +1615,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1633,7 +1633,7 @@
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
+          <t>Harness Manufacturing Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1653,7 +1653,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1671,7 +1671,7 @@
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
+          <t>Harness Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1691,7 +1691,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1709,7 +1709,7 @@
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Harness Design Engineer Intern (Summer 2027)</t>
+          <t>Mechanical Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1747,7 +1747,7 @@
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Associate (Summer 2027)</t>
+          <t>Mechanical Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1767,7 +1767,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1785,7 +1785,7 @@
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Intern (Summer 2027)</t>
+          <t>Power Electronics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1805,7 +1805,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1823,7 +1823,7 @@
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
         </is>
       </c>
     </row>
@@ -1835,15 +1835,15 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Associate Engineer (Summer 2027)</t>
+          <t>Production Quality Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
+          <t xml:space="preserve">San Francisco </t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1861,7 +1861,7 @@
       <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer Intern (Summer 2027)</t>
+          <t>Propulsion Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1881,7 +1881,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1899,7 +1899,7 @@
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Power Electronics Intern (Summer 2027)</t>
+          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1919,7 +1919,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1937,7 +1937,7 @@
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
         </is>
       </c>
     </row>
@@ -1949,15 +1949,15 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Production Quality Intern (Summer 2027)</t>
+          <t>Propulsion Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco </t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1975,7 +1975,7 @@
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineer Intern (Summer 2027)</t>
+          <t>RF Validation Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1995,7 +1995,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2013,7 +2013,7 @@
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
+          <t>RF Validation Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2033,7 +2033,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2051,7 +2051,7 @@
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Test Intern (Summer 2027)</t>
+          <t>Reliability Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2071,7 +2071,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2089,7 +2089,7 @@
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Associate (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2109,7 +2109,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2127,7 +2127,7 @@
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Intern (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2147,7 +2147,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2165,7 +2165,7 @@
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Reliability Test Intern (Summer 2027)</t>
+          <t>Software Developer, Network Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2185,7 +2185,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2203,7 +2203,7 @@
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
+          <t>Software Developer, Network Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2223,7 +2223,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2241,7 +2241,7 @@
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
         </is>
       </c>
     </row>
@@ -2253,15 +2253,15 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
+          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2279,7 +2279,7 @@
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
         </is>
       </c>
     </row>
@@ -2291,15 +2291,15 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Associate (Summer 2027)</t>
+          <t>Software Engineer Backend Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2317,7 +2317,7 @@
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Intern (Summer 2027)</t>
+          <t>Technical Project Management Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2337,7 +2337,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2355,7 +2355,7 @@
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
         </is>
       </c>
     </row>
@@ -2367,15 +2367,15 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
+          <t>Thermal Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2393,7 +2393,7 @@
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
         </is>
       </c>
     </row>
@@ -2405,15 +2405,15 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Backend Intern (Summer 2027)</t>
+          <t>Thermal Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2431,27 +2431,27 @@
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>BETA Technologies</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Technical Project Management Intern (Summer 2027)</t>
+          <t>BETA Internship</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
+          <t>South Burlington, Vermont, United States</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2469,27 +2469,27 @@
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
+          <t>https://job-boards.greenhouse.io/betatechnologiesinc/jobs/4218580009</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Thermal Associate Engineer (Summer 2027)</t>
+          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2507,27 +2507,27 @@
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Thermal Intern (Summer 2027)</t>
+          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
+          <t>USA - Hazelwood, MO</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2545,27 +2545,27 @@
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>BETA Technologies</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>BETA Internship</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>South Burlington, Vermont, United States</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2583,7 +2583,7 @@
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/betatechnologiesinc/jobs/4218580009</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2603,7 +2603,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2621,7 +2621,7 @@
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
         </is>
       </c>
     </row>
@@ -2633,15 +2633,15 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>USA - Hazelwood, MO</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2659,7 +2659,7 @@
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
         </is>
       </c>
     </row>
@@ -2671,15 +2671,15 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2697,7 +2697,7 @@
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
         </is>
       </c>
     </row>
@@ -2709,15 +2709,15 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2735,7 +2735,7 @@
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
         </is>
       </c>
     </row>
@@ -2747,15 +2747,15 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2773,7 +2773,7 @@
       <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
         </is>
       </c>
     </row>
@@ -2785,15 +2785,15 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2811,7 +2811,7 @@
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -2831,7 +2831,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2849,7 +2849,7 @@
       <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
         </is>
       </c>
     </row>
@@ -2861,15 +2861,15 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2887,7 +2887,7 @@
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
         </is>
       </c>
     </row>
@@ -2899,15 +2899,15 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2925,7 +2925,7 @@
       <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
         </is>
       </c>
     </row>
@@ -2937,15 +2937,15 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2963,7 +2963,7 @@
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
         </is>
       </c>
     </row>
@@ -2975,15 +2975,15 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3001,7 +3001,7 @@
       <c r="G62" s="4" t="inlineStr"/>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
         </is>
       </c>
     </row>
@@ -3013,15 +3013,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Environment, Health, and Safety (EHS)</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
+          <t>USA - Auburn, WA</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3039,7 +3039,7 @@
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Auburn-WA/Boeing-Summer-2027-Internship-Program--Paid----Environment--Health--and-Safety--EHS-_JR2026519561</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3059,7 +3059,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3077,7 +3077,7 @@
       <c r="G64" s="4" t="inlineStr"/>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3115,7 +3115,7 @@
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
         </is>
       </c>
     </row>
@@ -3127,15 +3127,15 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Environment, Health, and Safety (EHS)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>USA - Auburn, WA</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3153,7 +3153,7 @@
       <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Auburn-WA/Boeing-Summer-2027-Internship-Program--Paid----Environment--Health--and-Safety--EHS-_JR2026519561</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
+          <t>Intern to Entry Level Conversion – Business Functions (All) (Summer 2026 Intern Program)</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3173,14 +3173,14 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3191,7 +3191,7 @@
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Intern-to-Entry-Level-Conversion---Business-Functions--All---Summer-2026-Intern-Program-_JR2026516335</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
+          <t>Intern to Intern Conversion - Engineering (Summer 2026 Intern Program)</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3211,14 +3211,14 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3229,27 +3229,27 @@
       <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Intern-to-Intern-Conversion---Engineering--Summer-2026-Intern-Program-_JR2026516288</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
+          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3267,34 +3267,34 @@
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
+          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Intern to Entry Level Conversion – Business Functions (All) (Summer 2026 Intern Program)</t>
+          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -3305,7 +3305,7 @@
       <c r="G70" s="4" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Intern-to-Entry-Level-Conversion---Business-Functions--All---Summer-2026-Intern-Program-_JR2026516335</t>
+          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
+          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3325,7 +3325,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3343,7 +3343,7 @@
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
+          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
         </is>
       </c>
     </row>
@@ -3355,15 +3355,15 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
+          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3381,7 +3381,7 @@
       <c r="G72" s="4" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
+          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
         </is>
       </c>
     </row>
@@ -3393,15 +3393,15 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
+          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3419,7 +3419,7 @@
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
+          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
+          <t>Summer 2027 - Embedded Software Engineering Internship</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3439,7 +3439,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3457,7 +3457,7 @@
       <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
+          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
+          <t>Summer 2027 - Embedded Software Engineering Internship</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3477,7 +3477,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3495,7 +3495,7 @@
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
+          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
         </is>
       </c>
     </row>
@@ -3507,15 +3507,15 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Embedded Software Engineering Internship</t>
+          <t>Summer 2027 - Finance Internship</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3533,7 +3533,7 @@
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
+          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
         </is>
       </c>
     </row>
@@ -3545,15 +3545,15 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Embedded Software Engineering Internship</t>
+          <t>Summer 2027 - GNC Internship</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3571,7 +3571,7 @@
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
+          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Finance Internship</t>
+          <t>Summer 2027 - Manufacturing Internship</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3591,7 +3591,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3609,7 +3609,7 @@
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
+          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
         </is>
       </c>
     </row>
@@ -3621,15 +3621,15 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - GNC Internship</t>
+          <t>Summer 2027 - Mechanical Engineering Internship</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3647,7 +3647,7 @@
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
+          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
         </is>
       </c>
     </row>
@@ -3659,15 +3659,15 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Manufacturing Internship</t>
+          <t>Summer 2027 - Mechanical Engineering Internship</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3685,7 +3685,7 @@
       <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
+          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
         </is>
       </c>
     </row>
@@ -3697,15 +3697,15 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Internship</t>
+          <t>Summer 2027 - Supply Chain Internship</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3723,7 +3723,7 @@
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
+          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Internship</t>
+          <t>Summer 2027 - Systems Engineering Internship</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3743,7 +3743,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3761,7 +3761,7 @@
       <c r="G82" s="4" t="inlineStr"/>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
+          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
         </is>
       </c>
     </row>
@@ -3773,15 +3773,15 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Supply Chain Internship</t>
+          <t>Summer 2027 - Systems Engineering Internship</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3799,7 +3799,7 @@
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
+          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
         </is>
       </c>
     </row>
@@ -3811,15 +3811,15 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Systems Engineering Internship</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3837,7 +3837,7 @@
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
+          <t>https://jobs.lever.co/CesiumAstro/18d2c72e-30cd-4145-8b12-7db3a492d541</t>
         </is>
       </c>
     </row>
@@ -3849,15 +3849,15 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Systems Engineering Internship</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3875,7 +3875,7 @@
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
+          <t>https://jobs.lever.co/CesiumAstro/e82f19e5-68f7-4d87-816f-cf405191952e</t>
         </is>
       </c>
     </row>
@@ -3887,15 +3887,15 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>Summer 2027 – Test Engineering Internship</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3913,27 +3913,27 @@
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/18d2c72e-30cd-4145-8b12-7db3a492d541</t>
+          <t>https://jobs.lever.co/CesiumAstro/ab7dd1c4-7196-4cae-8fbd-cddec993b9b8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>E-Space</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>E-Space 2027 Summer Internship, Arlington TX</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3951,27 +3951,27 @@
       <c r="G87" s="4" t="inlineStr"/>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e82f19e5-68f7-4d87-816f-cf405191952e</t>
+          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Test Engineering Internship</t>
+          <t>Finance Intern – US – Summer 2027</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
+          <t>Evendale</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3989,27 +3989,23 @@
       <c r="G88" s="4" t="inlineStr"/>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ab7dd1c4-7196-4cae-8fbd-cddec993b9b8</t>
+          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>E-Space</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>E-Space 2027 Summer Internship, Arlington TX</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Arlington, TX</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
+          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr"/>
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4027,27 +4023,23 @@
       <c r="G89" s="4" t="inlineStr"/>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
+          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Finance Intern – US – Summer 2027</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Evendale</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
+          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4065,23 +4057,27 @@
       <c r="G90" s="4" t="inlineStr"/>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="6" t="inlineStr">
+          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4099,23 +4095,27 @@
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
+          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="6" t="inlineStr">
+          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4133,7 +4133,7 @@
       <c r="G92" s="4" t="inlineStr"/>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
+          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
         </is>
       </c>
     </row>
@@ -4145,22 +4145,22 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
+          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -4171,7 +4171,7 @@
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
+          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
+          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4191,7 +4191,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4209,7 +4209,7 @@
       <c r="G94" s="4" t="inlineStr"/>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
+          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
+          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -4229,7 +4229,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4247,7 +4247,7 @@
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
+          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
         </is>
       </c>
     </row>
@@ -4259,15 +4259,15 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
+          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4285,7 +4285,7 @@
       <c r="G96" s="4" t="inlineStr"/>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
+          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
         </is>
       </c>
     </row>
@@ -4297,15 +4297,15 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
+          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4323,7 +4323,7 @@
       <c r="G97" s="4" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
+          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -4343,7 +4343,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4361,7 +4361,7 @@
       <c r="G98" s="4" t="inlineStr"/>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
+          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -4381,7 +4381,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4399,7 +4399,7 @@
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
+          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
         </is>
       </c>
     </row>
@@ -4411,15 +4411,15 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4437,7 +4437,7 @@
       <c r="G100" s="4" t="inlineStr"/>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
+          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
         </is>
       </c>
     </row>
@@ -4449,15 +4449,15 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
+          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4475,7 +4475,7 @@
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
+          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
+          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -4495,7 +4495,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4513,7 +4513,7 @@
       <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
+          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
+          <t>Supply Chain Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -4533,7 +4533,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4551,7 +4551,7 @@
       <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
+          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
         </is>
       </c>
     </row>
@@ -4563,15 +4563,15 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Intern - Spring/Summer 2027</t>
+          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4589,19 +4589,19 @@
       <c r="G104" s="4" t="inlineStr"/>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
+          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
+          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4609,7 +4609,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4627,7 +4627,7 @@
       <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
+          <t>Dynamics Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -4647,7 +4647,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4665,7 +4665,7 @@
       <c r="G106" s="4" t="inlineStr"/>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Dynamics Engineering Intern – Summer 2027</t>
+          <t>Electrical Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -4685,7 +4685,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4703,7 +4703,7 @@
       <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern – Summer 2027</t>
+          <t>GNC Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -4723,7 +4723,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4741,7 +4741,7 @@
       <c r="G108" s="4" t="inlineStr"/>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>GNC Engineering Intern – Summer 2027</t>
+          <t>Mechanical  Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -4761,7 +4761,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4779,7 +4779,7 @@
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Mechanical  Engineering Intern – Summer 2027</t>
+          <t>RF Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -4799,7 +4799,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4817,7 +4817,7 @@
       <c r="G110" s="4" t="inlineStr"/>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411919008</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern – Summer 2027</t>
+          <t>Simulation Software Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -4837,7 +4837,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4855,7 +4855,7 @@
       <c r="G111" s="4" t="inlineStr"/>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411919008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5418727008</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Simulation Software Engineering Intern - Summer 2027</t>
+          <t>Software Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -4875,7 +4875,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4893,7 +4893,7 @@
       <c r="G112" s="4" t="inlineStr"/>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5418727008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411920008</t>
         </is>
       </c>
     </row>
@@ -4905,22 +4905,22 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Summer 2027</t>
+          <t>Supply Chain Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -4931,7 +4931,7 @@
       <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411920008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr"/>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr"/>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr"/>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5091,7 +5091,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5129,7 +5129,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5167,7 +5167,7 @@
           <t>Toronto, CAN</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5205,7 +5205,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5240,10 +5240,10 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
+          <t>Toronto, CAN</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5261,7 +5261,7 @@
       <c r="G122" s="4" t="inlineStr"/>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
         </is>
       </c>
     </row>
@@ -5278,10 +5278,10 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5299,7 +5299,7 @@
       <c r="G123" s="4" t="inlineStr"/>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
           <t>Pasadena, CA</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5357,7 +5357,7 @@
           <t>Littleton, CO</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5395,7 +5395,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5433,7 +5433,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5471,7 +5471,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5509,7 +5509,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5547,7 +5547,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5585,7 +5585,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5623,7 +5623,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5661,7 +5661,7 @@
           <t>Wallops Island, VA</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5696,10 +5696,10 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5717,7 +5717,7 @@
       <c r="G134" s="4" t="inlineStr"/>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
           <t>Toronto, CAN</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5772,10 +5772,10 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
+          <t>Silver Spring, MD</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5793,7 +5793,7 @@
       <c r="G136" s="4" t="inlineStr"/>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
           <t>Tucson, AZ</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5851,7 +5851,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5889,7 +5889,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5927,7 +5927,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5965,7 +5965,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6003,7 +6003,7 @@
           <t>Albuquerque, NM</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6041,7 +6041,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6076,10 +6076,10 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6097,7 +6097,7 @@
       <c r="G144" s="4" t="inlineStr"/>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
         </is>
       </c>
     </row>
@@ -6114,10 +6114,10 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
+          <t>Middle River, MD</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6135,7 +6135,7 @@
       <c r="G145" s="4" t="inlineStr"/>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
         </is>
       </c>
     </row>
@@ -6152,10 +6152,10 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6173,7 +6173,7 @@
       <c r="G146" s="4" t="inlineStr"/>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
           <t>Albuquerque, NM</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6231,7 +6231,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6269,7 +6269,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6307,7 +6307,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6342,10 +6342,10 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6363,7 +6363,7 @@
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -6380,10 +6380,10 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
+          <t>Tucson, AZ</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6401,7 +6401,7 @@
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
         </is>
       </c>
     </row>
@@ -6418,10 +6418,10 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
+          <t>Chantilly, VA</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6439,7 +6439,7 @@
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
         </is>
       </c>
     </row>
@@ -6456,10 +6456,10 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
+          <t>Pasadena, CA</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6477,7 +6477,7 @@
       <c r="G154" s="4" t="inlineStr"/>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6535,7 +6535,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6570,10 +6570,10 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Stennis Space Center, MS</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6591,7 +6591,7 @@
       <c r="G157" s="4" t="inlineStr"/>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
         </is>
       </c>
     </row>
@@ -6608,10 +6608,10 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
+          <t>Stennis Space Center, MS</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6629,7 +6629,7 @@
       <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D159" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6687,7 +6687,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D160" s="6" t="inlineStr">
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6725,7 +6725,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6763,7 +6763,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6801,7 +6801,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6839,7 +6839,7 @@
           <t>Seattle, Washington</t>
         </is>
       </c>
-      <c r="D164" s="6" t="inlineStr">
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6877,7 +6877,7 @@
           <t>San Diego, California</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D165" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6915,7 +6915,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D166" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6953,7 +6953,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D167" s="6" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6991,7 +6991,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7029,7 +7029,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7067,7 +7067,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D170" s="6" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7105,7 +7105,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D171" s="6" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7143,7 +7143,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7181,7 +7181,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D173" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7219,7 +7219,7 @@
           <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7257,7 +7257,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D175" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7295,7 +7295,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D176" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr"/>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr"/>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr"/>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr"/>
-      <c r="D180" s="6" t="inlineStr">
+      <c r="D180" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr"/>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr"/>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr"/>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7669,7 +7669,7 @@
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
-      <c r="D188" s="7" t="inlineStr">
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr"/>
-      <c r="D189" s="7" t="inlineStr">
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
-      <c r="D190" s="7" t="inlineStr">
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
-      <c r="D191" s="7" t="inlineStr">
+      <c r="D191" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
-      <c r="D192" s="7" t="inlineStr">
+      <c r="D192" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -8239,7 +8239,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8651,7 +8651,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8689,7 +8689,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8727,7 +8727,7 @@
           <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8765,7 +8765,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8803,7 +8803,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8841,7 +8841,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8879,7 +8879,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8917,7 +8917,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8955,7 +8955,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8993,7 +8993,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9031,7 +9031,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9069,7 +9069,7 @@
           <t>San Diego, California</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9107,7 +9107,7 @@
           <t>Seattle, Washington</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9145,7 +9145,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9183,7 +9183,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9221,7 +9221,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9259,7 +9259,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9297,7 +9297,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9332,10 +9332,10 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Stennis Space Center, MS</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9353,7 +9353,7 @@
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
         </is>
       </c>
     </row>
@@ -9370,10 +9370,10 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+          <t>Stennis Space Center, MS</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9391,7 +9391,7 @@
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9449,7 +9449,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9484,10 +9484,10 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9505,7 +9505,7 @@
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -9522,10 +9522,10 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
+          <t>Tucson, AZ</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9543,7 +9543,7 @@
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
         </is>
       </c>
     </row>
@@ -9560,10 +9560,10 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
+          <t>Chantilly, VA</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9581,7 +9581,7 @@
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
         </is>
       </c>
     </row>
@@ -9598,10 +9598,10 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
+          <t>Pasadena, CA</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9619,7 +9619,7 @@
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9639,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9677,7 +9677,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9715,7 +9715,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9750,10 +9750,10 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9771,7 +9771,7 @@
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
         </is>
       </c>
     </row>
@@ -9788,10 +9788,10 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
+          <t>Middle River, MD</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9809,7 +9809,7 @@
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
         </is>
       </c>
     </row>
@@ -9826,10 +9826,10 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9847,7 +9847,7 @@
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
           <t>Albuquerque, NM</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9905,7 +9905,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9943,7 +9943,7 @@
           <t>Albuquerque, NM</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9981,7 +9981,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10019,7 +10019,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10057,7 +10057,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10095,7 +10095,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10133,7 +10133,7 @@
           <t>Tucson, AZ</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10168,10 +10168,10 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10189,7 +10189,7 @@
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
           <t>Toronto, CAN</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10244,10 +10244,10 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
+          <t>Silver Spring, MD</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10265,7 +10265,7 @@
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10323,7 +10323,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10361,7 +10361,7 @@
           <t>Wallops Island, VA</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10399,7 +10399,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10437,7 +10437,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10475,7 +10475,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10513,7 +10513,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10551,7 +10551,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10589,7 +10589,7 @@
           <t>Littleton, CO</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10624,10 +10624,10 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
+          <t>Toronto, CAN</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10645,7 +10645,7 @@
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
         </is>
       </c>
     </row>
@@ -10662,10 +10662,10 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10683,7 +10683,7 @@
       <c r="G70" s="4" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10703,7 @@
           <t>Pasadena, CA</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10741,7 +10741,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10779,7 +10779,7 @@
           <t>Toronto, CAN</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10817,7 +10817,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10855,7 +10855,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10995,7 +10995,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11033,7 +11033,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11071,7 +11071,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11109,7 +11109,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11147,7 +11147,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11185,7 +11185,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11223,7 +11223,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11261,7 +11261,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11299,7 +11299,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11337,7 +11337,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11375,7 +11375,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11413,7 +11413,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11451,7 +11451,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11489,7 +11489,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11527,7 +11527,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11565,7 +11565,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11603,7 +11603,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11641,7 +11641,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11679,7 +11679,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11717,7 +11717,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11755,7 +11755,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11793,7 +11793,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11827,7 +11827,7 @@
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11861,7 +11861,7 @@
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11899,7 +11899,7 @@
           <t>Evendale</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11937,7 +11937,7 @@
           <t>Arlington, TX</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -11975,7 +11975,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12013,7 +12013,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12051,7 +12051,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12089,7 +12089,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12127,7 +12127,7 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12165,7 +12165,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12203,7 +12203,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12241,7 +12241,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12279,7 +12279,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12317,7 +12317,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12355,7 +12355,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12393,7 +12393,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12431,7 +12431,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12469,7 +12469,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12507,7 +12507,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12545,7 +12545,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12583,7 +12583,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12621,7 +12621,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12659,7 +12659,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12697,7 +12697,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12735,7 +12735,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12773,7 +12773,7 @@
           <t>USA - Auburn, WA</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12811,7 +12811,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12849,7 +12849,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12887,7 +12887,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12925,7 +12925,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -12963,7 +12963,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13001,7 +13001,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13039,7 +13039,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13077,7 +13077,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13115,7 +13115,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13153,7 +13153,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13191,7 +13191,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13229,7 +13229,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13267,7 +13267,7 @@
           <t>USA - Hazelwood, MO</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13305,7 +13305,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13343,7 +13343,7 @@
           <t>South Burlington, Vermont, United States</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13381,7 +13381,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13419,7 +13419,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13457,7 +13457,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13495,7 +13495,7 @@
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13533,7 +13533,7 @@
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13571,7 +13571,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13609,7 +13609,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13647,7 +13647,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13685,7 +13685,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13723,7 +13723,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13761,7 +13761,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D152" s="6" t="inlineStr">
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13799,7 +13799,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13837,7 +13837,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="D154" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13875,7 +13875,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13913,7 +13913,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13951,7 +13951,7 @@
           <t xml:space="preserve">San Francisco </t>
         </is>
       </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -13989,7 +13989,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="D158" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14027,7 +14027,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D159" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14065,7 +14065,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D160" s="6" t="inlineStr">
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14103,7 +14103,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14141,7 +14141,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14179,7 +14179,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14217,7 +14217,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D164" s="6" t="inlineStr">
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14255,7 +14255,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D165" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14293,7 +14293,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D166" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14331,7 +14331,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D167" s="6" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14369,7 +14369,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14407,7 +14407,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14445,7 +14445,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D170" s="6" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14483,7 +14483,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D171" s="6" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14521,7 +14521,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14559,7 +14559,7 @@
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D173" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14597,7 +14597,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14635,7 +14635,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D175" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14673,7 +14673,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D176" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14711,7 +14711,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14749,7 +14749,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14787,7 +14787,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14825,7 +14825,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D180" s="6" t="inlineStr">
+      <c r="D180" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14863,7 +14863,7 @@
           <t>Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14901,7 +14901,7 @@
           <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14939,7 +14939,7 @@
           <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -14977,7 +14977,7 @@
           <t>Ashville, Ohio, United States</t>
         </is>
       </c>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15015,7 +15015,7 @@
           <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
         </is>
       </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15053,7 +15053,7 @@
           <t>Costa Mesa, California, United States</t>
         </is>
       </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15091,7 +15091,7 @@
           <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15196,7 +15196,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15234,7 +15234,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15272,7 +15272,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15310,7 +15310,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15348,7 +15348,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15386,7 +15386,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15424,7 +15424,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15462,7 +15462,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15500,7 +15500,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15538,7 +15538,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15576,7 +15576,7 @@
           <t>Arlington, TX</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15614,7 +15614,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15652,7 +15652,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15690,7 +15690,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -15845,7 +15845,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -15875,7 +15875,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -15905,7 +15905,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -15935,7 +15935,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -15965,7 +15965,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -15995,7 +15995,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16025,7 +16025,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16055,7 +16055,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16085,7 +16085,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16115,7 +16115,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16145,7 +16145,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16175,7 +16175,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16205,7 +16205,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16235,7 +16235,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16265,7 +16265,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16295,7 +16295,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16325,7 +16325,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16355,7 +16355,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16385,7 +16385,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16415,7 +16415,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16445,7 +16445,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16475,7 +16475,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -16505,7 +16505,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -16535,7 +16535,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -16565,7 +16565,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -16595,7 +16595,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -16625,7 +16625,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -16655,7 +16655,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16685,7 +16685,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16715,7 +16715,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16745,7 +16745,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16775,7 +16775,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16805,7 +16805,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16835,7 +16835,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16865,7 +16865,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16895,7 +16895,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16925,7 +16925,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16955,7 +16955,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -16985,7 +16985,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -17015,7 +17015,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -17045,7 +17045,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -17075,7 +17075,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -17105,7 +17105,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17135,7 +17135,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17165,7 +17165,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17195,7 +17195,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17225,7 +17225,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17255,7 +17255,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17285,7 +17285,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17315,7 +17315,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17345,7 +17345,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17375,7 +17375,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17405,7 +17405,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17435,7 +17435,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17465,7 +17465,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17495,7 +17495,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17525,7 +17525,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17555,7 +17555,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17585,7 +17585,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17615,7 +17615,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17645,7 +17645,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17675,7 +17675,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17705,7 +17705,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17735,7 +17735,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17765,7 +17765,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17795,7 +17795,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17825,7 +17825,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17855,7 +17855,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17885,7 +17885,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17915,7 +17915,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17945,7 +17945,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -17975,7 +17975,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18005,7 +18005,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18035,7 +18035,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18065,7 +18065,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18095,7 +18095,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18125,7 +18125,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18155,7 +18155,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18185,7 +18185,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18215,7 +18215,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18245,7 +18245,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18275,7 +18275,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18305,7 +18305,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18335,7 +18335,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18365,7 +18365,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18395,7 +18395,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18425,7 +18425,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18455,7 +18455,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -18485,7 +18485,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$215</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
@@ -65,11 +65,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
@@ -81,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -695,109 +695,109 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2027 Supply Chain Intern</t>
+          <t>2027 Electrical Engineer Intern</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
+          <t>2027 Flight Software Engineer Intern</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>Costa Mesa, California, United States</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>2027 Industrial Engineer Intern</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
         </is>
       </c>
     </row>
@@ -809,15 +809,15 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2027 Electrical Engineer Intern</t>
+          <t>2027 Manufacturing Engineer Intern</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -829,13 +829,13 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
         </is>
       </c>
     </row>
@@ -847,15 +847,15 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2027 Flight Software Engineer Intern</t>
+          <t>2027 Manufacturing Optimization Engineer Intern</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+          <t>Ashville, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -867,13 +867,13 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
         </is>
       </c>
     </row>
@@ -885,33 +885,33 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2027 Industrial Engineer Intern</t>
+          <t>2027 Mechanical Engineer Intern</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
         </is>
       </c>
     </row>
@@ -923,15 +923,15 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Engineer Intern</t>
+          <t>2027 Software Engineer Intern</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -943,13 +943,13 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
         </is>
       </c>
     </row>
@@ -961,33 +961,33 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Optimization Engineer Intern</t>
+          <t>2027 Supply Chain Intern</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
         </is>
       </c>
     </row>
@@ -999,15 +999,15 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2027 Mechanical Engineer Intern</t>
+          <t>Winter 2027 Manufacturing Engineer Co-op</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+          <t>Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1019,33 +1019,33 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2027 Software Engineer Intern</t>
+          <t>Antenna Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1057,33 +1057,33 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Winter 2027 Manufacturing Engineer Co-op</t>
+          <t>Antenna Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1095,13 +1095,13 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Antenna Associate (Summer 2027)</t>
+          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1121,7 +1121,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1133,13 +1133,13 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Antenna Intern (Summer 2027)</t>
+          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1159,25 +1159,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
+          <t>Avionics Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1197,7 +1197,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1209,13 +1209,13 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
+          <t>Avionics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1235,25 +1235,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Avionics Associate Engineer (Summer 2027)</t>
+          <t>CAD Engineer Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1273,7 +1273,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1285,13 +1285,13 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Avionics Intern (Summer 2027)</t>
+          <t>CAD Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1311,7 +1311,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1323,13 +1323,13 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
         </is>
       </c>
     </row>
@@ -1341,15 +1341,15 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Associate (Summer 2027)</t>
+          <t>Electrical Integration Associate - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1361,13 +1361,13 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Intern (Summer 2027)</t>
+          <t>Electrical Integration Intern - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1387,7 +1387,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1399,13 +1399,13 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
         </is>
       </c>
     </row>
@@ -1417,15 +1417,15 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Associate - RF (Summer 2027)</t>
+          <t>Electrical Reliability Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1437,13 +1437,13 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Intern - RF (Summer 2027)</t>
+          <t>Electrical Reliability Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1463,7 +1463,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1475,13 +1475,13 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Associate (Summer 2027)</t>
+          <t>FPGA Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1501,7 +1501,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1513,13 +1513,13 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Intern (Summer 2027)</t>
+          <t>FPGA Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1539,7 +1539,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1551,13 +1551,13 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>FPGA Associate (Summer 2027)</t>
+          <t>Flight Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1589,13 +1589,13 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>FPGA Intern (Summer 2027)</t>
+          <t>Flight Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1615,7 +1615,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1627,13 +1627,13 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Associate (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1653,7 +1653,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1665,13 +1665,13 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Intern (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1691,7 +1691,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1703,13 +1703,13 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
+          <t>Harness Design Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1741,13 +1741,13 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
+          <t>Harness Manufacturing Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1767,7 +1767,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1779,13 +1779,13 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Harness Design Engineer Intern (Summer 2027)</t>
+          <t>Harness Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1805,7 +1805,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1817,13 +1817,13 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Associate (Summer 2027)</t>
+          <t>Mechanical Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1843,7 +1843,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1855,13 +1855,13 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Intern (Summer 2027)</t>
+          <t>Mechanical Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1881,7 +1881,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1893,13 +1893,13 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Associate Engineer (Summer 2027)</t>
+          <t>Power Electronics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1919,7 +1919,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1931,13 +1931,13 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
         </is>
       </c>
     </row>
@@ -1949,15 +1949,15 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer Intern (Summer 2027)</t>
+          <t>Production Quality Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+          <t xml:space="preserve">San Francisco </t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1969,13 +1969,13 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Power Electronics Intern (Summer 2027)</t>
+          <t>Propulsion Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1995,7 +1995,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2007,13 +2007,13 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
         </is>
       </c>
     </row>
@@ -2025,15 +2025,15 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Production Quality Intern (Summer 2027)</t>
+          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco </t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2045,13 +2045,13 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineer Intern (Summer 2027)</t>
+          <t>Propulsion Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2071,7 +2071,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2083,13 +2083,13 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
+          <t>RF Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2109,25 +2109,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Test Intern (Summer 2027)</t>
+          <t>RF Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2147,25 +2147,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Associate (Summer 2027)</t>
+          <t>RF Validation Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2185,25 +2185,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Intern (Summer 2027)</t>
+          <t>RF Validation Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2223,25 +2223,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Associate (Summer 2027)</t>
+          <t>Reliability Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2261,7 +2261,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2273,13 +2273,13 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Intern (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2299,7 +2299,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2311,13 +2311,13 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Reliability Test Intern (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2337,7 +2337,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2349,13 +2349,13 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
+          <t>Software Developer, Network Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2387,13 +2387,13 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
+          <t>Software Developer, Network Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2413,7 +2413,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2425,13 +2425,13 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
         </is>
       </c>
     </row>
@@ -2443,15 +2443,15 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Associate (Summer 2027)</t>
+          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2463,13 +2463,13 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
         </is>
       </c>
     </row>
@@ -2481,15 +2481,15 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Intern (Summer 2027)</t>
+          <t>Software Engineer Backend Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2501,13 +2501,13 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
         </is>
       </c>
     </row>
@@ -2519,15 +2519,15 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
+          <t>Technical Project Management Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2539,13 +2539,13 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
         </is>
       </c>
     </row>
@@ -2557,15 +2557,15 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Backend Intern (Summer 2027)</t>
+          <t>Thermal Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2577,13 +2577,13 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Technical Project Management Intern (Summer 2027)</t>
+          <t>Thermal Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2603,7 +2603,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2615,33 +2615,33 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Thermal Associate Engineer (Summer 2027)</t>
+          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2653,33 +2653,33 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Thermal Intern (Summer 2027)</t>
+          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+          <t>USA - Hazelwood, MO</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2691,13 +2691,13 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2717,7 +2717,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2729,13 +2729,13 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
         </is>
       </c>
     </row>
@@ -2747,15 +2747,15 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>USA - Hazelwood, MO</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2767,13 +2767,13 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2793,7 +2793,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2805,13 +2805,13 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
         </is>
       </c>
     </row>
@@ -2823,15 +2823,15 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2843,13 +2843,13 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
         </is>
       </c>
     </row>
@@ -2861,15 +2861,15 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2881,13 +2881,13 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2907,7 +2907,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2919,13 +2919,13 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2945,7 +2945,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2957,13 +2957,13 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
         </is>
       </c>
     </row>
@@ -2975,15 +2975,15 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2995,13 +2995,13 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
         </is>
       </c>
     </row>
@@ -3013,15 +3013,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3033,13 +3033,13 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
         </is>
       </c>
     </row>
@@ -3051,15 +3051,15 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3071,13 +3071,13 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3109,13 +3109,13 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
         </is>
       </c>
     </row>
@@ -3127,15 +3127,15 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3147,13 +3147,13 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3173,7 +3173,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3185,13 +3185,13 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3211,7 +3211,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3223,13 +3223,13 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3249,7 +3249,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3261,71 +3261,71 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
+          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
+          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
+          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3337,13 +3337,13 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
+          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
         </is>
       </c>
     </row>
@@ -3355,15 +3355,15 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
+          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3375,13 +3375,13 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
+          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
         </is>
       </c>
     </row>
@@ -3398,10 +3398,10 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3413,13 +3413,13 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
+          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
+          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3439,7 +3439,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3451,13 +3451,13 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
+          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
         </is>
       </c>
     </row>
@@ -3474,10 +3474,10 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3489,13 +3489,13 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
+          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
         </is>
       </c>
     </row>
@@ -3507,15 +3507,15 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
+          <t>Summer 2027 - Embedded Software Engineering Internship</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3527,13 +3527,13 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
+          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
         </is>
       </c>
     </row>
@@ -3550,10 +3550,10 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3565,13 +3565,13 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
+          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Embedded Software Engineering Internship</t>
+          <t>Summer 2027 - Finance Internship</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3591,7 +3591,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3603,13 +3603,13 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
+          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
         </is>
       </c>
     </row>
@@ -3621,15 +3621,15 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Finance Internship</t>
+          <t>Summer 2027 - GNC Internship</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3641,13 +3641,13 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
+          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
         </is>
       </c>
     </row>
@@ -3659,15 +3659,15 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - GNC Internship</t>
+          <t>Summer 2027 - Manufacturing Internship</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3679,13 +3679,13 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
+          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Manufacturing Internship</t>
+          <t>Summer 2027 - Mechanical Engineering Internship</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3705,7 +3705,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3717,13 +3717,13 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
+          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
         </is>
       </c>
     </row>
@@ -3740,10 +3740,10 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3755,13 +3755,13 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
+          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Internship</t>
+          <t>Summer 2027 - Supply Chain Internship</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3781,7 +3781,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3793,13 +3793,13 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
+          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Supply Chain Internship</t>
+          <t>Summer 2027 - Systems Engineering Internship</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -3819,7 +3819,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3831,13 +3831,13 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
+          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
         </is>
       </c>
     </row>
@@ -3854,10 +3854,10 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3869,13 +3869,13 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
+          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Systems Engineering Internship</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -3895,25 +3895,25 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
+          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
           <t>Arlington, TX</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
           <t>Evendale</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4115,7 +4115,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr"/>
@@ -4153,7 +4153,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
@@ -4191,7 +4191,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
@@ -4229,7 +4229,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
@@ -4267,7 +4267,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
@@ -4305,7 +4305,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
@@ -4343,7 +4343,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
@@ -4381,7 +4381,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
@@ -4419,7 +4419,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
@@ -4457,7 +4457,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
@@ -4533,7 +4533,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
@@ -4647,7 +4647,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
@@ -4685,7 +4685,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
@@ -4723,7 +4723,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
@@ -4761,7 +4761,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
@@ -4799,7 +4799,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
@@ -4875,7 +4875,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
@@ -4989,7 +4989,7 @@
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
@@ -5027,7 +5027,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr"/>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr"/>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
@@ -5167,7 +5167,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
@@ -5205,7 +5205,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
@@ -5243,7 +5243,7 @@
           <t>Toronto, CAN</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
@@ -5281,7 +5281,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
@@ -5319,7 +5319,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
@@ -5357,7 +5357,7 @@
           <t>Toronto, CAN</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
@@ -5395,7 +5395,7 @@
           <t>Pasadena, CA</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
@@ -5433,7 +5433,7 @@
           <t>Littleton, CO</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
@@ -5471,7 +5471,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
@@ -5509,7 +5509,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
@@ -5547,7 +5547,7 @@
           <t>Littleton, CO</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
@@ -5585,7 +5585,7 @@
           <t>Washington, DC</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
@@ -5623,7 +5623,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
@@ -5661,7 +5661,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
@@ -5699,7 +5699,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
@@ -5737,7 +5737,7 @@
           <t>Wallops Island, VA</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
@@ -5813,7 +5813,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
           <t>Silver Spring, MD</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
@@ -5889,7 +5889,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
@@ -5927,7 +5927,7 @@
           <t>Toronto, CAN</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
@@ -5965,7 +5965,7 @@
           <t>Tucson, AZ</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
@@ -6003,7 +6003,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
@@ -6041,7 +6041,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
@@ -6079,7 +6079,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
@@ -6117,7 +6117,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
@@ -6155,7 +6155,7 @@
           <t>Albuquerque, NM</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
@@ -6193,7 +6193,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
@@ -6231,7 +6231,7 @@
           <t>Wallops Island, VA</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
@@ -6269,7 +6269,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
@@ -6307,7 +6307,7 @@
           <t>Albuquerque, NM</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
@@ -6345,7 +6345,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
@@ -6383,7 +6383,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D152" s="6" t="inlineStr">
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
@@ -6421,7 +6421,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
@@ -6459,7 +6459,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="D154" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
@@ -6497,7 +6497,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
           <t>Pasadena, CA</t>
         </is>
       </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
@@ -6573,7 +6573,7 @@
           <t>Tucson, AZ</t>
         </is>
       </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
@@ -6611,7 +6611,7 @@
           <t>Chantilly, VA</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="D158" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
@@ -6649,7 +6649,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D159" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D160" s="6" t="inlineStr">
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
@@ -6725,7 +6725,7 @@
           <t>Stennis Space Center, MS</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
@@ -6763,7 +6763,7 @@
           <t>Wallops Island, VA</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
@@ -6801,7 +6801,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
@@ -6839,7 +6839,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D164" s="6" t="inlineStr">
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
@@ -6877,7 +6877,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D165" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
@@ -6915,7 +6915,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D166" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
@@ -6953,7 +6953,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D167" s="6" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
@@ -6991,7 +6991,7 @@
           <t>Seattle, Washington</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
@@ -7029,7 +7029,7 @@
           <t>San Diego, California</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
@@ -7067,7 +7067,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D170" s="6" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
@@ -7105,7 +7105,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D171" s="6" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
@@ -7143,7 +7143,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D173" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
@@ -7219,7 +7219,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
@@ -7257,7 +7257,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D175" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
@@ -7295,7 +7295,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D176" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
@@ -7333,7 +7333,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
@@ -7371,7 +7371,7 @@
           <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
@@ -7409,7 +7409,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
@@ -7447,7 +7447,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D180" s="6" t="inlineStr">
+      <c r="D180" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr"/>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr"/>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr"/>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr"/>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="D191" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
@@ -7859,7 +7859,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D192" s="6" t="inlineStr">
+      <c r="D192" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
@@ -7897,7 +7897,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D193" s="6" t="inlineStr">
+      <c r="D193" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
@@ -7935,7 +7935,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D194" s="6" t="inlineStr">
+      <c r="D194" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
@@ -7973,7 +7973,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D195" s="6" t="inlineStr">
+      <c r="D195" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
@@ -8011,7 +8011,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D196" s="6" t="inlineStr">
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr"/>
@@ -8049,7 +8049,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D197" s="6" t="inlineStr">
+      <c r="D197" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
@@ -8087,7 +8087,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D198" s="6" t="inlineStr">
+      <c r="D198" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
@@ -8125,7 +8125,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D199" s="6" t="inlineStr">
+      <c r="D199" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
@@ -8163,7 +8163,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D200" s="6" t="inlineStr">
+      <c r="D200" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr"/>
@@ -8201,7 +8201,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D201" s="6" t="inlineStr">
+      <c r="D201" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
@@ -8239,7 +8239,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D202" s="6" t="inlineStr">
+      <c r="D202" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr"/>
@@ -8277,7 +8277,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D203" s="6" t="inlineStr">
+      <c r="D203" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
@@ -8315,7 +8315,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D204" s="6" t="inlineStr">
+      <c r="D204" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
@@ -8353,7 +8353,7 @@
           <t>South Burlington, Vermont, United States</t>
         </is>
       </c>
-      <c r="D205" s="7" t="inlineStr">
+      <c r="D205" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8391,7 +8391,7 @@
           <t>USA - Auburn, WA</t>
         </is>
       </c>
-      <c r="D206" s="7" t="inlineStr">
+      <c r="D206" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8429,7 +8429,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D207" s="7" t="inlineStr">
+      <c r="D207" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8467,7 +8467,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D208" s="7" t="inlineStr">
+      <c r="D208" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8505,7 +8505,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D209" s="7" t="inlineStr">
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8543,7 +8543,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D210" s="7" t="inlineStr">
+      <c r="D210" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr"/>
-      <c r="D211" s="7" t="inlineStr">
+      <c r="D211" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr"/>
-      <c r="D212" s="7" t="inlineStr">
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr"/>
-      <c r="D213" s="7" t="inlineStr">
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
-      <c r="D214" s="7" t="inlineStr">
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr"/>
-      <c r="D215" s="7" t="inlineStr">
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8747,7 +8747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8802,122 +8802,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2027 Supply Chain Intern</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CesiumAstro</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CesiumAstro</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9001,7 +8887,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -9011,7 +8897,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9039,7 +8925,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -9049,7 +8935,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9077,7 +8963,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -9087,7 +8973,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9113,7 +8999,7 @@
           <t>Littleton, CO</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9125,7 +9011,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9151,7 +9037,7 @@
           <t>Washington, DC</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9163,7 +9049,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9189,7 +9075,7 @@
           <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9201,7 +9087,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9227,7 +9113,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9239,7 +9125,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -9265,7 +9151,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9277,7 +9163,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -9303,7 +9189,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9315,7 +9201,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -9341,7 +9227,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9353,7 +9239,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -9379,7 +9265,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9391,7 +9277,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -9417,7 +9303,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9429,7 +9315,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -9455,7 +9341,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9467,7 +9353,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -9493,7 +9379,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9505,7 +9391,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -9531,7 +9417,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9543,7 +9429,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -9569,7 +9455,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9581,7 +9467,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -9607,7 +9493,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9619,7 +9505,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -9645,7 +9531,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9657,7 +9543,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -9683,7 +9569,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9695,7 +9581,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -9721,7 +9607,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9733,7 +9619,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -9759,7 +9645,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9771,7 +9657,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -9797,7 +9683,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9809,7 +9695,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -9835,7 +9721,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9847,7 +9733,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
@@ -9873,7 +9759,7 @@
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9885,7 +9771,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -9911,7 +9797,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9923,7 +9809,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -10016,7 +9902,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10028,7 +9914,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -10054,7 +9940,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10066,7 +9952,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -10092,7 +9978,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10104,7 +9990,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -10130,7 +10016,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10142,7 +10028,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -10168,7 +10054,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10180,7 +10066,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -10206,7 +10092,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10218,7 +10104,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -10244,7 +10130,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10256,7 +10142,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -10282,7 +10168,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10294,7 +10180,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -10320,7 +10206,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10332,7 +10218,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -10358,7 +10244,7 @@
           <t>Arlington, TX</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10370,7 +10256,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -10396,7 +10282,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10408,7 +10294,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -10434,7 +10320,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10446,7 +10332,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -10472,7 +10358,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10484,7 +10370,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -10627,7 +10513,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10637,7 +10523,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10657,7 +10543,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10667,7 +10553,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10687,7 +10573,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10697,7 +10583,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10717,7 +10603,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10727,7 +10613,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10747,7 +10633,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10757,7 +10643,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10777,7 +10663,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10787,7 +10673,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10807,7 +10693,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10817,7 +10703,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10837,7 +10723,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10847,7 +10733,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -10867,7 +10753,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10877,7 +10763,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10897,7 +10783,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10907,7 +10793,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10927,7 +10813,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10937,7 +10823,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10957,7 +10843,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10967,7 +10853,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10987,7 +10873,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10997,7 +10883,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -11017,7 +10903,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11027,7 +10913,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -11047,7 +10933,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11057,7 +10943,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -11077,7 +10963,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11087,7 +10973,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11107,7 +10993,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11117,7 +11003,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11137,7 +11023,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11147,7 +11033,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -11167,7 +11053,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11177,7 +11063,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11197,7 +11083,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11207,7 +11093,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11227,7 +11113,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11237,7 +11123,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -11257,7 +11143,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11267,7 +11153,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11287,7 +11173,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11297,7 +11183,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11317,7 +11203,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11327,7 +11213,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -11347,7 +11233,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11357,7 +11243,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11377,7 +11263,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11387,7 +11273,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -11407,7 +11293,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11417,7 +11303,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -11437,7 +11323,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11447,7 +11333,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -11467,7 +11353,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11477,7 +11363,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -11497,7 +11383,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11507,7 +11393,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11527,7 +11413,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11537,7 +11423,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11557,7 +11443,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11567,7 +11453,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11587,7 +11473,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11597,7 +11483,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11617,7 +11503,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11627,7 +11513,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -11647,7 +11533,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11657,7 +11543,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -11677,7 +11563,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11687,7 +11573,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -11707,7 +11593,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11717,7 +11603,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11737,7 +11623,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11747,7 +11633,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11767,7 +11653,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11777,7 +11663,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -11797,7 +11683,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11807,7 +11693,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -11827,7 +11713,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11837,7 +11723,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -11857,7 +11743,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11867,7 +11753,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -11887,7 +11773,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11897,7 +11783,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -11917,7 +11803,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11927,7 +11813,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -11947,7 +11833,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11957,7 +11843,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -11977,7 +11863,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11987,7 +11873,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -12007,7 +11893,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12017,7 +11903,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -12037,7 +11923,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12047,7 +11933,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -12067,7 +11953,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12077,7 +11963,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -12097,7 +11983,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12107,7 +11993,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -12127,7 +12013,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12137,7 +12023,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -12157,7 +12043,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12167,7 +12053,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -12187,7 +12073,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12197,7 +12083,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -12217,7 +12103,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12227,7 +12113,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -12247,7 +12133,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12257,7 +12143,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -12277,7 +12163,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12287,7 +12173,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -12307,7 +12193,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12317,7 +12203,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -12337,7 +12223,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12347,7 +12233,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -12367,7 +12253,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12377,7 +12263,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -12397,7 +12283,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12407,7 +12293,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -12427,7 +12313,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12437,7 +12323,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -12457,7 +12343,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12467,7 +12353,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -12487,7 +12373,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12497,7 +12383,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -12517,7 +12403,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12527,7 +12413,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -12547,7 +12433,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12557,7 +12443,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -12577,7 +12463,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12587,7 +12473,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -12607,7 +12493,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12617,7 +12503,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -12637,7 +12523,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12647,7 +12533,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -12667,7 +12553,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12677,7 +12563,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -12697,7 +12583,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12707,7 +12593,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -12727,7 +12613,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12737,7 +12623,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -12757,7 +12643,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12767,7 +12653,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -12787,7 +12673,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12797,7 +12683,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -12817,7 +12703,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12827,7 +12713,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -12847,7 +12733,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12857,7 +12743,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -12877,7 +12763,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12887,7 +12773,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -12907,7 +12793,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12917,7 +12803,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -12937,7 +12823,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12947,7 +12833,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -12967,7 +12853,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12977,7 +12863,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -12997,7 +12883,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13007,7 +12893,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -13027,7 +12913,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13037,7 +12923,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -13057,7 +12943,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13067,7 +12953,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -13087,7 +12973,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13097,7 +12983,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -13117,7 +13003,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13127,7 +13013,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -13147,7 +13033,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13157,7 +13043,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -13177,7 +13063,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13187,7 +13073,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -13207,7 +13093,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13217,7 +13103,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -13237,7 +13123,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13247,7 +13133,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -13267,7 +13153,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13277,7 +13163,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -16,9 +16,9 @@
     <sheet name="SOURCE HEALTH" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$215</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SOURCE HEALTH'!$A$1:$F$90</definedName>
@@ -65,6 +65,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
@@ -76,11 +81,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE5CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H215"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -690,38 +690,38 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2027 Electrical Engineer Intern</t>
+          <t>RF Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
         </is>
       </c>
     </row>
@@ -733,15 +733,15 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2027 Flight Software Engineer Intern</t>
+          <t>2027 Electrical Engineer Intern</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -753,13 +753,13 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
         </is>
       </c>
     </row>
@@ -771,33 +771,33 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2027 Industrial Engineer Intern</t>
+          <t>2027 Flight Software Engineer Intern</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+          <t>Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
         </is>
       </c>
     </row>
@@ -809,33 +809,33 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Engineer Intern</t>
+          <t>2027 Industrial Engineer Intern</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
         </is>
       </c>
     </row>
@@ -847,15 +847,15 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Optimization Engineer Intern</t>
+          <t>2027 Manufacturing Engineer Intern</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -867,13 +867,13 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
         </is>
       </c>
     </row>
@@ -885,15 +885,15 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2027 Mechanical Engineer Intern</t>
+          <t>2027 Manufacturing Optimization Engineer Intern</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+          <t>Ashville, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -905,13 +905,13 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2027 Software Engineer Intern</t>
+          <t>2027 Mechanical Engineer Intern</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -931,7 +931,7 @@
           <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -943,13 +943,13 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
         </is>
       </c>
     </row>
@@ -961,33 +961,33 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2027 Supply Chain Intern</t>
+          <t>2027 Software Engineer Intern</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
         </is>
       </c>
     </row>
@@ -999,53 +999,53 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Winter 2027 Manufacturing Engineer Co-op</t>
+          <t>2027 Supply Chain Intern</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Antenna Associate (Summer 2027)</t>
+          <t>Winter 2027 Manufacturing Engineer Co-op</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+          <t>Ashville, Ohio, United States; Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1057,13 +1057,13 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Antenna Intern (Summer 2027)</t>
+          <t>Antenna Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1083,7 +1083,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1095,13 +1095,13 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
+          <t>Antenna Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1121,7 +1121,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1133,13 +1133,13 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
+          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1159,25 +1159,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Avionics Associate Engineer (Summer 2027)</t>
+          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1197,25 +1197,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Avionics Intern (Summer 2027)</t>
+          <t>Avionics Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1235,7 +1235,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1247,13 +1247,13 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Associate (Summer 2027)</t>
+          <t>Avionics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1273,7 +1273,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1285,13 +1285,13 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Intern (Summer 2027)</t>
+          <t>CAD Engineer Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1311,7 +1311,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1323,13 +1323,13 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
         </is>
       </c>
     </row>
@@ -1341,15 +1341,15 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Associate - RF (Summer 2027)</t>
+          <t>CAD Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1361,13 +1361,13 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
         </is>
       </c>
     </row>
@@ -1379,15 +1379,15 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Intern - RF (Summer 2027)</t>
+          <t>Electrical Integration Associate - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1399,13 +1399,13 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Associate (Summer 2027)</t>
+          <t>Electrical Integration Intern - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1425,7 +1425,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1437,13 +1437,13 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Intern (Summer 2027)</t>
+          <t>Electrical Reliability Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1463,7 +1463,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1475,13 +1475,13 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>FPGA Associate (Summer 2027)</t>
+          <t>Electrical Reliability Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1501,7 +1501,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1513,13 +1513,13 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>FPGA Intern (Summer 2027)</t>
+          <t>FPGA Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1539,7 +1539,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1551,13 +1551,13 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Associate (Summer 2027)</t>
+          <t>FPGA Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1589,13 +1589,13 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Intern (Summer 2027)</t>
+          <t>Flight Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1615,7 +1615,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1627,13 +1627,13 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
+          <t>Flight Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1653,7 +1653,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1665,13 +1665,13 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1691,7 +1691,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1703,13 +1703,13 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Harness Design Engineer Intern (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1741,13 +1741,13 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Associate (Summer 2027)</t>
+          <t>Harness Design Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1767,7 +1767,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1779,13 +1779,13 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Intern (Summer 2027)</t>
+          <t>Harness Manufacturing Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1805,7 +1805,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1817,13 +1817,13 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Associate Engineer (Summer 2027)</t>
+          <t>Harness Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1843,7 +1843,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1855,13 +1855,13 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer Intern (Summer 2027)</t>
+          <t>Mechanical Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1881,7 +1881,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1893,13 +1893,13 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Power Electronics Intern (Summer 2027)</t>
+          <t>Mechanical Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1919,7 +1919,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1931,13 +1931,13 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
         </is>
       </c>
     </row>
@@ -1949,15 +1949,15 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Production Quality Intern (Summer 2027)</t>
+          <t>Power Electronics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco </t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1969,13 +1969,13 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
         </is>
       </c>
     </row>
@@ -1987,15 +1987,15 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineer Intern (Summer 2027)</t>
+          <t>Production Quality Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
+          <t xml:space="preserve">San Francisco </t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2007,13 +2007,13 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
+          <t>Propulsion Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2033,7 +2033,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2045,13 +2045,13 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Test Intern (Summer 2027)</t>
+          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2071,7 +2071,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2083,13 +2083,13 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Associate (Summer 2027)</t>
+          <t>Propulsion Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2109,25 +2109,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Intern (Summer 2027)</t>
+          <t>RF Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2147,7 +2147,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2159,13 +2159,13 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Associate (Summer 2027)</t>
+          <t>RF Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2185,25 +2185,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Intern (Summer 2027)</t>
+          <t>RF Validation Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2223,7 +2223,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2235,13 +2235,13 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Reliability Test Intern (Summer 2027)</t>
+          <t>RF Validation Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2261,7 +2261,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2273,13 +2273,13 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
+          <t>Reliability Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2299,7 +2299,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2311,13 +2311,13 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2337,7 +2337,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2349,13 +2349,13 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Associate (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2387,13 +2387,13 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Intern (Summer 2027)</t>
+          <t>Software Developer, Network Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2413,7 +2413,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2425,13 +2425,13 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
         </is>
       </c>
     </row>
@@ -2443,15 +2443,15 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
+          <t>Software Developer, Network Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2463,13 +2463,13 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Backend Intern (Summer 2027)</t>
+          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2489,7 +2489,7 @@
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2501,13 +2501,13 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
         </is>
       </c>
     </row>
@@ -2519,15 +2519,15 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Technical Project Management Intern (Summer 2027)</t>
+          <t>Software Engineer Backend Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2539,13 +2539,13 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Thermal Associate Engineer (Summer 2027)</t>
+          <t>Technical Project Management Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2565,7 +2565,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2577,13 +2577,13 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Thermal Intern (Summer 2027)</t>
+          <t>Thermal Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2603,7 +2603,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2615,33 +2615,33 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
+          <t>Thermal Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2653,13 +2653,13 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
         </is>
       </c>
     </row>
@@ -2671,15 +2671,15 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
+          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>USA - Hazelwood, MO</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2691,13 +2691,13 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
         </is>
       </c>
     </row>
@@ -2709,15 +2709,15 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
+          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
+          <t>USA - Hazelwood, MO</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2729,13 +2729,13 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2755,7 +2755,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2767,13 +2767,13 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2793,7 +2793,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2805,13 +2805,13 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
         </is>
       </c>
     </row>
@@ -2823,15 +2823,15 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2843,13 +2843,13 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
         </is>
       </c>
     </row>
@@ -2861,15 +2861,15 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2881,13 +2881,13 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
         </is>
       </c>
     </row>
@@ -2899,15 +2899,15 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2919,13 +2919,13 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
         </is>
       </c>
     </row>
@@ -2937,15 +2937,15 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2957,13 +2957,13 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -2983,7 +2983,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2995,13 +2995,13 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
         </is>
       </c>
     </row>
@@ -3013,15 +3013,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3033,13 +3033,13 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
         </is>
       </c>
     </row>
@@ -3051,15 +3051,15 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3071,13 +3071,13 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
         </is>
       </c>
     </row>
@@ -3089,15 +3089,15 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3109,13 +3109,13 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
         </is>
       </c>
     </row>
@@ -3127,15 +3127,15 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3147,13 +3147,13 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
         </is>
       </c>
     </row>
@@ -3165,15 +3165,15 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3185,13 +3185,13 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
         </is>
       </c>
     </row>
@@ -3203,15 +3203,15 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3223,13 +3223,13 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
         </is>
       </c>
     </row>
@@ -3241,15 +3241,15 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3261,51 +3261,51 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
         </is>
       </c>
     </row>
@@ -3322,28 +3322,28 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
+          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
         </is>
       </c>
     </row>
@@ -3355,15 +3355,15 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
+          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3375,13 +3375,13 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
+          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
         </is>
       </c>
     </row>
@@ -3398,10 +3398,10 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3413,13 +3413,13 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
+          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
+          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3439,7 +3439,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3451,13 +3451,13 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
+          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
         </is>
       </c>
     </row>
@@ -3474,10 +3474,10 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3489,13 +3489,13 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
+          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
         </is>
       </c>
     </row>
@@ -3507,15 +3507,15 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Embedded Software Engineering Internship</t>
+          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3527,13 +3527,13 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
+          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
         </is>
       </c>
     </row>
@@ -3550,10 +3550,10 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3565,13 +3565,13 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
+          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Finance Internship</t>
+          <t>Summer 2027 - Embedded Software Engineering Internship</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3591,7 +3591,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3603,13 +3603,13 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
+          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
         </is>
       </c>
     </row>
@@ -3621,15 +3621,15 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - GNC Internship</t>
+          <t>Summer 2027 - Finance Internship</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3641,13 +3641,13 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
+          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
         </is>
       </c>
     </row>
@@ -3659,15 +3659,15 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Manufacturing Internship</t>
+          <t>Summer 2027 - GNC Internship</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3679,13 +3679,13 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
+          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Internship</t>
+          <t>Summer 2027 - Manufacturing Internship</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3705,7 +3705,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3717,13 +3717,13 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
+          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
         </is>
       </c>
     </row>
@@ -3740,10 +3740,10 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3755,13 +3755,13 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
+          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Supply Chain Internship</t>
+          <t>Summer 2027 - Mechanical Engineering Internship</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3781,7 +3781,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3793,13 +3793,13 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
+          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Systems Engineering Internship</t>
+          <t>Summer 2027 - Supply Chain Internship</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -3819,7 +3819,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3831,13 +3831,13 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
+          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
         </is>
       </c>
     </row>
@@ -3854,10 +3854,10 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3869,13 +3869,13 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
+          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>Summer 2027 - Systems Engineering Internship</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -3895,25 +3895,25 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
+          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
         </is>
       </c>
     </row>
@@ -3925,53 +3925,53 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Test Engineering Internship</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ab7dd1c4-7196-4cae-8fbd-cddec993b9b8</t>
+          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>E-Space</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>E-Space 2027 Summer Internship, Arlington TX</t>
+          <t>Summer 2027 – Test Engineering Internship</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3983,33 +3983,33 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
+          <t>https://jobs.lever.co/CesiumAstro/ab7dd1c4-7196-4cae-8fbd-cddec993b9b8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>E-Space</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Finance Intern – US – Summer 2027</t>
+          <t>E-Space 2027 Summer Internship, Arlington TX</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Evendale</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4021,29 +4021,33 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
+          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr"/>
-      <c r="D90" s="5" t="inlineStr">
+          <t>Finance Intern – US – Summer 2027</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Evendale</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4055,13 +4059,13 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr"/>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
+          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4077,11 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
+          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4095,27 +4099,23 @@
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
+          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
+          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr"/>
+      <c r="D92" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4127,13 +4127,13 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr"/>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
+          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -4153,7 +4153,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4165,13 +4165,13 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
+          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
         </is>
       </c>
     </row>
@@ -4183,33 +4183,33 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
+          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
+          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
         </is>
       </c>
     </row>
@@ -4221,33 +4221,33 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
+          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
+          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
         </is>
       </c>
     </row>
@@ -4259,33 +4259,33 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
+          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
+          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
         </is>
       </c>
     </row>
@@ -4297,33 +4297,33 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
+          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
+          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
         </is>
       </c>
     </row>
@@ -4335,15 +4335,15 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
+          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4355,13 +4355,13 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
+          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
         </is>
       </c>
     </row>
@@ -4373,15 +4373,15 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
+          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4393,13 +4393,13 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
+          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
+          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -4419,7 +4419,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4431,13 +4431,13 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
+          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -4457,7 +4457,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4469,13 +4469,13 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
+          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
         </is>
       </c>
     </row>
@@ -4487,15 +4487,15 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4507,13 +4507,13 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
+          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
         </is>
       </c>
     </row>
@@ -4525,15 +4525,15 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4545,13 +4545,13 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
+          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
+          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -4571,7 +4571,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4583,13 +4583,13 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
+          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Intern - Spring/Summer 2027</t>
+          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4609,7 +4609,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4621,13 +4621,13 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
+          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
         </is>
       </c>
     </row>
@@ -4639,15 +4639,15 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
+          <t>Supply Chain Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4659,25 +4659,25 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
+          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
+          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -4685,7 +4685,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4697,13 +4697,13 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
+          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Dynamics Engineering Intern – Summer 2027</t>
+          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -4723,7 +4723,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4735,13 +4735,13 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern – Summer 2027</t>
+          <t>Dynamics Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -4761,7 +4761,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4773,13 +4773,13 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>GNC Engineering Intern – Summer 2027</t>
+          <t>Electrical Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -4799,7 +4799,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4811,13 +4811,13 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Mechanical  Engineering Intern – Summer 2027</t>
+          <t>GNC Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -4837,7 +4837,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4849,13 +4849,13 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern – Summer 2027</t>
+          <t>Mechanical  Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -4875,7 +4875,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D112" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4887,13 +4887,13 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411919008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Simulation Software Engineering Intern - Summer 2027</t>
+          <t>RF Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -4913,7 +4913,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4925,13 +4925,13 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5418727008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411919008</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Summer 2027</t>
+          <t>Simulation Software Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -4951,7 +4951,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4963,13 +4963,13 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411920008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5418727008</t>
         </is>
       </c>
     </row>
@@ -4981,33 +4981,33 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Internship - Summer 2027</t>
+          <t>Software Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411920008</t>
         </is>
       </c>
     </row>
@@ -5019,49 +5019,53 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Vehicle Operations Engineering Intern – Summer 2027</t>
+          <t>Supply Chain Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411914008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>MIT Lincoln Laboratory</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Airborne Radar Systems and Techniques Intern (Summer 2027) - Group 105</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr"/>
-      <c r="D117" s="5" t="inlineStr">
+          <t>Vehicle Operations Engineering Intern – Summer 2027</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5073,13 +5077,13 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>https://careers.ll.mit.edu/job/Lexington-Airborne-Radar-Systems-and-Techniques-Intern-%28Summer-2027%29-Group-105-MA-02420/1410581200/</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411914008</t>
         </is>
       </c>
     </row>
@@ -5091,11 +5095,11 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Optical Engineering Intern - Optical Engineer (Summer 2027) - Group 78</t>
+          <t>Airborne Radar Systems and Techniques Intern (Summer 2027) - Group 105</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr"/>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5107,13 +5111,13 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>https://careers.ll.mit.edu/job/Lexington-Optical-Engineering-Intern-Optical-Engineer-%28Summer-2027%29-Group-78-MA-02420/1433573800/</t>
+          <t>https://careers.ll.mit.edu/job/Lexington-Airborne-Radar-Systems-and-Techniques-Intern-%28Summer-2027%29-Group-105-MA-02420/1410581200/</t>
         </is>
       </c>
     </row>
@@ -5125,11 +5129,11 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Software and Electronics Engineering Intern (Summer 2027) - Group 76</t>
+          <t>Optical Engineering Intern - Optical Engineer (Summer 2027) - Group 78</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5141,33 +5145,29 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>https://careers.ll.mit.edu/job/Lexington-Software-and-Electronics-Engineering-Intern-%28Summer-2027%29-Group-76-MA-02420/1431440000/</t>
+          <t>https://careers.ll.mit.edu/job/Lexington-Optical-Engineering-Intern-Optical-Engineer-%28Summer-2027%29-Group-78-MA-02420/1433573800/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>MIT Lincoln Laboratory</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Additive Manufacturing Intern Summer 2027</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
+          <t>Software and Electronics Engineering Intern (Summer 2027) - Group 76</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr"/>
+      <c r="D120" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5179,13 +5179,13 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984600003</t>
+          <t>https://careers.ll.mit.edu/job/Lexington-Software-and-Electronics-Engineering-Intern-%28Summer-2027%29-Group-76-MA-02420/1431440000/</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Avionics Engineering Intern Summer 2027</t>
+          <t>Additive Manufacturing Intern Summer 2027</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -5205,7 +5205,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D121" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5217,13 +5217,13 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989733003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984600003</t>
         </is>
       </c>
     </row>
@@ -5235,15 +5235,15 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Business Development Intern Summer 2027</t>
+          <t>Avionics Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5255,13 +5255,13 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7993738003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989733003</t>
         </is>
       </c>
     </row>
@@ -5273,15 +5273,15 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Combustion Devices Intern Summer 2027</t>
+          <t>Business Development Intern Summer 2027</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
+          <t>Toronto, CAN</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5293,13 +5293,13 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986748003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7993738003</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern Summer 2027</t>
+          <t>Combustion Devices Intern Summer 2027</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -5319,7 +5319,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="D124" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5331,13 +5331,13 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986748003</t>
         </is>
       </c>
     </row>
@@ -5354,10 +5354,10 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5369,13 +5369,13 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
           <t>Pasadena, CA</t>
         </is>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D126" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
@@ -5425,15 +5425,15 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Intern Summer 2027</t>
+          <t>Electrical Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
+          <t>Toronto, CAN</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5445,13 +5445,13 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989722003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
         </is>
       </c>
     </row>
@@ -5463,15 +5463,15 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Fluid Component Intern Summer 2027</t>
+          <t>Flight Software Intern Summer 2027</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
+          <t>Littleton, CO</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5483,13 +5483,13 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990365003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989722003</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Fluid Systems Intern Summer 2027</t>
+          <t>Fluid Component Intern Summer 2027</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -5509,7 +5509,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D129" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5521,13 +5521,13 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986794003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990365003</t>
         </is>
       </c>
     </row>
@@ -5539,33 +5539,33 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Government Operations Intern Summer 2027</t>
+          <t>Fluid Systems Intern Summer 2027</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986794003</t>
         </is>
       </c>
     </row>
@@ -5582,10 +5582,10 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
+          <t>Littleton, CO</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5597,13 +5597,13 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
         </is>
       </c>
     </row>
@@ -5615,33 +5615,33 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>HITL Engineering Intern Summer 2027</t>
+          <t>Government Operations Intern Summer 2027</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990268003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Indirect Procurement Intern Summer 2027</t>
+          <t>HITL Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -5661,7 +5661,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D133" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5673,13 +5673,13 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989063003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990268003</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Test Intern Summer 2027</t>
+          <t>Indirect Procurement Intern Summer 2027</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -5699,7 +5699,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D134" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5711,13 +5711,13 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987250003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989063003</t>
         </is>
       </c>
     </row>
@@ -5729,15 +5729,15 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Intern Summer 2027</t>
+          <t>Integration &amp; Test Intern Summer 2027</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5749,13 +5749,13 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987250003</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
@@ -5810,10 +5810,10 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5825,13 +5825,13 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
         </is>
       </c>
     </row>
@@ -5843,15 +5843,15 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern Summer 2027</t>
+          <t>Manufacturing Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
+          <t>Middle River, MD</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5863,13 +5863,13 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D139" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
@@ -5924,10 +5924,10 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="inlineStr">
+          <t>Silver Spring, MD</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5939,13 +5939,13 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -5957,15 +5957,15 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Optical Engineering Intern Summer 2027</t>
+          <t>Mechanical Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
+          <t>Toronto, CAN</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5977,13 +5977,13 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992102003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
         </is>
       </c>
     </row>
@@ -5995,15 +5995,15 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>People &amp; Culture Intern Summer 2027</t>
+          <t>Optical Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
+          <t>Tucson, AZ</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6015,13 +6015,13 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990245003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992102003</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Analyst Intern Summer 2027</t>
+          <t>People &amp; Culture Intern Summer 2027</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -6041,7 +6041,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D143" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6053,13 +6053,13 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986820003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990245003</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Design Intern Summer 2027</t>
+          <t>Propulsion Analyst Intern Summer 2027</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -6079,7 +6079,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D144" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6091,13 +6091,13 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986816003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986820003</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Intern Summer 2027</t>
+          <t>Propulsion Design Intern Summer 2027</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -6117,7 +6117,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D145" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6129,13 +6129,13 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986792003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986816003</t>
         </is>
       </c>
     </row>
@@ -6147,15 +6147,15 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D Engineering Intern Summer 2027</t>
+          <t>Propulsion Intern Summer 2027</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6167,13 +6167,13 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996576003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986792003</t>
         </is>
       </c>
     </row>
@@ -6185,15 +6185,15 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern Summer 2027</t>
+          <t>R&amp;D Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
+          <t>Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6205,13 +6205,13 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991657003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996576003</t>
         </is>
       </c>
     </row>
@@ -6228,10 +6228,10 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6243,13 +6243,13 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
         </is>
       </c>
     </row>
@@ -6266,10 +6266,10 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
+          <t>Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6281,13 +6281,13 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
         </is>
       </c>
     </row>
@@ -6304,10 +6304,10 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="inlineStr">
+          <t>Middle River, MD</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6319,13 +6319,13 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
         </is>
       </c>
     </row>
@@ -6342,10 +6342,10 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6357,13 +6357,13 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D152" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
@@ -6421,7 +6421,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="D153" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
@@ -6459,7 +6459,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="D154" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
@@ -6494,10 +6494,10 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
+          <t>Tucson, AZ</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6509,13 +6509,13 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
         </is>
       </c>
     </row>
@@ -6532,10 +6532,10 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
+          <t>Chantilly, VA</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6547,13 +6547,13 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
         </is>
       </c>
     </row>
@@ -6570,10 +6570,10 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr">
+          <t>Pasadena, CA</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6585,13 +6585,13 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -6608,10 +6608,10 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6623,13 +6623,13 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="D160" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Stennis Space Center, MS</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6737,13 +6737,13 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
         </is>
       </c>
     </row>
@@ -6760,10 +6760,10 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
+          <t>Stennis Space Center, MS</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6775,13 +6775,13 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D163" s="5" t="inlineStr">
+      <c r="D163" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
@@ -6839,7 +6839,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="D164" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
@@ -6877,7 +6877,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D165" s="5" t="inlineStr">
+      <c r="D165" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
@@ -6915,7 +6915,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D166" s="5" t="inlineStr">
+      <c r="D166" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
@@ -6953,7 +6953,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D167" s="5" t="inlineStr">
+      <c r="D167" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
@@ -6991,7 +6991,7 @@
           <t>Seattle, Washington</t>
         </is>
       </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="D168" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
@@ -7029,7 +7029,7 @@
           <t>San Diego, California</t>
         </is>
       </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="D169" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
@@ -7067,7 +7067,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D170" s="5" t="inlineStr">
+      <c r="D170" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
@@ -7105,7 +7105,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D171" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
@@ -7143,7 +7143,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="D172" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D173" s="5" t="inlineStr">
+      <c r="D173" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
@@ -7219,7 +7219,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D174" s="5" t="inlineStr">
+      <c r="D174" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
@@ -7257,7 +7257,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="D175" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
@@ -7295,7 +7295,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="D176" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
@@ -7333,7 +7333,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D177" s="5" t="inlineStr">
+      <c r="D177" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
@@ -7371,7 +7371,7 @@
           <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
         </is>
       </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="D178" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
@@ -7409,7 +7409,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="D179" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
@@ -7447,7 +7447,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="D180" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr"/>
-      <c r="D181" s="5" t="inlineStr">
+      <c r="D181" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr"/>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="D182" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr"/>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="D184" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr"/>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
-      <c r="D191" s="5" t="inlineStr">
+      <c r="D191" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
@@ -7859,7 +7859,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D192" s="5" t="inlineStr">
+      <c r="D192" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
@@ -7897,7 +7897,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D193" s="5" t="inlineStr">
+      <c r="D193" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
@@ -7935,7 +7935,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D194" s="5" t="inlineStr">
+      <c r="D194" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
@@ -7973,7 +7973,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D195" s="5" t="inlineStr">
+      <c r="D195" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
@@ -8011,7 +8011,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="D196" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr"/>
@@ -8049,7 +8049,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D197" s="5" t="inlineStr">
+      <c r="D197" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
@@ -8087,7 +8087,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D198" s="5" t="inlineStr">
+      <c r="D198" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
@@ -8125,7 +8125,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D199" s="5" t="inlineStr">
+      <c r="D199" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
@@ -8163,7 +8163,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D200" s="5" t="inlineStr">
+      <c r="D200" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr"/>
@@ -8201,7 +8201,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D201" s="5" t="inlineStr">
+      <c r="D201" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
@@ -8239,7 +8239,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D202" s="5" t="inlineStr">
+      <c r="D202" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr"/>
@@ -8277,7 +8277,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D203" s="5" t="inlineStr">
+      <c r="D203" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
@@ -8315,7 +8315,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D204" s="5" t="inlineStr">
+      <c r="D204" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
@@ -8353,7 +8353,7 @@
           <t>South Burlington, Vermont, United States</t>
         </is>
       </c>
-      <c r="D205" s="6" t="inlineStr">
+      <c r="D205" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8391,7 +8391,7 @@
           <t>USA - Auburn, WA</t>
         </is>
       </c>
-      <c r="D206" s="6" t="inlineStr">
+      <c r="D206" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8429,7 +8429,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D207" s="6" t="inlineStr">
+      <c r="D207" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8467,7 +8467,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D208" s="6" t="inlineStr">
+      <c r="D208" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8505,7 +8505,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D209" s="6" t="inlineStr">
+      <c r="D209" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8543,7 +8543,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D210" s="6" t="inlineStr">
+      <c r="D210" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr"/>
-      <c r="D211" s="6" t="inlineStr">
+      <c r="D211" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr"/>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="D212" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr"/>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="D213" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="D214" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr"/>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="D215" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8735,8 +8735,46 @@
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>Rocket Lab</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>RF Engineering Intern Summer 2027</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr"/>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991657003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H215"/>
+  <autoFilter ref="A1:H216"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8747,7 +8785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8802,8 +8840,46 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Rocket Lab</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>RF Engineering Intern Summer 2027</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8814,7 +8890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8872,38 +8948,38 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>RF Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8991,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -8923,7 +8999,7 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8935,33 +9011,33 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
+          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2027 Supply Chain Intern</t>
+          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8973,51 +9049,51 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
+          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Government Operations Intern Summer 2027</t>
+          <t>2027 Supply Chain Intern</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
         </is>
       </c>
     </row>
@@ -9034,10 +9110,10 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+          <t>Littleton, CO</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9049,33 +9125,33 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2027 Industrial Engineer Intern</t>
+          <t>Government Operations Intern Summer 2027</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9087,51 +9163,51 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
+          <t>2027 Industrial Engineer Intern</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, California, United States</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9219,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Thermal Engineering Internship - Summer 2027</t>
+          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -9151,7 +9227,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9163,13 +9239,13 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9257,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Structures Engineering Internship - Summer 2027</t>
+          <t>Thermal Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -9189,7 +9265,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9201,13 +9277,13 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9295,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineering Internship - Summer 2027</t>
+          <t>Structures Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -9227,7 +9303,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9239,13 +9315,13 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9333,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Mission Operations Internship - Summer 2027</t>
+          <t>Propulsion Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -9265,7 +9341,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9277,13 +9353,13 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9371,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
+          <t>Mission Operations Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -9303,7 +9379,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9315,13 +9391,13 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9409,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Internship - Summer 2027</t>
+          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -9341,7 +9417,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9353,13 +9429,13 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9447,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
+          <t>Manufacturing Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -9379,7 +9455,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9391,13 +9467,13 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9485,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Formulation Science Internship - Summer 2027</t>
+          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -9417,7 +9493,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9429,13 +9505,13 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9523,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Internship - Summer 2027</t>
+          <t>Formulation Science Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -9455,7 +9531,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9467,13 +9543,13 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9561,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Internship - Summer 2027</t>
+          <t>Flight Software Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -9493,7 +9569,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9505,13 +9581,13 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9599,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Avionics Engineering Internship - Summer 2027</t>
+          <t>Cybersecurity Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -9531,7 +9607,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9543,13 +9619,13 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9637,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
+          <t>Avionics Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -9569,7 +9645,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9581,33 +9657,33 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
+          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+          <t>El Segundo, California, United States</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9619,33 +9695,33 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Intern (Summer 2027)</t>
+          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9657,13 +9733,13 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
+          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9751,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Associate (Summer 2027)</t>
+          <t>RF Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -9683,7 +9759,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9695,13 +9771,13 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9789,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
+          <t>RF Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -9721,7 +9797,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9733,71 +9809,71 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Internship - Summer 2027</t>
+          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
+          <t>Supply Chain Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9809,18 +9885,56 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Hermeus</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
           <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H26"/>
+  <autoFilter ref="A1:H27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9902,7 +10016,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9914,7 +10028,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9940,7 +10054,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9952,7 +10066,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9978,7 +10092,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9990,7 +10104,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -10016,7 +10130,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10028,7 +10142,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -10054,7 +10168,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10066,7 +10180,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -10092,7 +10206,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10104,7 +10218,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -10130,7 +10244,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10142,7 +10256,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -10168,7 +10282,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10180,7 +10294,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -10206,7 +10320,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10218,7 +10332,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -10244,7 +10358,7 @@
           <t>Arlington, TX</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10256,7 +10370,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -10282,7 +10396,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10294,7 +10408,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -10320,7 +10434,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10332,7 +10446,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -10358,7 +10472,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10370,7 +10484,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -10513,7 +10627,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10523,7 +10637,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10543,7 +10657,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10553,7 +10667,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10573,7 +10687,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10583,7 +10697,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10603,7 +10717,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10613,7 +10727,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10633,7 +10747,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10643,7 +10757,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10663,7 +10777,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10673,7 +10787,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10693,7 +10807,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10703,7 +10817,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10723,7 +10837,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10733,7 +10847,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -10753,7 +10867,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10763,7 +10877,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10783,7 +10897,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10793,7 +10907,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10813,7 +10927,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10823,7 +10937,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10843,7 +10957,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10853,7 +10967,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10873,7 +10987,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10883,7 +10997,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10903,7 +11017,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10913,7 +11027,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -10933,7 +11047,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10943,7 +11057,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10963,7 +11077,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10973,7 +11087,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10993,7 +11107,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11003,7 +11117,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11023,7 +11137,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11033,7 +11147,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -11053,7 +11167,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11063,7 +11177,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11083,7 +11197,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11093,7 +11207,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11113,7 +11227,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11123,7 +11237,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -11143,7 +11257,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11153,7 +11267,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11173,7 +11287,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11183,7 +11297,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11203,7 +11317,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11213,7 +11327,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -11233,7 +11347,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11243,7 +11357,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11263,7 +11377,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11273,7 +11387,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -11293,7 +11407,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11303,7 +11417,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -11323,7 +11437,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11333,7 +11447,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -11353,7 +11467,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11363,7 +11477,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -11383,7 +11497,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11393,7 +11507,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11413,7 +11527,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11423,7 +11537,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11443,7 +11557,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11453,7 +11567,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11473,7 +11587,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11483,7 +11597,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11503,7 +11617,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11513,7 +11627,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -11533,7 +11647,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11543,7 +11657,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -11563,7 +11677,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11573,7 +11687,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -11593,7 +11707,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11603,7 +11717,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11623,7 +11737,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11633,7 +11747,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11653,7 +11767,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11663,7 +11777,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -11683,7 +11797,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11693,7 +11807,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -11713,7 +11827,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11723,7 +11837,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -11743,7 +11857,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11753,7 +11867,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -11773,7 +11887,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11783,7 +11897,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -11803,7 +11917,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11813,7 +11927,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -11833,7 +11947,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11843,7 +11957,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -11863,7 +11977,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11873,7 +11987,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -11893,7 +12007,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11903,7 +12017,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -11923,7 +12037,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11933,7 +12047,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11953,7 +12067,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11963,7 +12077,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -11983,7 +12097,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11993,7 +12107,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -12013,7 +12127,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12023,7 +12137,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -12043,7 +12157,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12053,7 +12167,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -12073,7 +12187,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12083,7 +12197,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -12103,7 +12217,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12113,7 +12227,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -12133,7 +12247,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12143,7 +12257,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -12163,7 +12277,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12173,7 +12287,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -12193,7 +12307,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12203,7 +12317,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -12223,7 +12337,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12233,7 +12347,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -12253,7 +12367,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12263,7 +12377,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -12283,7 +12397,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12293,7 +12407,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -12313,7 +12427,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12323,7 +12437,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -12343,7 +12457,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12353,7 +12467,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -12373,7 +12487,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12383,7 +12497,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -12403,7 +12517,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12413,7 +12527,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -12433,7 +12547,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12443,7 +12557,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -12463,7 +12577,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12473,7 +12587,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -12493,7 +12607,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12503,7 +12617,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -12523,7 +12637,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12533,7 +12647,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -12553,7 +12667,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12563,7 +12677,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -12583,7 +12697,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12593,7 +12707,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -12613,7 +12727,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12623,7 +12737,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -12643,7 +12757,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12653,7 +12767,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -12673,7 +12787,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12683,7 +12797,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -12703,7 +12817,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12713,7 +12827,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -12733,7 +12847,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12743,7 +12857,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -12763,7 +12877,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12773,7 +12887,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -12793,7 +12907,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12803,7 +12917,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -12823,7 +12937,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12833,7 +12947,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -12853,7 +12967,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12863,7 +12977,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -12883,7 +12997,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12893,7 +13007,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -12913,7 +13027,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12923,7 +13037,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -12943,7 +13057,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12953,7 +13067,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -12973,7 +13087,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12983,7 +13097,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -13003,7 +13117,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13013,7 +13127,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -13033,7 +13147,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13043,7 +13157,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -13063,7 +13177,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13073,7 +13187,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -13093,7 +13207,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13103,7 +13217,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -13123,7 +13237,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13133,7 +13247,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -13153,7 +13267,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13163,7 +13277,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -16,10 +16,10 @@
     <sheet name="SOURCE HEALTH" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$216</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SOURCE HEALTH'!$A$1:$F$90</definedName>
   </definedNames>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -690,17 +690,17 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern Summer 2027</t>
+          <t>2027 Quality &amp; Test Engineer Intern</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -710,18 +710,18 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257674007?gh_jid=5257674007</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2027 Electrical Engineer Intern</t>
+          <t>2027 Reliability Engineer Intern</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257682007?gh_jid=5257682007</t>
         </is>
       </c>
     </row>
@@ -771,33 +771,33 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2027 Flight Software Engineer Intern</t>
+          <t>2027 Systems Engineer Intern</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257690007?gh_jid=5257690007</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2027 Industrial Engineer Intern</t>
+          <t>2027 Electrical Engineer Intern</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -824,18 +824,18 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Engineer Intern</t>
+          <t>2027 Flight Software Engineer Intern</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
+          <t>Costa Mesa, California, United States</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -867,13 +867,13 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Optimization Engineer Intern</t>
+          <t>2027 Industrial Engineer Intern</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States</t>
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -900,18 +900,18 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2027 Mechanical Engineer Intern</t>
+          <t>2027 Manufacturing Engineer Intern</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -943,13 +943,13 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2027 Software Engineer Intern</t>
+          <t>2027 Manufacturing Optimization Engineer Intern</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+          <t>Ashville, Ohio, United States</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -981,13 +981,13 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2027 Supply Chain Intern</t>
+          <t>2027 Mechanical Engineer Intern</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1014,18 +1014,18 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Winter 2027 Manufacturing Engineer Co-op</t>
+          <t>2027 Software Engineer Intern</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1057,30 +1057,30 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Antenna Associate (Summer 2027)</t>
+          <t>2027 Supply Chain Intern</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1090,35 +1090,35 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Antenna Intern (Summer 2027)</t>
+          <t>Winter 2027 Manufacturing Engineer Co-op</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Ashville, Ohio, United States; Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1133,13 +1133,13 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
+          <t>Antenna Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1171,13 +1171,13 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
+          <t>Antenna Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1204,18 +1204,18 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Avionics Associate Engineer (Summer 2027)</t>
+          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1247,13 +1247,13 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Avionics Intern (Summer 2027)</t>
+          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1280,18 +1280,18 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Associate (Summer 2027)</t>
+          <t>Avionics Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1323,13 +1323,13 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Intern (Summer 2027)</t>
+          <t>Avionics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1361,13 +1361,13 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Associate - RF (Summer 2027)</t>
+          <t>CAD Engineer Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1399,13 +1399,13 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Intern - RF (Summer 2027)</t>
+          <t>CAD Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1437,13 +1437,13 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Associate (Summer 2027)</t>
+          <t>Electrical Integration Associate - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1475,13 +1475,13 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Intern (Summer 2027)</t>
+          <t>Electrical Integration Intern - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1513,13 +1513,13 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>FPGA Associate (Summer 2027)</t>
+          <t>Electrical Reliability Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1551,13 +1551,13 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>FPGA Intern (Summer 2027)</t>
+          <t>Electrical Reliability Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1589,13 +1589,13 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Associate (Summer 2027)</t>
+          <t>FPGA Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1627,13 +1627,13 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Intern (Summer 2027)</t>
+          <t>FPGA Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1665,13 +1665,13 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
+          <t>Flight Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1703,13 +1703,13 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
+          <t>Flight Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1741,13 +1741,13 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Harness Design Engineer Intern (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1779,13 +1779,13 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Associate (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1817,13 +1817,13 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Intern (Summer 2027)</t>
+          <t>Harness Design Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1855,13 +1855,13 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Associate Engineer (Summer 2027)</t>
+          <t>Harness Manufacturing Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1893,13 +1893,13 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer Intern (Summer 2027)</t>
+          <t>Harness Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1931,13 +1931,13 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Power Electronics Intern (Summer 2027)</t>
+          <t>Mechanical Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1969,13 +1969,13 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Production Quality Intern (Summer 2027)</t>
+          <t>Mechanical Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco </t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2007,13 +2007,13 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineer Intern (Summer 2027)</t>
+          <t>Power Electronics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2045,13 +2045,13 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
+          <t>Production Quality Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t xml:space="preserve">San Francisco </t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -2083,13 +2083,13 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Test Intern (Summer 2027)</t>
+          <t>Propulsion Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2121,13 +2121,13 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Associate (Summer 2027)</t>
+          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2154,18 +2154,18 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Intern (Summer 2027)</t>
+          <t>Propulsion Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2192,18 +2192,18 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Associate (Summer 2027)</t>
+          <t>RF Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2230,18 +2230,18 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Intern (Summer 2027)</t>
+          <t>RF Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2268,18 +2268,18 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Reliability Test Intern (Summer 2027)</t>
+          <t>RF Validation Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2311,13 +2311,13 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
+          <t>RF Validation Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2349,13 +2349,13 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
+          <t>Reliability Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2387,13 +2387,13 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Associate (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2425,13 +2425,13 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Intern (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2463,13 +2463,13 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
+          <t>Software Developer, Network Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -2501,13 +2501,13 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Backend Intern (Summer 2027)</t>
+          <t>Software Developer, Network Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -2539,13 +2539,13 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Technical Project Management Intern (Summer 2027)</t>
+          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -2577,13 +2577,13 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Thermal Associate Engineer (Summer 2027)</t>
+          <t>Software Engineer Backend Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -2615,13 +2615,13 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Thermal Intern (Summer 2027)</t>
+          <t>Technical Project Management Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2653,30 +2653,30 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
+          <t>Thermal Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2691,30 +2691,30 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
+          <t>Thermal Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>USA - Hazelwood, MO</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2729,13 +2729,13 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
+          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2767,13 +2767,13 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
         </is>
       </c>
     </row>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
+          <t>USA - Hazelwood, MO</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2805,13 +2805,13 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -2843,13 +2843,13 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
+          <t>USA - Everett, WA</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2881,13 +2881,13 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
+          <t>USA - Everett, WA</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2919,13 +2919,13 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
+          <t>USA - Seattle, WA</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2957,13 +2957,13 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
         </is>
       </c>
     </row>
@@ -2975,12 +2975,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
+          <t>USA - Arlington, VA</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2995,13 +2995,13 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3033,13 +3033,13 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3051,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
+          <t>USA - Seattle, WA</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -3071,13 +3071,13 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
+          <t>USA - Everett, WA</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -3109,13 +3109,13 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
+          <t>USA - Arlington, VA</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -3147,13 +3147,13 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
         </is>
       </c>
     </row>
@@ -3165,12 +3165,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
+          <t>USA - Everett, WA</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -3185,13 +3185,13 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
+          <t>USA - Seattle, WA</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -3223,13 +3223,13 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
         </is>
       </c>
     </row>
@@ -3241,12 +3241,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
+          <t>USA - Everett, WA</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -3261,13 +3261,13 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
+          <t>USA - Seattle, WA</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -3299,30 +3299,30 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>USA - Everett, WA</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -3332,18 +3332,18 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -3370,18 +3370,18 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
+          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
+          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Westminster, CO</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -3413,13 +3413,13 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
+          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -3451,13 +3451,13 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
+          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
+          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3489,13 +3489,13 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
+          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Westminster, CO</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -3527,13 +3527,13 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
+          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Embedded Software Engineering Internship</t>
+          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -3565,13 +3565,13 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
+          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Westminster, CO</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -3603,13 +3603,13 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
+          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Finance Internship</t>
+          <t>Summer 2027 - Embedded Software Engineering Internship</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3641,13 +3641,13 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
+          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - GNC Internship</t>
+          <t>Summer 2027 - Finance Internship</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -3679,13 +3679,13 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
+          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Manufacturing Internship</t>
+          <t>Summer 2027 - GNC Internship</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Westminster, CO</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -3717,13 +3717,13 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
+          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Internship</t>
+          <t>Summer 2027 - Manufacturing Internship</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3755,13 +3755,13 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
+          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -3793,13 +3793,13 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
+          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Supply Chain Internship</t>
+          <t>Summer 2027 - Mechanical Engineering Internship</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -3831,13 +3831,13 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
+          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Systems Engineering Internship</t>
+          <t>Summer 2027 - Supply Chain Internship</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3869,13 +3869,13 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
+          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>Westminster, CO</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -3907,13 +3907,13 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
+          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>Summer 2027 - Systems Engineering Internship</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3940,18 +3940,18 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
+          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
         </is>
       </c>
     </row>
@@ -3963,12 +3963,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Test Engineering Internship</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -3978,35 +3978,35 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ab7dd1c4-7196-4cae-8fbd-cddec993b9b8</t>
+          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>E-Space</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>E-Space 2027 Summer Internship, Arlington TX</t>
+          <t>Summer 2027 – Test Engineering Internship</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Westminster, CO</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -4021,30 +4021,30 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
+          <t>https://jobs.lever.co/CesiumAstro/ab7dd1c4-7196-4cae-8fbd-cddec993b9b8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>E-Space</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Finance Intern – US – Summer 2027</t>
+          <t>E-Space 2027 Summer Internship, Arlington TX</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Evendale</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -4059,28 +4059,32 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr"/>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
+          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr"/>
+          <t>Finance Intern – US – Summer 2027</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Evendale</t>
+        </is>
+      </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -4093,13 +4097,13 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
+          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4115,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
+          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -4133,26 +4137,22 @@
       <c r="G92" s="4" t="inlineStr"/>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
+          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
+          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr"/>
       <c r="D93" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -4165,13 +4165,13 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
+          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4203,13 +4203,13 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
+          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
+          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -4236,18 +4236,18 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
+          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
+          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -4274,18 +4274,18 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
+          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
         </is>
       </c>
     </row>
@@ -4297,12 +4297,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
+          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -4312,18 +4312,18 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
+          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
+          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -4350,18 +4350,18 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
+          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
+          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -4393,13 +4393,13 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
+          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4411,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
+          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -4431,13 +4431,13 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
+          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
+          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -4469,13 +4469,13 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
+          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -4507,13 +4507,13 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
+          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
         </is>
       </c>
     </row>
@@ -4525,12 +4525,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -4545,13 +4545,13 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
+          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4563,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -4583,13 +4583,13 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
+          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
+          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4621,13 +4621,13 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
+          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Intern - Spring/Summer 2027</t>
+          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -4659,13 +4659,13 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
+          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
         </is>
       </c>
     </row>
@@ -4677,12 +4677,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
+          <t>Supply Chain Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -4697,25 +4697,25 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
+          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
+          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -4735,13 +4735,13 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
+          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Dynamics Engineering Intern – Summer 2027</t>
+          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -4773,13 +4773,13 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern – Summer 2027</t>
+          <t>Dynamics Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -4811,13 +4811,13 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>GNC Engineering Intern – Summer 2027</t>
+          <t>Electrical Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -4849,13 +4849,13 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Mechanical  Engineering Intern – Summer 2027</t>
+          <t>GNC Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -4887,13 +4887,13 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern – Summer 2027</t>
+          <t>Mechanical  Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -4925,13 +4925,13 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411919008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Simulation Software Engineering Intern - Summer 2027</t>
+          <t>RF Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -4963,13 +4963,13 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5418727008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411919008</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Summer 2027</t>
+          <t>Simulation Software Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -5001,13 +5001,13 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411920008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5418727008</t>
         </is>
       </c>
     </row>
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Internship - Summer 2027</t>
+          <t>Software Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -5034,18 +5034,18 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411920008</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Vehicle Operations Engineering Intern – Summer 2027</t>
+          <t>Supply Chain Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -5072,33 +5072,37 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411914008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>MIT Lincoln Laboratory</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Airborne Radar Systems and Techniques Intern (Summer 2027) - Group 105</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr"/>
+          <t>Vehicle Operations Engineering Intern – Summer 2027</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -5111,13 +5115,13 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>https://careers.ll.mit.edu/job/Lexington-Airborne-Radar-Systems-and-Techniques-Intern-%28Summer-2027%29-Group-105-MA-02420/1410581200/</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411914008</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5133,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Optical Engineering Intern - Optical Engineer (Summer 2027) - Group 78</t>
+          <t>Airborne Radar Systems and Techniques Intern (Summer 2027) - Group 105</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
@@ -5145,13 +5149,13 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>https://careers.ll.mit.edu/job/Lexington-Optical-Engineering-Intern-Optical-Engineer-%28Summer-2027%29-Group-78-MA-02420/1433573800/</t>
+          <t>https://careers.ll.mit.edu/job/Lexington-Airborne-Radar-Systems-and-Techniques-Intern-%28Summer-2027%29-Group-105-MA-02420/1410581200/</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5167,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Software and Electronics Engineering Intern (Summer 2027) - Group 76</t>
+          <t>Optical Engineering Intern - Optical Engineer (Summer 2027) - Group 78</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
@@ -5179,32 +5183,28 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>https://careers.ll.mit.edu/job/Lexington-Software-and-Electronics-Engineering-Intern-%28Summer-2027%29-Group-76-MA-02420/1431440000/</t>
+          <t>https://careers.ll.mit.edu/job/Lexington-Optical-Engineering-Intern-Optical-Engineer-%28Summer-2027%29-Group-78-MA-02420/1433573800/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>MIT Lincoln Laboratory</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Additive Manufacturing Intern Summer 2027</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
+          <t>Software and Electronics Engineering Intern (Summer 2027) - Group 76</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr"/>
       <c r="D121" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -5217,13 +5217,13 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984600003</t>
+          <t>https://careers.ll.mit.edu/job/Lexington-Software-and-Electronics-Engineering-Intern-%28Summer-2027%29-Group-76-MA-02420/1431440000/</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Avionics Engineering Intern Summer 2027</t>
+          <t>Additive Manufacturing Intern Summer 2027</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -5255,13 +5255,13 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989733003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984600003</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Business Development Intern Summer 2027</t>
+          <t>Avionics Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -5293,13 +5293,13 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7993738003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989733003</t>
         </is>
       </c>
     </row>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Combustion Devices Intern Summer 2027</t>
+          <t>Business Development Intern Summer 2027</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Toronto, CAN</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -5331,13 +5331,13 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986748003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7993738003</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern Summer 2027</t>
+          <t>Combustion Devices Intern Summer 2027</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -5369,13 +5369,13 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986748003</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Toronto, CAN</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -5407,13 +5407,13 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -5445,13 +5445,13 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
         </is>
       </c>
     </row>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Intern Summer 2027</t>
+          <t>Electrical Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -5483,13 +5483,13 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989722003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Fluid Component Intern Summer 2027</t>
+          <t>Flight Software Intern Summer 2027</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Littleton, CO</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -5521,13 +5521,13 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990365003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989722003</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Fluid Systems Intern Summer 2027</t>
+          <t>Fluid Component Intern Summer 2027</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -5559,13 +5559,13 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986794003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990365003</t>
         </is>
       </c>
     </row>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Government Operations Intern Summer 2027</t>
+          <t>Fluid Systems Intern Summer 2027</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -5592,18 +5592,18 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986794003</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Littleton, CO</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -5635,13 +5635,13 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
         </is>
       </c>
     </row>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>HITL Engineering Intern Summer 2027</t>
+          <t>Government Operations Intern Summer 2027</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -5668,18 +5668,18 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990268003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Indirect Procurement Intern Summer 2027</t>
+          <t>HITL Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -5711,13 +5711,13 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989063003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990268003</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Test Intern Summer 2027</t>
+          <t>Indirect Procurement Intern Summer 2027</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -5749,13 +5749,13 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987250003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989063003</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Intern Summer 2027</t>
+          <t>Integration &amp; Test Intern Summer 2027</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -5787,13 +5787,13 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984564003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987250003</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -5825,13 +5825,13 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -5863,13 +5863,13 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984564003</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern Summer 2027</t>
+          <t>Manufacturing Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -5901,13 +5901,13 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
+          <t>Toronto, CAN</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
@@ -5939,13 +5939,13 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
+          <t>Silver Spring, MD</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
@@ -5977,13 +5977,13 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -5995,12 +5995,12 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Optical Engineering Intern Summer 2027</t>
+          <t>Mechanical Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -6015,13 +6015,13 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992102003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>People &amp; Culture Intern Summer 2027</t>
+          <t>Optical Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Tucson, AZ</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
@@ -6053,13 +6053,13 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990245003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992102003</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Analyst Intern Summer 2027</t>
+          <t>People &amp; Culture Intern Summer 2027</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -6091,13 +6091,13 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986820003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990245003</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Design Intern Summer 2027</t>
+          <t>Propulsion Analyst Intern Summer 2027</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -6129,13 +6129,13 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986816003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986820003</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Intern Summer 2027</t>
+          <t>Propulsion Design Intern Summer 2027</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -6167,13 +6167,13 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986792003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986816003</t>
         </is>
       </c>
     </row>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D Engineering Intern Summer 2027</t>
+          <t>Propulsion Intern Summer 2027</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -6205,13 +6205,13 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996576003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986792003</t>
         </is>
       </c>
     </row>
@@ -6223,12 +6223,12 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Security Analyst Intern Summer 2027</t>
+          <t>R&amp;D Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -6243,13 +6243,13 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996576003</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6261,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Security Analyst Intern Summer 2027</t>
+          <t>RF Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
@@ -6276,18 +6276,18 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
@@ -6319,13 +6319,13 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
@@ -6357,13 +6357,13 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
         </is>
       </c>
     </row>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Structural Analysis Intern Summer 2027</t>
+          <t>Security Analyst Intern Summer 2027</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
@@ -6395,13 +6395,13 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986690003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Intern Summer 2027</t>
+          <t>Security Analyst Intern Summer 2027</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
@@ -6433,13 +6433,13 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -6451,12 +6451,12 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Intern Summer 2027</t>
+          <t>Structural Analysis Intern Summer 2027</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
@@ -6471,13 +6471,13 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990063003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986690003</t>
         </is>
       </c>
     </row>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineering Intern Summer 2027</t>
+          <t>Supply Chain Intern Summer 2027</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
@@ -6509,13 +6509,13 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990063003</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineering Intern Summer 2027</t>
+          <t>Supply Chain Intern Summer 2027</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
@@ -6547,13 +6547,13 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Chantilly, VA</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
@@ -6623,13 +6623,13 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern Summer 2027</t>
+          <t>Systems Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Tucson, AZ</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
@@ -6661,13 +6661,13 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990319003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Test Engineering Intern - Avionics Summer 2027</t>
+          <t>Systems Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -6699,13 +6699,13 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987159003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -6717,12 +6717,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Test Engineering Intern Summer 2027</t>
+          <t>Talent Acquisition Intern Summer 2027</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
@@ -6737,13 +6737,13 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990319003</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Test Engineering Intern Summer 2027</t>
+          <t>Test Engineering Intern - Avionics Summer 2027</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Stennis Space Center, MS</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
@@ -6775,13 +6775,13 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987159003</t>
         </is>
       </c>
     </row>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Thermal Engineering Intern Summer 2027</t>
+          <t>Test Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Stennis Space Center, MS</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -6813,13 +6813,13 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8000958003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
         </is>
       </c>
     </row>
@@ -6831,12 +6831,12 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Turbomachinery Intern Summer 2027</t>
+          <t>Test Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
@@ -6851,30 +6851,30 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987208003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Shield AI</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Advanced Manufacturing Engineering Intern</t>
+          <t>Thermal Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Dallas, Texas</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
@@ -6889,30 +6889,30 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/c41c41a2-83d8-41a0-8a3b-ff8b84dc1c8a</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8000958003</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Shield AI</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Co-op (June 2027)</t>
+          <t>Turbomachinery Intern Summer 2027</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Dallas, Texas</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
@@ -6927,13 +6927,13 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/8c6cfcee-c6da-4a73-9bdf-3ef098ff59e6</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987208003</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Intern</t>
+          <t>Summer 2027 - Advanced Manufacturing Engineering Intern</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -6965,13 +6965,13 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/200a293f-71ce-4982-a100-ac4b500c4cf7</t>
+          <t>https://jobs.lever.co/shieldai/c41c41a2-83d8-41a0-8a3b-ff8b84dc1c8a</t>
         </is>
       </c>
     </row>
@@ -6983,12 +6983,12 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Intern</t>
+          <t>Summer 2027 - Electrical Engineering Co-op (June 2027)</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Seattle, Washington</t>
+          <t>Dallas, Texas</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
@@ -7003,13 +7003,13 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/da54c482-fe62-4f60-98b1-55ac0b82b3bc</t>
+          <t>https://jobs.lever.co/shieldai/8c6cfcee-c6da-4a73-9bdf-3ef098ff59e6</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Software Engineer Intern</t>
+          <t>Summer 2027 - Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>San Diego, California</t>
+          <t>Dallas, Texas</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
@@ -7041,30 +7041,30 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/8c850c75-081d-4d09-bebf-096379a93010</t>
+          <t>https://jobs.lever.co/shieldai/200a293f-71ce-4982-a100-ac4b500c4cf7</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Shield AI</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Business Operations Internship/Co-op</t>
+          <t>Summer 2027 - Mechanical Engineering Intern</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Flexible - Any SpaceX Site</t>
+          <t>Seattle, Washington</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
@@ -7079,30 +7079,30 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621771002?gh_jid=8621771002</t>
+          <t>https://jobs.lever.co/shieldai/da54c482-fe62-4f60-98b1-55ac0b82b3bc</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Shield AI</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Civil Engineering Internship</t>
+          <t>Summer 2027 - Software Engineer Intern</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Flexible - Any SpaceX Site</t>
+          <t>San Diego, California</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
@@ -7117,13 +7117,13 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8636144002?gh_jid=8636144002</t>
+          <t>https://jobs.lever.co/shieldai/8c850c75-081d-4d09-bebf-096379a93010</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Engineering Internship/Co-op</t>
+          <t>Summer 2027 Business Operations Internship/Co-op</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -7155,13 +7155,13 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621740002?gh_jid=8621740002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621771002?gh_jid=8621771002</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Graduate Engineer Internship/Co-op</t>
+          <t>Summer 2027 Civil Engineering Internship</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -7193,13 +7193,13 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621753002?gh_jid=8621753002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8636144002?gh_jid=8636144002</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Silicon Engineering Internship/Co-op</t>
+          <t>Summer 2027 Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -7231,13 +7231,13 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621763002?gh_jid=8621763002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621740002?gh_jid=8621740002</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Software Engineering Internship/Co-op</t>
+          <t>Summer 2027 Graduate Engineer Internship/Co-op</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -7269,30 +7269,30 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621757002?gh_jid=8621757002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621753002?gh_jid=8621753002</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Star Catcher</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Engineering Internship</t>
+          <t>Summer 2027 Silicon Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Jacksonville, Florida, United States</t>
+          <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
@@ -7307,30 +7307,30 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413079009</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621763002?gh_jid=8621763002</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Star Catcher</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Marketing &amp; Communications Internship</t>
+          <t>Summer 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Jacksonville, Florida, United States</t>
+          <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
@@ -7345,30 +7345,30 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413215009</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621757002?gh_jid=8621757002</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Stoke Space</t>
+          <t>Star Catcher</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Internship - Engineering</t>
+          <t>Summer 2027 Engineering Internship</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
+          <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
@@ -7383,30 +7383,30 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6175828004</t>
+          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413079009</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Stoke Space</t>
+          <t>Star Catcher</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Internship - Operations</t>
+          <t>Summer 2027 Marketing &amp; Communications Internship</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Kent, Washington</t>
+          <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
@@ -7421,13 +7421,13 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176785004</t>
+          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413215009</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Internship - Software</t>
+          <t>Summer 2027 Internship - Engineering</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Kent, Washington</t>
+          <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
@@ -7459,28 +7459,32 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176786004</t>
+          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6175828004</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>United Launch Alliance</t>
+          <t>Stoke Space</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Aerospace Engineering Internship Summer 2027</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr"/>
+          <t>Summer 2027 Internship - Operations</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Kent, Washington</t>
+        </is>
+      </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -7493,28 +7497,32 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Aerospace-Engineering-Internship-Summer-2027-CO-80112/1427399400/</t>
+          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176785004</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>United Launch Alliance</t>
+          <t>Stoke Space</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Avionics &amp; Electrical Engineering Internship Summer 2027</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr"/>
+          <t>Summer 2027 Internship - Software</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Kent, Washington</t>
+        </is>
+      </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -7527,13 +7535,13 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Avionics-&amp;-Electrical-Engineering-Internship-Summer-2027-CO-80112/1427399200/</t>
+          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176786004</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7553,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Civil Engineering Internship - Summer 2027</t>
+          <t>Aerospace Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
@@ -7561,13 +7569,13 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Civil%E2%80%AFEngineering-Internship-Summer-2027-FL-32925/1427396600/</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Aerospace-Engineering-Internship-Summer-2027-CO-80112/1427399400/</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7587,7 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Composite Engineering Internship - Summer 2027</t>
+          <t>Avionics &amp; Electrical Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr"/>
@@ -7595,13 +7603,13 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Composite-Engineering-Internship-Summer-2027-AL-35601/1427397600/</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Avionics-&amp;-Electrical-Engineering-Internship-Summer-2027-CO-80112/1427399200/</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7621,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Industrial Engineering Internship - Summer 2027</t>
+          <t>Civil Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
@@ -7629,13 +7637,13 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Industrial-Engineering-Internship-Summer-2027-FL-32925/1427396900/</t>
+          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Civil%E2%80%AFEngineering-Internship-Summer-2027-FL-32925/1427396600/</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7655,7 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Material Requirements Planning Specialist (MRP) Internship - Summer 2027</t>
+          <t>Composite Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
@@ -7663,13 +7671,13 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Material-Requirements-Planning-Specialist-%28MRP%29-Internship-Summer-2027-AL-35601/1427398800/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Composite-Engineering-Internship-Summer-2027-AL-35601/1427397600/</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7689,7 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Material and Process Engineering Internship Summer 2027</t>
+          <t>Industrial Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
@@ -7697,13 +7705,13 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Material-and-Process-Engineering-Internship-Summer-2027-CO-80112/1427398900/</t>
+          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Industrial-Engineering-Internship-Summer-2027-FL-32925/1427396900/</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7723,7 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Internship - Summer 2027</t>
+          <t>Material Requirements Planning Specialist (MRP) Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
@@ -7731,13 +7739,13 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Mechanical-Engineering-Internship-Summer-2027-FL-32925/1427396400/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Material-Requirements-Planning-Specialist-%28MRP%29-Internship-Summer-2027-AL-35601/1427398800/</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7757,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Quality Engineering Internship Summer 2027</t>
+          <t>Material and Process Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr"/>
@@ -7765,13 +7773,13 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Quality-Engineering-Internship-Summer-2027-AL-35601/1427398600/</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Material-and-Process-Engineering-Internship-Summer-2027-CO-80112/1427398900/</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7791,7 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Internship Summer 2027</t>
+          <t>Mechanical Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
@@ -7799,13 +7807,13 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Software-Engineering-Internship-Summer-2027-CO-80112/1427398300/</t>
+          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Mechanical-Engineering-Internship-Summer-2027-FL-32925/1427396400/</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7825,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Weld Engineering Internship - Summer 2027</t>
+          <t>Quality Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
@@ -7833,32 +7841,28 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Weld-Engineering-Internship-Summer-2027-AL-35601/1427397200/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Quality-Engineering-Internship-Summer-2027-AL-35601/1427398600/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>United Launch Alliance</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>El Segundo, California, United States</t>
-        </is>
-      </c>
+          <t>Software Engineering Internship Summer 2027</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr"/>
       <c r="D192" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -7866,37 +7870,33 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Software-Engineering-Internship-Summer-2027-CO-80112/1427398300/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>United Launch Alliance</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Avionics Engineering Internship - Summer 2027</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>El Segundo, California, United States</t>
-        </is>
-      </c>
+          <t>Weld Engineering Internship - Summer 2027</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr"/>
       <c r="D193" s="6" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -7904,18 +7904,18 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Weld-Engineering-Internship-Summer-2027-AL-35601/1427397200/</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Internship - Summer 2027</t>
+          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -7947,13 +7947,13 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Internship - Summer 2027</t>
+          <t>Avionics Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -7985,13 +7985,13 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Formulation Science Internship - Summer 2027</t>
+          <t>Cybersecurity Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -8023,13 +8023,13 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr"/>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
+          <t>Flight Software Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -8061,13 +8061,13 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Internship - Summer 2027</t>
+          <t>Formulation Science Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -8099,13 +8099,13 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
+          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -8137,13 +8137,13 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Mission Operations Internship - Summer 2027</t>
+          <t>Manufacturing Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -8175,13 +8175,13 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr"/>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineering Internship - Summer 2027</t>
+          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -8213,13 +8213,13 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Structures Engineering Internship - Summer 2027</t>
+          <t>Mission Operations Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -8251,13 +8251,13 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr"/>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Thermal Engineering Internship - Summer 2027</t>
+          <t>Propulsion Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -8289,13 +8289,13 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
+          <t>Structures Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -8327,106 +8327,106 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>BETA Technologies</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>BETA Internship</t>
+          <t>Thermal Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>South Burlington, Vermont, United States</t>
-        </is>
-      </c>
-      <c r="D205" s="7" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
+          <t>El Segundo, California, United States</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr"/>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/betatechnologiesinc/jobs/4218580009</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Environment, Health, and Safety (EHS)</t>
+          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>USA - Auburn, WA</t>
-        </is>
-      </c>
-      <c r="D206" s="7" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
+          <t>El Segundo, California, United States</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr"/>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Auburn-WA/Boeing-Summer-2027-Internship-Program--Paid----Environment--Health--and-Safety--EHS-_JR2026519561</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>BETA Technologies</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Intern to Entry Level Conversion – Business Functions (All) (Summer 2026 Intern Program)</t>
+          <t>BETA Internship</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
+          <t>South Burlington, Vermont, United States</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
@@ -8436,18 +8436,18 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr"/>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Intern-to-Entry-Level-Conversion---Business-Functions--All---Summer-2026-Intern-Program-_JR2026516335</t>
+          <t>https://job-boards.greenhouse.io/betatechnologiesinc/jobs/4218580009</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Intern to Intern Conversion - Engineering (Summer 2026 Intern Program)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
+          <t>USA - Arlington, VA</t>
         </is>
       </c>
       <c r="D208" s="7" t="inlineStr">
@@ -8474,35 +8474,35 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr"/>
       <c r="H208" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Intern-to-Intern-Conversion---Engineering--Summer-2026-Intern-Program-_JR2026516288</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Environment, Health, and Safety (EHS)</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>USA - Auburn, WA</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
@@ -8517,30 +8517,30 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr"/>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/18d2c72e-30cd-4145-8b12-7db3a492d541</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Auburn-WA/Boeing-Summer-2027-Internship-Program--Paid----Environment--Health--and-Safety--EHS-_JR2026519561</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>Intern to Entry Level Conversion – Business Functions (All) (Summer 2026 Intern Program)</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
+          <t>USA - Everett, WA</t>
         </is>
       </c>
       <c r="D210" s="7" t="inlineStr">
@@ -8550,33 +8550,37 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr"/>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e82f19e5-68f7-4d87-816f-cf405191952e</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Intern-to-Entry-Level-Conversion---Business-Functions--All---Summer-2026-Intern-Program-_JR2026516335</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Flight Operations Engineer Collegiate Associate Intern</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr"/>
+          <t>Intern to Intern Conversion - Engineering (Summer 2026 Intern Program)</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
@@ -8584,33 +8588,37 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr"/>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Operations-Engineer-Collegiate-Associate-Intern-GA-31401/1421926200/</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Intern-to-Intern-Conversion---Engineering--Summer-2026-Intern-Program-_JR2026516288</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Flight Sciences Engineer Collegiate Associate Intern</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr"/>
+          <t>Summer 2027 – Power Electronics Internship</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
@@ -8623,28 +8631,32 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr"/>
       <c r="H212" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Sciences-Engineer-Collegiate-Associate-Intern-GA-31401/1421898000/</t>
+          <t>https://jobs.lever.co/CesiumAstro/18d2c72e-30cd-4145-8b12-7db3a492d541</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Flight Test Engineer Collegiate Associate Intern</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr"/>
+          <t>Summer 2027 – Power Electronics Internship</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>Westminster, CO</t>
+        </is>
+      </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
@@ -8657,13 +8669,13 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr"/>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Test-Engineer-Collegiate-Associate-Intern-GA-31401/1421914300/</t>
+          <t>https://jobs.lever.co/CesiumAstro/e82f19e5-68f7-4d87-816f-cf405191952e</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8687,7 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Flight/System Simulation Engineer Collegiate Associate Intern</t>
+          <t>Summer 2027 - IEF - Flight Operations Engineer Collegiate Associate Intern</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
@@ -8697,7 +8709,7 @@
       <c r="G214" s="4" t="inlineStr"/>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-FlightSystem-Simulation-Engineer-Collegiate-Associate-Intern-GA-31401/1421866000/</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Operations-Engineer-Collegiate-Associate-Intern-GA-31401/1421926200/</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8721,7 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Powerplant/Propulsion Engineer Collegiate Associate Intern</t>
+          <t>Summer 2027 - IEF - Flight Sciences Engineer Collegiate Associate Intern</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr"/>
@@ -8725,32 +8737,28 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr"/>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-PowerplantPropulsion-Engineer-Collegiate-Associate-Intern-GA-31401/1421952200/</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Sciences-Engineer-Collegiate-Associate-Intern-GA-31401/1421898000/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern Summer 2027</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr">
-        <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
+          <t>Summer 2027 - IEF - Flight Test Engineer Collegiate Associate Intern</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr"/>
       <c r="D216" s="7" t="inlineStr">
         <is>
           <t>CLOSED</t>
@@ -8763,18 +8771,124 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr"/>
       <c r="H216" s="4" t="inlineStr">
         <is>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Test-Engineer-Collegiate-Associate-Intern-GA-31401/1421914300/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>Gulfstream Aerospace</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Summer 2027 - IEF - Flight/System Simulation Engineer Collegiate Associate Intern</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr"/>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G217" s="4" t="inlineStr"/>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-FlightSystem-Simulation-Engineer-Collegiate-Associate-Intern-GA-31401/1421866000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>Gulfstream Aerospace</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Summer 2027 - IEF - Powerplant/Propulsion Engineer Collegiate Associate Intern</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr"/>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr"/>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-PowerplantPropulsion-Engineer-Collegiate-Associate-Intern-GA-31401/1421952200/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>Rocket Lab</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>RF Engineering Intern Summer 2027</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr"/>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991657003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H216"/>
+  <autoFilter ref="A1:H219"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8785,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8843,17 +8957,17 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern Summer 2027</t>
+          <t>2027 Quality &amp; Test Engineer Intern</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -8863,23 +8977,99 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257674007?gh_jid=5257674007</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2027 Reliability Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257682007?gh_jid=5257682007</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2027 Systems Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257690007?gh_jid=5257690007</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8890,7 +9080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8948,17 +9138,17 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern Summer 2027</t>
+          <t>2027 Systems Engineer Intern</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -8968,111 +9158,111 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257690007?gh_jid=5257690007</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>2027 Reliability Engineer Intern</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257682007?gh_jid=5257682007</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
+          <t>2027 Quality &amp; Test Engineer Intern</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257674007?gh_jid=5257674007</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2027 Supply Chain Intern</t>
+          <t>RF Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -9082,35 +9272,35 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Government Operations Intern Summer 2027</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -9120,35 +9310,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
+          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Government Operations Intern Summer 2027</t>
+          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -9158,18 +9348,18 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9371,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2027 Industrial Engineer Intern</t>
+          <t>2027 Supply Chain Intern</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
+          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -9196,35 +9386,35 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
+          <t>Government Operations Intern Summer 2027</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, California, United States</t>
+          <t>Littleton, CO</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -9234,35 +9424,35 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Thermal Engineering Internship - Summer 2027</t>
+          <t>Government Operations Intern Summer 2027</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, California, United States</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -9272,35 +9462,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Structures Engineering Internship - Summer 2027</t>
+          <t>2027 Industrial Engineer Intern</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, California, United States</t>
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -9310,18 +9500,18 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9523,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineering Internship - Summer 2027</t>
+          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -9353,13 +9543,13 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9561,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mission Operations Internship - Summer 2027</t>
+          <t>Thermal Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -9391,13 +9581,13 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9599,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
+          <t>Structures Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -9429,13 +9619,13 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9637,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Internship - Summer 2027</t>
+          <t>Propulsion Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -9467,13 +9657,13 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9675,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
+          <t>Mission Operations Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -9505,13 +9695,13 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9713,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Formulation Science Internship - Summer 2027</t>
+          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -9543,13 +9733,13 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9751,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Internship - Summer 2027</t>
+          <t>Manufacturing Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -9581,13 +9771,13 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9789,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Internship - Summer 2027</t>
+          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -9619,13 +9809,13 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
         </is>
       </c>
     </row>
@@ -9637,7 +9827,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Avionics Engineering Internship - Summer 2027</t>
+          <t>Formulation Science Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -9657,13 +9847,13 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9865,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
+          <t>Flight Software Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -9695,30 +9885,30 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
+          <t>Cybersecurity Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>El Segundo, California, United States</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -9733,30 +9923,30 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Intern (Summer 2027)</t>
+          <t>Avionics Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>El Segundo, California, United States</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -9771,30 +9961,30 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Associate (Summer 2027)</t>
+          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>El Segundo, California, United States</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -9809,30 +9999,30 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
+          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -9847,30 +10037,30 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
+          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Internship - Summer 2027</t>
+          <t>RF Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -9880,35 +10070,35 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
+          <t>RF Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -9918,23 +10108,61 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Astranis</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H27"/>
+  <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9945,7 +10173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10008,7 +10236,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10028,13 +10256,13 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10274,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10066,30 +10294,30 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
+          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -10104,13 +10332,13 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
+          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10350,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
+          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10142,13 +10370,13 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
+          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
         </is>
       </c>
     </row>
@@ -10160,7 +10388,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
+          <t>Summer 2027 - Embedded Software Engineering Internship</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10180,13 +10408,13 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
+          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10426,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Embedded Software Engineering Internship</t>
+          <t>Summer 2027 - Finance Internship</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10218,13 +10446,13 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
+          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10464,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Finance Internship</t>
+          <t>Summer 2027 - Manufacturing Internship</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10256,13 +10484,13 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
+          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10502,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Manufacturing Internship</t>
+          <t>Summer 2027 - Mechanical Engineering Internship</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -10294,30 +10522,30 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
+          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>E-Space</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Internship</t>
+          <t>E-Space 2027 Summer Internship, Arlington TX</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -10332,30 +10560,30 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
+          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>E-Space</t>
+          <t>Shield AI</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>E-Space 2027 Summer Internship, Arlington TX</t>
+          <t>Summer 2027 - Advanced Manufacturing Engineering Intern</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Dallas, Texas</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -10370,13 +10598,13 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
+          <t>https://jobs.lever.co/shieldai/c41c41a2-83d8-41a0-8a3b-ff8b84dc1c8a</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10616,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Advanced Manufacturing Engineering Intern</t>
+          <t>Summer 2027 - Electrical Engineering Co-op (June 2027)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10408,13 +10636,13 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/c41c41a2-83d8-41a0-8a3b-ff8b84dc1c8a</t>
+          <t>https://jobs.lever.co/shieldai/8c6cfcee-c6da-4a73-9bdf-3ef098ff59e6</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10654,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Co-op (June 2027)</t>
+          <t>Summer 2027 - Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10446,56 +10674,18 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/8c6cfcee-c6da-4a73-9bdf-3ef098ff59e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Shield AI</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Summer 2027 - Electrical Engineering Intern</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Dallas, Texas</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
           <t>https://jobs.lever.co/shieldai/200a293f-71ce-4982-a100-ac4b500c4cf7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10633,11 +10823,11 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10667,7 +10857,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10697,7 +10887,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10723,11 +10913,11 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10757,7 +10947,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10787,7 +10977,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10817,7 +11007,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10847,7 +11037,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -10877,7 +11067,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10907,7 +11097,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10937,7 +11127,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10967,7 +11157,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10997,7 +11187,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -11027,7 +11217,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -11057,7 +11247,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -11087,7 +11277,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11117,7 +11307,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11147,7 +11337,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -11177,7 +11367,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11207,7 +11397,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11237,7 +11427,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -11267,7 +11457,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11297,7 +11487,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11327,7 +11517,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -11357,7 +11547,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11387,7 +11577,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -11417,7 +11607,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -11447,7 +11637,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -11477,7 +11667,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -11507,7 +11697,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11537,7 +11727,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11567,7 +11757,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11597,7 +11787,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11627,7 +11817,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -11657,7 +11847,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -11687,7 +11877,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -11717,7 +11907,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11747,7 +11937,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11777,7 +11967,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -11807,7 +11997,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -11837,7 +12027,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -11867,7 +12057,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -11897,7 +12087,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -11927,7 +12117,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -11957,7 +12147,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -11987,7 +12177,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -12017,7 +12207,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -12047,7 +12237,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -12077,7 +12267,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -12107,7 +12297,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -12137,7 +12327,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -12167,7 +12357,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -12197,7 +12387,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -12227,7 +12417,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -12257,7 +12447,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -12287,7 +12477,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -12317,7 +12507,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -12347,7 +12537,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -12377,7 +12567,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -12407,7 +12597,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -12437,7 +12627,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -12467,7 +12657,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -12497,7 +12687,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -12527,7 +12717,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -12557,7 +12747,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -12587,7 +12777,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -12617,7 +12807,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -12647,7 +12837,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -12677,7 +12867,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -12707,7 +12897,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -12737,7 +12927,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -12767,7 +12957,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -12797,7 +12987,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -12827,7 +13017,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -12857,7 +13047,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -12887,7 +13077,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -12917,7 +13107,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -12947,7 +13137,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -12977,7 +13167,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -13007,7 +13197,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -13037,7 +13227,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -13067,7 +13257,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -13097,7 +13287,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -13127,7 +13317,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -13157,7 +13347,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -13187,7 +13377,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -13217,7 +13407,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -13247,7 +13437,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -13277,7 +13467,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$219</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
@@ -65,11 +65,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
@@ -81,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -695,33 +695,33 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2027 Quality &amp; Test Engineer Intern</t>
+          <t>2027 Electrical Engineer Intern</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257674007?gh_jid=5257674007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2027 Reliability Engineer Intern</t>
+          <t>2027 Flight Software Engineer Intern</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -743,23 +743,23 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257682007?gh_jid=5257682007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
         </is>
       </c>
     </row>
@@ -771,33 +771,33 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2027 Systems Engineer Intern</t>
+          <t>2027 Industrial Engineer Intern</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257690007?gh_jid=5257690007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
         </is>
       </c>
     </row>
@@ -809,15 +809,15 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2027 Electrical Engineer Intern</t>
+          <t>2027 Manufacturing Engineer Intern</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -829,13 +829,13 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
         </is>
       </c>
     </row>
@@ -847,15 +847,15 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2027 Flight Software Engineer Intern</t>
+          <t>2027 Manufacturing Optimization Engineer Intern</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+          <t>Ashville, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -867,13 +867,13 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
         </is>
       </c>
     </row>
@@ -885,33 +885,33 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2027 Industrial Engineer Intern</t>
+          <t>2027 Mechanical Engineer Intern</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
         </is>
       </c>
     </row>
@@ -923,33 +923,33 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Engineer Intern</t>
+          <t>2027 Quality &amp; Test Engineer Intern</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257674007?gh_jid=5257674007</t>
         </is>
       </c>
     </row>
@@ -961,33 +961,33 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Optimization Engineer Intern</t>
+          <t>2027 Reliability Engineer Intern</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+          <t>Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257682007?gh_jid=5257682007</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2027 Mechanical Engineer Intern</t>
+          <t>2027 Software Engineer Intern</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1007,7 +1007,7 @@
           <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1019,13 +1019,13 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
         </is>
       </c>
     </row>
@@ -1037,33 +1037,33 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2027 Software Engineer Intern</t>
+          <t>2027 Supply Chain Intern</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
         </is>
       </c>
     </row>
@@ -1075,33 +1075,33 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2027 Supply Chain Intern</t>
+          <t>2027 Systems Engineer Intern</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+          <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257690007?gh_jid=5257690007</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
           <t>Ashville, Ohio, United States; Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -1159,7 +1159,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -1349,7 +1349,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -1501,7 +1501,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -1539,7 +1539,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
@@ -1577,7 +1577,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -1653,7 +1653,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1805,7 +1805,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
@@ -1881,7 +1881,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
@@ -1919,7 +1919,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
@@ -1957,7 +1957,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -2071,7 +2071,7 @@
           <t xml:space="preserve">San Francisco </t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
@@ -2147,7 +2147,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
@@ -2185,7 +2185,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
@@ -2261,7 +2261,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
@@ -2299,7 +2299,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
@@ -2375,7 +2375,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
@@ -2413,7 +2413,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
@@ -2489,7 +2489,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
@@ -2527,7 +2527,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
@@ -2565,7 +2565,7 @@
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
@@ -2641,7 +2641,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
@@ -2679,7 +2679,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
           <t>USA - Hazelwood, MO</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
@@ -2831,7 +2831,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
@@ -2869,7 +2869,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
@@ -2907,7 +2907,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
@@ -2945,7 +2945,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
@@ -3021,7 +3021,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
@@ -3059,7 +3059,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
@@ -3097,7 +3097,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
@@ -3135,7 +3135,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
@@ -3173,7 +3173,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -3287,7 +3287,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
@@ -3325,7 +3325,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -3363,7 +3363,7 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
@@ -3401,7 +3401,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
@@ -3439,7 +3439,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
@@ -3477,7 +3477,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
@@ -3515,7 +3515,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
@@ -3553,7 +3553,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
@@ -3591,7 +3591,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
@@ -3667,7 +3667,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
@@ -3705,7 +3705,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
@@ -3743,7 +3743,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
@@ -3781,7 +3781,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
@@ -3819,7 +3819,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
@@ -3857,7 +3857,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
@@ -3895,7 +3895,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
@@ -3933,7 +3933,7 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
@@ -4047,7 +4047,7 @@
           <t>Arlington, TX</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr"/>
@@ -4072,20 +4072,16 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Finance Intern – US – Summer 2027</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Evendale</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
+          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr"/>
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4097,13 +4093,13 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
+          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
         </is>
       </c>
     </row>
@@ -4115,11 +4111,11 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
+          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4137,23 +4133,27 @@
       <c r="G92" s="4" t="inlineStr"/>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr"/>
-      <c r="D93" s="6" t="inlineStr">
+          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4165,13 +4165,13 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
+          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
+          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4191,7 +4191,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4203,13 +4203,13 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
+          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
         </is>
       </c>
     </row>
@@ -4221,33 +4221,33 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
+          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
+          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
         </is>
       </c>
     </row>
@@ -4259,33 +4259,33 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
+          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
+          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
         </is>
       </c>
     </row>
@@ -4297,33 +4297,33 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
+          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
+          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
         </is>
       </c>
     </row>
@@ -4335,33 +4335,33 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
+          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
+          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
         </is>
       </c>
     </row>
@@ -4373,15 +4373,15 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
+          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4393,13 +4393,13 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
+          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
         </is>
       </c>
     </row>
@@ -4411,15 +4411,15 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
+          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4431,13 +4431,13 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
+          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -4457,7 +4457,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4469,13 +4469,13 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
+          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -4495,7 +4495,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4507,13 +4507,13 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
+          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
         </is>
       </c>
     </row>
@@ -4525,15 +4525,15 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4545,13 +4545,13 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
+          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
         </is>
       </c>
     </row>
@@ -4563,15 +4563,15 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
+          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4583,13 +4583,13 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
+          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
+          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4609,7 +4609,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4621,13 +4621,13 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
+          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
+          <t>Supply Chain Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -4647,7 +4647,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4659,13 +4659,13 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
+          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
         </is>
       </c>
     </row>
@@ -4677,15 +4677,15 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Intern - Spring/Summer 2027</t>
+          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4697,25 +4697,25 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
+          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
+          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -4723,7 +4723,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4735,13 +4735,13 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
+          <t>Dynamics Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -4761,7 +4761,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4773,13 +4773,13 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Dynamics Engineering Intern – Summer 2027</t>
+          <t>Electrical Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -4799,7 +4799,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4811,13 +4811,13 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern – Summer 2027</t>
+          <t>GNC Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -4837,7 +4837,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4849,13 +4849,13 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>GNC Engineering Intern – Summer 2027</t>
+          <t>Mechanical  Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -4875,7 +4875,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4887,13 +4887,13 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Mechanical  Engineering Intern – Summer 2027</t>
+          <t>RF Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -4913,7 +4913,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4925,13 +4925,13 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411919008</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern – Summer 2027</t>
+          <t>Simulation Software Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -4951,7 +4951,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4963,13 +4963,13 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411919008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5418727008</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Simulation Software Engineering Intern - Summer 2027</t>
+          <t>Software Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -4989,7 +4989,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5001,13 +5001,13 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5418727008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411920008</t>
         </is>
       </c>
     </row>
@@ -5019,33 +5019,33 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Summer 2027</t>
+          <t>Supply Chain Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411920008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
         </is>
       </c>
     </row>
@@ -5057,53 +5057,49 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Internship - Summer 2027</t>
+          <t>Vehicle Operations Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5436468008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411914008</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>MIT Lincoln Laboratory</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Vehicle Operations Engineering Intern – Summer 2027</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
+          <t>Airborne Radar Systems and Techniques Intern (Summer 2027) - Group 105</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr"/>
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5115,13 +5111,13 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411914008</t>
+          <t>https://careers.ll.mit.edu/job/Lexington-Airborne-Radar-Systems-and-Techniques-Intern-%28Summer-2027%29-Group-105-MA-02420/1410581200/</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5129,11 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Airborne Radar Systems and Techniques Intern (Summer 2027) - Group 105</t>
+          <t>Optical Engineering Intern - Optical Engineer (Summer 2027) - Group 78</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5149,13 +5145,13 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>https://careers.ll.mit.edu/job/Lexington-Airborne-Radar-Systems-and-Techniques-Intern-%28Summer-2027%29-Group-105-MA-02420/1410581200/</t>
+          <t>https://careers.ll.mit.edu/job/Lexington-Optical-Engineering-Intern-Optical-Engineer-%28Summer-2027%29-Group-78-MA-02420/1433573800/</t>
         </is>
       </c>
     </row>
@@ -5167,11 +5163,11 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Optical Engineering Intern - Optical Engineer (Summer 2027) - Group 78</t>
+          <t>Software and Electronics Engineering Intern (Summer 2027) - Group 76</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5183,29 +5179,33 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>https://careers.ll.mit.edu/job/Lexington-Optical-Engineering-Intern-Optical-Engineer-%28Summer-2027%29-Group-78-MA-02420/1433573800/</t>
+          <t>https://careers.ll.mit.edu/job/Lexington-Software-and-Electronics-Engineering-Intern-%28Summer-2027%29-Group-76-MA-02420/1431440000/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>MIT Lincoln Laboratory</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Software and Electronics Engineering Intern (Summer 2027) - Group 76</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr"/>
-      <c r="D121" s="6" t="inlineStr">
+          <t>Additive Manufacturing Intern Summer 2027</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5217,13 +5217,13 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>https://careers.ll.mit.edu/job/Lexington-Software-and-Electronics-Engineering-Intern-%28Summer-2027%29-Group-76-MA-02420/1431440000/</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984600003</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Additive Manufacturing Intern Summer 2027</t>
+          <t>Avionics Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -5243,7 +5243,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5255,13 +5255,13 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984600003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989733003</t>
         </is>
       </c>
     </row>
@@ -5273,15 +5273,15 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Avionics Engineering Intern Summer 2027</t>
+          <t>Business Development Intern Summer 2027</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
+          <t>Toronto, CAN</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5293,13 +5293,13 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989733003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7993738003</t>
         </is>
       </c>
     </row>
@@ -5311,15 +5311,15 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Business Development Intern Summer 2027</t>
+          <t>Combustion Devices Intern Summer 2027</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5331,13 +5331,13 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7993738003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986748003</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Combustion Devices Intern Summer 2027</t>
+          <t>Electrical Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -5357,7 +5357,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5369,13 +5369,13 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986748003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
           <t>Toronto, CAN</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
+          <t>Pasadena, CA</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5445,13 +5445,13 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
         </is>
       </c>
     </row>
@@ -5463,15 +5463,15 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern Summer 2027</t>
+          <t>Flight Software Intern Summer 2027</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
+          <t>Littleton, CO</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5483,13 +5483,13 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989722003</t>
         </is>
       </c>
     </row>
@@ -5501,15 +5501,15 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Intern Summer 2027</t>
+          <t>Fluid Component Intern Summer 2027</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5521,13 +5521,13 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989722003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990365003</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Fluid Component Intern Summer 2027</t>
+          <t>Fluid Systems Intern Summer 2027</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -5547,7 +5547,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5559,13 +5559,13 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990365003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986794003</t>
         </is>
       </c>
     </row>
@@ -5577,33 +5577,33 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Fluid Systems Intern Summer 2027</t>
+          <t>Government Operations Intern Summer 2027</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986794003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
           <t>Littleton, CO</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
@@ -5653,33 +5653,33 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Government Operations Intern Summer 2027</t>
+          <t>HITL Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990268003</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>HITL Engineering Intern Summer 2027</t>
+          <t>Indirect Procurement Intern Summer 2027</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -5699,7 +5699,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5711,13 +5711,13 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990268003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989063003</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Indirect Procurement Intern Summer 2027</t>
+          <t>Integration &amp; Test Intern Summer 2027</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -5737,7 +5737,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5749,13 +5749,13 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989063003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987250003</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Test Intern Summer 2027</t>
+          <t>Manufacturing Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -5775,7 +5775,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5787,13 +5787,13 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987250003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984564003</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
@@ -5848,10 +5848,10 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5863,13 +5863,13 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984564003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
         </is>
       </c>
     </row>
@@ -5881,15 +5881,15 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Intern Summer 2027</t>
+          <t>Mechanical Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
+          <t>Toronto, CAN</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5901,13 +5901,13 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
         </is>
       </c>
     </row>
@@ -5924,10 +5924,10 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
+          <t>Silver Spring, MD</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5939,13 +5939,13 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -5962,10 +5962,10 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5977,13 +5977,13 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -5995,15 +5995,15 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern Summer 2027</t>
+          <t>Optical Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
+          <t>Tucson, AZ</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6015,13 +6015,13 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992102003</t>
         </is>
       </c>
     </row>
@@ -6033,15 +6033,15 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Optical Engineering Intern Summer 2027</t>
+          <t>People &amp; Culture Intern Summer 2027</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6053,13 +6053,13 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992102003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990245003</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>People &amp; Culture Intern Summer 2027</t>
+          <t>Propulsion Analyst Intern Summer 2027</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -6079,7 +6079,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6091,13 +6091,13 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990245003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986820003</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Analyst Intern Summer 2027</t>
+          <t>Propulsion Design Intern Summer 2027</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -6117,7 +6117,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6129,13 +6129,13 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986820003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986816003</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Design Intern Summer 2027</t>
+          <t>Propulsion Intern Summer 2027</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -6155,7 +6155,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6167,13 +6167,13 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986816003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986792003</t>
         </is>
       </c>
     </row>
@@ -6185,15 +6185,15 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Intern Summer 2027</t>
+          <t>R&amp;D Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
+          <t>Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6205,13 +6205,13 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986792003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996576003</t>
         </is>
       </c>
     </row>
@@ -6223,33 +6223,33 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D Engineering Intern Summer 2027</t>
+          <t>RF Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996576003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
         </is>
       </c>
     </row>
@@ -6261,33 +6261,33 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern Summer 2027</t>
+          <t>Security Analyst Intern Summer 2027</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
           <t>Albuquerque, NM</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
@@ -6342,10 +6342,10 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
+          <t>Middle River, MD</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6357,13 +6357,13 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
         </is>
       </c>
     </row>
@@ -6380,10 +6380,10 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6395,13 +6395,13 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
         </is>
       </c>
     </row>
@@ -6413,15 +6413,15 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Security Analyst Intern Summer 2027</t>
+          <t>Structural Analysis Intern Summer 2027</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6433,13 +6433,13 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986690003</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Structural Analysis Intern Summer 2027</t>
+          <t>Supply Chain Intern Summer 2027</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -6459,7 +6459,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="D154" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6471,13 +6471,13 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986690003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
@@ -6527,15 +6527,15 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Intern Summer 2027</t>
+          <t>Systems Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
+          <t>Tucson, AZ</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6547,13 +6547,13 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
           <t>Pasadena, CA</t>
         </is>
       </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
@@ -6611,7 +6611,7 @@
           <t>Chantilly, VA</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="D158" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6661,13 +6661,13 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineering Intern Summer 2027</t>
+          <t>Talent Acquisition Intern Summer 2027</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -6687,7 +6687,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D160" s="6" t="inlineStr">
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6699,13 +6699,13 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990319003</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern Summer 2027</t>
+          <t>Test Engineering Intern - Avionics Summer 2027</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -6725,7 +6725,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6737,13 +6737,13 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990319003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987159003</t>
         </is>
       </c>
     </row>
@@ -6755,15 +6755,15 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Test Engineering Intern - Avionics Summer 2027</t>
+          <t>Test Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6775,13 +6775,13 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987159003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
           <t>Stennis Space Center, MS</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
@@ -6831,15 +6831,15 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Test Engineering Intern Summer 2027</t>
+          <t>Thermal Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6851,13 +6851,13 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8000958003</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Thermal Engineering Intern Summer 2027</t>
+          <t>Turbomachinery Intern Summer 2027</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -6877,7 +6877,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D165" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6889,33 +6889,33 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8000958003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987208003</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Shield AI</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Turbomachinery Intern Summer 2027</t>
+          <t>Summer 2027 - Advanced Manufacturing Engineering Intern</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr">
+          <t>Dallas, Texas</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6927,13 +6927,13 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987208003</t>
+          <t>https://jobs.lever.co/shieldai/c41c41a2-83d8-41a0-8a3b-ff8b84dc1c8a</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Advanced Manufacturing Engineering Intern</t>
+          <t>Summer 2027 - Electrical Engineering Co-op (June 2027)</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -6953,7 +6953,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D167" s="6" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6965,13 +6965,13 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/c41c41a2-83d8-41a0-8a3b-ff8b84dc1c8a</t>
+          <t>https://jobs.lever.co/shieldai/8c6cfcee-c6da-4a73-9bdf-3ef098ff59e6</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Co-op (June 2027)</t>
+          <t>Summer 2027 - Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -6991,7 +6991,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7003,13 +7003,13 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/8c6cfcee-c6da-4a73-9bdf-3ef098ff59e6</t>
+          <t>https://jobs.lever.co/shieldai/200a293f-71ce-4982-a100-ac4b500c4cf7</t>
         </is>
       </c>
     </row>
@@ -7021,15 +7021,15 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Intern</t>
+          <t>Summer 2027 - Mechanical Engineering Intern</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Dallas, Texas</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="inlineStr">
+          <t>Seattle, Washington</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7041,13 +7041,13 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/200a293f-71ce-4982-a100-ac4b500c4cf7</t>
+          <t>https://jobs.lever.co/shieldai/da54c482-fe62-4f60-98b1-55ac0b82b3bc</t>
         </is>
       </c>
     </row>
@@ -7059,15 +7059,15 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Intern</t>
+          <t>Summer 2027 - Software Engineer Intern</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Seattle, Washington</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
+          <t>San Diego, California</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7079,33 +7079,33 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/da54c482-fe62-4f60-98b1-55ac0b82b3bc</t>
+          <t>https://jobs.lever.co/shieldai/8c850c75-081d-4d09-bebf-096379a93010</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Shield AI</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Software Engineer Intern</t>
+          <t>Summer 2027 Business Operations Internship/Co-op</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>San Diego, California</t>
-        </is>
-      </c>
-      <c r="D171" s="6" t="inlineStr">
+          <t>Flexible - Any SpaceX Site</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7117,13 +7117,13 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/8c850c75-081d-4d09-bebf-096379a93010</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621771002?gh_jid=8621771002</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Business Operations Internship/Co-op</t>
+          <t>Summer 2027 Civil Engineering Internship</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -7143,7 +7143,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7155,13 +7155,13 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621771002?gh_jid=8621771002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8636144002?gh_jid=8636144002</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Civil Engineering Internship</t>
+          <t>Summer 2027 Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -7181,7 +7181,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D173" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7193,13 +7193,13 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8636144002?gh_jid=8636144002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621740002?gh_jid=8621740002</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Engineering Internship/Co-op</t>
+          <t>Summer 2027 Graduate Engineer Internship/Co-op</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -7219,7 +7219,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7231,13 +7231,13 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621740002?gh_jid=8621740002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621753002?gh_jid=8621753002</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Graduate Engineer Internship/Co-op</t>
+          <t>Summer 2027 Silicon Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -7257,7 +7257,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D175" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7269,13 +7269,13 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621753002?gh_jid=8621753002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621763002?gh_jid=8621763002</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Silicon Engineering Internship/Co-op</t>
+          <t>Summer 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -7295,7 +7295,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D176" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7307,33 +7307,33 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621763002?gh_jid=8621763002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621757002?gh_jid=8621757002</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Star Catcher</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Software Engineering Internship/Co-op</t>
+          <t>Summer 2027 Engineering Internship</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Flexible - Any SpaceX Site</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr">
+          <t>Jacksonville, Florida, United States</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7345,13 +7345,13 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621757002?gh_jid=8621757002</t>
+          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413079009</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Engineering Internship</t>
+          <t>Summer 2027 Marketing &amp; Communications Internship</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -7371,7 +7371,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7383,33 +7383,33 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413079009</t>
+          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413215009</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Star Catcher</t>
+          <t>Stoke Space</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Marketing &amp; Communications Internship</t>
+          <t>Summer 2027 Internship - Engineering</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Jacksonville, Florida, United States</t>
-        </is>
-      </c>
-      <c r="D179" s="6" t="inlineStr">
+          <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7421,13 +7421,13 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413215009</t>
+          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6175828004</t>
         </is>
       </c>
     </row>
@@ -7439,15 +7439,15 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Internship - Engineering</t>
+          <t>Summer 2027 Internship - Operations</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
+          <t>Kent, Washington</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7459,13 +7459,13 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6175828004</t>
+          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176785004</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Internship - Operations</t>
+          <t>Summer 2027 Internship - Software</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -7485,7 +7485,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7497,33 +7497,29 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176785004</t>
+          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176786004</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Stoke Space</t>
+          <t>United Launch Alliance</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Internship - Software</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>Kent, Washington</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
+          <t>Aerospace Engineering Internship Summer 2027</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr"/>
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7535,13 +7531,13 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176786004</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Aerospace-Engineering-Internship-Summer-2027-CO-80112/1427399400/</t>
         </is>
       </c>
     </row>
@@ -7553,11 +7549,11 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Aerospace Engineering Internship Summer 2027</t>
+          <t>Avionics &amp; Electrical Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7569,13 +7565,13 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Aerospace-Engineering-Internship-Summer-2027-CO-80112/1427399400/</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Avionics-&amp;-Electrical-Engineering-Internship-Summer-2027-CO-80112/1427399200/</t>
         </is>
       </c>
     </row>
@@ -7587,11 +7583,11 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Avionics &amp; Electrical Engineering Internship Summer 2027</t>
+          <t>Civil Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr"/>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7603,13 +7599,13 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Avionics-&amp;-Electrical-Engineering-Internship-Summer-2027-CO-80112/1427399200/</t>
+          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Civil%E2%80%AFEngineering-Internship-Summer-2027-FL-32925/1427396600/</t>
         </is>
       </c>
     </row>
@@ -7621,11 +7617,11 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Civil Engineering Internship - Summer 2027</t>
+          <t>Composite Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7637,13 +7633,13 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Civil%E2%80%AFEngineering-Internship-Summer-2027-FL-32925/1427396600/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Composite-Engineering-Internship-Summer-2027-AL-35601/1427397600/</t>
         </is>
       </c>
     </row>
@@ -7655,11 +7651,11 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Composite Engineering Internship - Summer 2027</t>
+          <t>Industrial Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7671,13 +7667,13 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Composite-Engineering-Internship-Summer-2027-AL-35601/1427397600/</t>
+          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Industrial-Engineering-Internship-Summer-2027-FL-32925/1427396900/</t>
         </is>
       </c>
     </row>
@@ -7689,11 +7685,11 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Industrial Engineering Internship - Summer 2027</t>
+          <t>Material Requirements Planning Specialist (MRP) Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7705,13 +7701,13 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Industrial-Engineering-Internship-Summer-2027-FL-32925/1427396900/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Material-Requirements-Planning-Specialist-%28MRP%29-Internship-Summer-2027-AL-35601/1427398800/</t>
         </is>
       </c>
     </row>
@@ -7723,11 +7719,11 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Material Requirements Planning Specialist (MRP) Internship - Summer 2027</t>
+          <t>Material and Process Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7739,13 +7735,13 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Material-Requirements-Planning-Specialist-%28MRP%29-Internship-Summer-2027-AL-35601/1427398800/</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Material-and-Process-Engineering-Internship-Summer-2027-CO-80112/1427398900/</t>
         </is>
       </c>
     </row>
@@ -7757,11 +7753,11 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Material and Process Engineering Internship Summer 2027</t>
+          <t>Mechanical Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr"/>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7773,13 +7769,13 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Material-and-Process-Engineering-Internship-Summer-2027-CO-80112/1427398900/</t>
+          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Mechanical-Engineering-Internship-Summer-2027-FL-32925/1427396400/</t>
         </is>
       </c>
     </row>
@@ -7791,11 +7787,11 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Internship - Summer 2027</t>
+          <t>Quality Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7807,13 +7803,13 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Mechanical-Engineering-Internship-Summer-2027-FL-32925/1427396400/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Quality-Engineering-Internship-Summer-2027-AL-35601/1427398600/</t>
         </is>
       </c>
     </row>
@@ -7825,11 +7821,11 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Quality Engineering Internship Summer 2027</t>
+          <t>Software Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="D191" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7841,13 +7837,13 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Quality-Engineering-Internship-Summer-2027-AL-35601/1427398600/</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Software-Engineering-Internship-Summer-2027-CO-80112/1427398300/</t>
         </is>
       </c>
     </row>
@@ -7859,11 +7855,11 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Internship Summer 2027</t>
+          <t>Weld Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
-      <c r="D192" s="6" t="inlineStr">
+      <c r="D192" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7875,47 +7871,51 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Software-Engineering-Internship-Summer-2027-CO-80112/1427398300/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Weld-Engineering-Internship-Summer-2027-AL-35601/1427397200/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>United Launch Alliance</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Weld Engineering Internship - Summer 2027</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr"/>
-      <c r="D193" s="6" t="inlineStr">
+          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>El Segundo, California, United States</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Weld-Engineering-Internship-Summer-2027-AL-35601/1427397200/</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
+          <t>Avionics Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -7935,7 +7935,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D194" s="6" t="inlineStr">
+      <c r="D194" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7947,13 +7947,13 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Avionics Engineering Internship - Summer 2027</t>
+          <t>Cybersecurity Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -7973,7 +7973,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D195" s="6" t="inlineStr">
+      <c r="D195" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7985,13 +7985,13 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Internship - Summer 2027</t>
+          <t>Flight Software Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -8011,7 +8011,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D196" s="6" t="inlineStr">
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8023,13 +8023,13 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr"/>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Internship - Summer 2027</t>
+          <t>Formulation Science Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -8049,7 +8049,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D197" s="6" t="inlineStr">
+      <c r="D197" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8061,13 +8061,13 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Formulation Science Internship - Summer 2027</t>
+          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -8087,7 +8087,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D198" s="6" t="inlineStr">
+      <c r="D198" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8099,13 +8099,13 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
+          <t>Manufacturing Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -8125,7 +8125,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D199" s="6" t="inlineStr">
+      <c r="D199" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8137,13 +8137,13 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Internship - Summer 2027</t>
+          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -8163,7 +8163,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D200" s="6" t="inlineStr">
+      <c r="D200" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8175,13 +8175,13 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr"/>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
+          <t>Mission Operations Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -8201,7 +8201,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D201" s="6" t="inlineStr">
+      <c r="D201" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8213,13 +8213,13 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Mission Operations Internship - Summer 2027</t>
+          <t>Propulsion Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -8239,7 +8239,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D202" s="6" t="inlineStr">
+      <c r="D202" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8251,13 +8251,13 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr"/>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineering Internship - Summer 2027</t>
+          <t>Structures Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -8277,7 +8277,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D203" s="6" t="inlineStr">
+      <c r="D203" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8289,13 +8289,13 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Structures Engineering Internship - Summer 2027</t>
+          <t>Thermal Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -8315,7 +8315,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D204" s="6" t="inlineStr">
+      <c r="D204" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8327,13 +8327,13 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Thermal Engineering Internship - Summer 2027</t>
+          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -8353,7 +8353,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D205" s="6" t="inlineStr">
+      <c r="D205" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8365,71 +8365,71 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr"/>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>BETA Technologies</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
+          <t>BETA Internship</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, California, United States</t>
+          <t>South Burlington, Vermont, United States</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr"/>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
+          <t>https://job-boards.greenhouse.io/betatechnologiesinc/jobs/4218580009</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>BETA Technologies</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>BETA Internship</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>South Burlington, Vermont, United States</t>
-        </is>
-      </c>
-      <c r="D207" s="7" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8441,13 +8441,13 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr"/>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/betatechnologiesinc/jobs/4218580009</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
         </is>
       </c>
     </row>
@@ -8459,15 +8459,15 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Environment, Health, and Safety (EHS)</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D208" s="7" t="inlineStr">
+          <t>USA - Auburn, WA</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8479,13 +8479,13 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr"/>
       <c r="H208" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Auburn-WA/Boeing-Summer-2027-Internship-Program--Paid----Environment--Health--and-Safety--EHS-_JR2026519561</t>
         </is>
       </c>
     </row>
@@ -8497,22 +8497,22 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Environment, Health, and Safety (EHS)</t>
+          <t>Intern to Entry Level Conversion – Business Functions (All) (Summer 2026 Intern Program)</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>USA - Auburn, WA</t>
-        </is>
-      </c>
-      <c r="D209" s="7" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -8523,7 +8523,7 @@
       <c r="G209" s="4" t="inlineStr"/>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Auburn-WA/Boeing-Summer-2027-Internship-Program--Paid----Environment--Health--and-Safety--EHS-_JR2026519561</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Intern-to-Entry-Level-Conversion---Business-Functions--All---Summer-2026-Intern-Program-_JR2026516335</t>
         </is>
       </c>
     </row>
@@ -8535,71 +8535,71 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Intern to Entry Level Conversion – Business Functions (All) (Summer 2026 Intern Program)</t>
+          <t>Intern to Intern Conversion - Engineering (Summer 2026 Intern Program)</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D210" s="7" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr"/>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Intern-to-Entry-Level-Conversion---Business-Functions--All---Summer-2026-Intern-Program-_JR2026516335</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Intern-to-Intern-Conversion---Engineering--Summer-2026-Intern-Program-_JR2026516288</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Intern to Intern Conversion - Engineering (Summer 2026 Intern Program)</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D211" s="7" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr"/>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Intern-to-Intern-Conversion---Engineering--Summer-2026-Intern-Program-_JR2026516288</t>
+          <t>https://jobs.lever.co/CesiumAstro/18d2c72e-30cd-4145-8b12-7db3a492d541</t>
         </is>
       </c>
     </row>
@@ -8616,10 +8616,10 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D212" s="7" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8637,27 +8637,27 @@
       <c r="G212" s="4" t="inlineStr"/>
       <c r="H212" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/18d2c72e-30cd-4145-8b12-7db3a492d541</t>
+          <t>https://jobs.lever.co/CesiumAstro/e82f19e5-68f7-4d87-816f-cf405191952e</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>Finance Intern – US – Summer 2027</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D213" s="7" t="inlineStr">
+          <t>Evendale</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8669,13 +8669,13 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr"/>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e82f19e5-68f7-4d87-816f-cf405191952e</t>
+          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8691,7 @@
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
-      <c r="D214" s="7" t="inlineStr">
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr"/>
-      <c r="D215" s="7" t="inlineStr">
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr"/>
-      <c r="D216" s="7" t="inlineStr">
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr"/>
-      <c r="D217" s="7" t="inlineStr">
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr"/>
-      <c r="D218" s="7" t="inlineStr">
+      <c r="D218" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8865,7 +8865,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D219" s="7" t="inlineStr">
+      <c r="D219" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8954,122 +8954,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2027 Quality &amp; Test Engineer Intern</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257674007?gh_jid=5257674007</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2027 Reliability Engineer Intern</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257682007?gh_jid=5257682007</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2027 Systems Engineer Intern</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257690007?gh_jid=5257690007</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9153,7 +9039,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -9163,7 +9049,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9191,7 +9077,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -9201,7 +9087,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9229,7 +9115,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -9239,7 +9125,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9265,7 +9151,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9277,7 +9163,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9303,7 +9189,7 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9315,7 +9201,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9341,7 +9227,7 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9353,7 +9239,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9379,7 +9265,7 @@
           <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9391,7 +9277,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -9414,10 +9300,10 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9429,13 +9315,13 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
@@ -9452,10 +9338,10 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+          <t>Littleton, CO</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9467,13 +9353,13 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9379,7 @@
           <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9505,7 +9391,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -9531,7 +9417,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9543,7 +9429,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -9569,7 +9455,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9581,7 +9467,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -9607,7 +9493,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9619,7 +9505,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -9645,7 +9531,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9657,7 +9543,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -9683,7 +9569,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9695,7 +9581,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -9721,7 +9607,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9733,7 +9619,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -9759,7 +9645,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9771,7 +9657,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -9797,7 +9683,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9809,7 +9695,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -9835,7 +9721,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9847,7 +9733,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -9873,7 +9759,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9885,7 +9771,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -9911,7 +9797,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9923,7 +9809,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -9949,7 +9835,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9961,7 +9847,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -9987,7 +9873,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9999,7 +9885,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
@@ -10025,7 +9911,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10037,7 +9923,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -10063,7 +9949,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10075,7 +9961,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -10101,7 +9987,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10113,7 +9999,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -10139,7 +10025,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10151,7 +10037,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
@@ -10244,7 +10130,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10256,7 +10142,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -10282,7 +10168,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10294,7 +10180,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -10320,7 +10206,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10332,7 +10218,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -10358,7 +10244,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10370,7 +10256,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -10396,7 +10282,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10408,7 +10294,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -10434,7 +10320,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10446,7 +10332,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -10472,7 +10358,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10484,7 +10370,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -10510,7 +10396,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10522,7 +10408,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -10548,7 +10434,7 @@
           <t>Arlington, TX</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10560,7 +10446,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -10586,7 +10472,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10598,7 +10484,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -10624,7 +10510,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10636,7 +10522,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -10662,7 +10548,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10674,7 +10560,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -10817,7 +10703,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10827,7 +10713,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10847,7 +10733,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10857,7 +10743,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10877,7 +10763,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10887,7 +10773,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10907,7 +10793,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10917,7 +10803,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10937,7 +10823,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10947,7 +10833,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10967,7 +10853,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10977,7 +10863,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10997,17 +10883,17 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -11027,7 +10913,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11037,7 +10923,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11057,7 +10943,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11067,7 +10953,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -11087,7 +10973,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11097,7 +10983,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11117,7 +11003,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11127,7 +11013,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -11147,7 +11033,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11157,7 +11043,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -11177,7 +11063,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11187,7 +11073,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -11207,7 +11093,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11217,7 +11103,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -11237,7 +11123,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11247,7 +11133,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -11267,7 +11153,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11277,7 +11163,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11297,7 +11183,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11307,7 +11193,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11327,7 +11213,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11337,7 +11223,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -11357,7 +11243,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11367,7 +11253,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11387,7 +11273,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11397,7 +11283,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11417,7 +11303,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11427,7 +11313,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -11447,7 +11333,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11457,7 +11343,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11477,7 +11363,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11487,7 +11373,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11507,7 +11393,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11517,7 +11403,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -11537,7 +11423,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11547,7 +11433,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11567,7 +11453,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11577,7 +11463,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -11597,7 +11483,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11607,7 +11493,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -11627,7 +11513,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11637,7 +11523,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -11657,7 +11543,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11667,7 +11553,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -11687,7 +11573,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11697,7 +11583,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11717,7 +11603,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11727,7 +11613,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11747,7 +11633,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11757,7 +11643,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11777,7 +11663,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11787,7 +11673,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11807,7 +11693,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11817,7 +11703,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -11837,7 +11723,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11847,7 +11733,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -11867,7 +11753,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11877,7 +11763,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -11897,7 +11783,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11907,7 +11793,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11927,7 +11813,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11937,7 +11823,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11957,7 +11843,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11967,7 +11853,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -11987,7 +11873,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11997,7 +11883,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -12017,7 +11903,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -12027,7 +11913,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -12047,7 +11933,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12057,7 +11943,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -12077,7 +11963,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12087,7 +11973,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -12107,7 +11993,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12117,7 +12003,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -12137,7 +12023,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12147,7 +12033,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -12167,7 +12053,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12177,7 +12063,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -12197,7 +12083,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12207,7 +12093,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -12227,7 +12113,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12237,7 +12123,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -12257,7 +12143,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12267,7 +12153,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -12287,7 +12173,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12297,7 +12183,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -12317,7 +12203,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12327,7 +12213,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -12347,7 +12233,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12357,7 +12243,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -12377,7 +12263,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12387,7 +12273,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -12407,7 +12293,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12417,7 +12303,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -12437,7 +12323,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12447,7 +12333,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -12467,7 +12353,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12477,7 +12363,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -12497,7 +12383,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12507,7 +12393,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -12527,7 +12413,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12537,7 +12423,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -12557,7 +12443,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12567,7 +12453,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -12587,7 +12473,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12597,7 +12483,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -12617,7 +12503,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12627,7 +12513,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -12647,7 +12533,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12657,7 +12543,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -12677,7 +12563,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12687,7 +12573,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -12707,7 +12593,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12717,7 +12603,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -12737,7 +12623,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12747,7 +12633,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -12767,7 +12653,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12777,7 +12663,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -12797,7 +12683,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12807,7 +12693,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -12827,7 +12713,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12837,7 +12723,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -12857,7 +12743,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12867,7 +12753,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -12887,7 +12773,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12897,7 +12783,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -12917,7 +12803,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12927,7 +12813,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -12947,7 +12833,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12957,7 +12843,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -12977,7 +12863,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12987,7 +12873,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -13007,7 +12893,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13017,7 +12903,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -13037,7 +12923,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13047,7 +12933,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -13067,7 +12953,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13077,7 +12963,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -13097,7 +12983,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13107,7 +12993,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -13127,7 +13013,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13137,7 +13023,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -13157,7 +13043,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13167,7 +13053,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -13187,7 +13073,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13197,7 +13083,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -13217,7 +13103,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13227,7 +13113,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -13247,7 +13133,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13257,7 +13143,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -13277,7 +13163,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13287,7 +13173,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -13307,7 +13193,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13317,7 +13203,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -13337,7 +13223,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13347,7 +13233,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -13367,7 +13253,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13377,7 +13263,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -13397,7 +13283,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13407,7 +13293,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -13427,7 +13313,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13437,7 +13323,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -13457,7 +13343,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -13467,7 +13353,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$221</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SOURCE HEALTH'!$A$1:$F$90</definedName>
@@ -65,11 +65,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
@@ -81,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -690,76 +690,76 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mission Operations Engineering Intern – Summer 2027 </t>
+          <t>2027 Electrical Engineer Intern</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5447292008</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Platform Engineering Intern – Summer 2027 </t>
+          <t>2027 Flight Software Engineer Intern</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Costa Mesa, California, United States</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5447206008</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
         </is>
       </c>
     </row>
@@ -771,33 +771,33 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2027 Electrical Engineer Intern</t>
+          <t>2027 Industrial Engineer Intern</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148101007?gh_jid=5148101007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
         </is>
       </c>
     </row>
@@ -809,15 +809,15 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2027 Flight Software Engineer Intern</t>
+          <t>2027 Manufacturing Engineer Intern</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -829,13 +829,13 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5239083007?gh_jid=5239083007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
         </is>
       </c>
     </row>
@@ -847,33 +847,33 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2027 Industrial Engineer Intern</t>
+          <t>2027 Mechanical Engineer Intern</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
         </is>
       </c>
     </row>
@@ -885,33 +885,33 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Engineer Intern</t>
+          <t>2027 Quality &amp; Test Engineer Intern</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+          <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153218007?gh_jid=5153218007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257674007?gh_jid=5257674007</t>
         </is>
       </c>
     </row>
@@ -923,33 +923,33 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2027 Mechanical Engineer Intern</t>
+          <t>2027 Reliability Engineer Intern</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
+          <t>Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5153187007?gh_jid=5153187007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257682007?gh_jid=5257682007</t>
         </is>
       </c>
     </row>
@@ -961,33 +961,33 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2027 Quality &amp; Test Engineer Intern</t>
+          <t>2027 Software Engineer Intern</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257674007?gh_jid=5257674007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
         </is>
       </c>
     </row>
@@ -999,33 +999,33 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2027 Reliability Engineer Intern</t>
+          <t>2027 Supply Chain Intern</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257682007?gh_jid=5257682007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
         </is>
       </c>
     </row>
@@ -1037,33 +1037,33 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2027 Software Engineer Intern</t>
+          <t>2027 Systems Engineer Intern</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States; Boston, Massachusetts, United States; Broomfield, Colorado, United States; Colorado Springs, Colorado, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Irvine, California, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+          <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5148079007?gh_jid=5148079007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257690007?gh_jid=5257690007</t>
         </is>
       </c>
     </row>
@@ -1075,91 +1075,91 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2027 Supply Chain Intern</t>
+          <t>Winter 2027 Manufacturing Engineer Co-op</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+          <t>Ashville, Ohio, United States; Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2027 Systems Engineer Intern</t>
+          <t>Antenna Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257690007?gh_jid=5257690007</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Astranis</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Winter 2027 Manufacturing Engineer Co-op</t>
+          <t>Antenna Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States; Lexington, Massachusetts, United States; Quincy, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1171,13 +1171,13 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236589007?gh_jid=5236589007</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Antenna Associate (Summer 2027)</t>
+          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1197,7 +1197,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1209,13 +1209,13 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704301006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Antenna Intern (Summer 2027)</t>
+          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1235,25 +1235,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704274006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Assembly, Integration, and Test Intern (Summer 2027)</t>
+          <t>Avionics Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1273,7 +1273,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1285,13 +1285,13 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704761006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Automation &amp; Controls Engineering Intern (Summer 2027)</t>
+          <t>Avionics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1311,25 +1311,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4718206006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Avionics Associate Engineer (Summer 2027)</t>
+          <t>CAD Engineer Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1349,7 +1349,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1361,13 +1361,13 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4680324006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Avionics Intern (Summer 2027)</t>
+          <t>CAD Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1387,7 +1387,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1399,13 +1399,13 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706024006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
         </is>
       </c>
     </row>
@@ -1417,15 +1417,15 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Associate (Summer 2027)</t>
+          <t>Electrical Integration Associate - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1437,13 +1437,13 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704755006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CAD Engineer Intern (Summer 2027)</t>
+          <t>Electrical Integration Intern - RF (Summer 2027)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1463,7 +1463,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1475,13 +1475,13 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704742006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
         </is>
       </c>
     </row>
@@ -1493,15 +1493,15 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Associate - RF (Summer 2027)</t>
+          <t>Electrical Reliability Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1513,13 +1513,13 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Electrical Integration Intern - RF (Summer 2027)</t>
+          <t>Electrical Reliability Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1539,7 +1539,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1551,13 +1551,13 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715788006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Associate (Summer 2027)</t>
+          <t>FPGA Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1589,13 +1589,13 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704793006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Electrical Reliability Intern (Summer 2027)</t>
+          <t>FPGA Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1615,7 +1615,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1627,13 +1627,13 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704784006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>FPGA Associate (Summer 2027)</t>
+          <t>Flight Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1653,7 +1653,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1665,13 +1665,13 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704813006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>FPGA Intern (Summer 2027)</t>
+          <t>Flight Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1691,7 +1691,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1703,13 +1703,13 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704805006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Associate (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1741,13 +1741,13 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704716006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Intern (Summer 2027)</t>
+          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1767,7 +1767,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1779,13 +1779,13 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704598006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Associate (Summer 2027)</t>
+          <t>Harness Design Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1805,7 +1805,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1817,13 +1817,13 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704765006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation, and Control Intern (Summer 2027)</t>
+          <t>Harness Manufacturing Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1843,7 +1843,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1855,13 +1855,13 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705172006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Harness Design Engineer Intern (Summer 2027)</t>
+          <t>Harness Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1881,7 +1881,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1893,13 +1893,13 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704779006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Associate (Summer 2027)</t>
+          <t>Mechanical Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1919,7 +1919,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1931,13 +1931,13 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705260006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Harness Manufacturing Intern (Summer 2027)</t>
+          <t>Mechanical Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1957,7 +1957,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1969,13 +1969,13 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705255006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Associate Engineer (Summer 2027)</t>
+          <t>Power Electronics Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1995,7 +1995,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2007,13 +2007,13 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704620006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
         </is>
       </c>
     </row>
@@ -2025,15 +2025,15 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer Intern (Summer 2027)</t>
+          <t>Production Quality Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
+          <t xml:space="preserve">San Francisco </t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2045,13 +2045,13 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704601006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Power Electronics Intern (Summer 2027)</t>
+          <t>Propulsion Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2071,7 +2071,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2083,13 +2083,13 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4706425006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
         </is>
       </c>
     </row>
@@ -2101,15 +2101,15 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Production Quality Intern (Summer 2027)</t>
+          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco </t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2121,13 +2121,13 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705675006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineer Intern (Summer 2027)</t>
+          <t>Propulsion Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2147,7 +2147,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2159,13 +2159,13 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4713184006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Manufacturing Intern (Summer 2027)</t>
+          <t>RF Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2185,25 +2185,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705648006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Test Intern (Summer 2027)</t>
+          <t>RF Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2223,25 +2223,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705640006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Associate (Summer 2027)</t>
+          <t>RF Validation Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2261,25 +2261,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4707945006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>RF Hardware Intern (Summer 2027)</t>
+          <t>RF Validation Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708436006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Associate (Summer 2027)</t>
+          <t>Reliability Test Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2337,7 +2337,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2349,13 +2349,13 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716826006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>RF Validation Intern (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2387,13 +2387,13 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716499006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Reliability Test Intern (Summer 2027)</t>
+          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2413,7 +2413,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2425,13 +2425,13 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705629006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Associate (Summer 2027)</t>
+          <t>Software Developer, Network Software Associate (Summer 2027)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2451,7 +2451,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2463,13 +2463,13 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4715983006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Software Defined Radio Hardware Intern (Summer 2027)</t>
+          <t>Software Developer, Network Software Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2489,7 +2489,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2501,13 +2501,13 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
         </is>
       </c>
     </row>
@@ -2519,15 +2519,15 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Associate (Summer 2027)</t>
+          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2539,13 +2539,13 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705615006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
         </is>
       </c>
     </row>
@@ -2557,15 +2557,15 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Software Developer, Network Software Intern (Summer 2027)</t>
+          <t>Software Engineer Backend Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2577,13 +2577,13 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705597006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
         </is>
       </c>
     </row>
@@ -2595,15 +2595,15 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Enterprise Systems Intern (Summer 2027)</t>
+          <t>Technical Project Management Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2615,13 +2615,13 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705610006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
         </is>
       </c>
     </row>
@@ -2633,15 +2633,15 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Backend Intern (Summer 2027)</t>
+          <t>Thermal Associate Engineer (Summer 2027)</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2653,13 +2653,13 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4705214006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Technical Project Management Intern (Summer 2027)</t>
+          <t>Thermal Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2679,7 +2679,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2691,33 +2691,33 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006</t>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Thermal Associate Engineer (Summer 2027)</t>
+          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2729,33 +2729,33 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704831006</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Astranis</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Thermal Intern (Summer 2027)</t>
+          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
+          <t>USA - Hazelwood, MO</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2767,13 +2767,13 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/astranis/jobs/4704820006</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Boeing Business Internship Program (Paid) Summer 2027 - Human Resources</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2793,7 +2793,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2805,13 +2805,13 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Business-Internship-Program--Paid--Summer-2027---Human-Resources_JR2026520801</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
         </is>
       </c>
     </row>
@@ -2823,15 +2823,15 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (PAID) – Finance (Evergreen)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>USA - Hazelwood, MO</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2843,13 +2843,13 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Hazelwood-MO/Boeing-Summer-2027-Internship-Program--PAID----Finance--Evergreen-_JR2026519225</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Business Operations</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -2869,7 +2869,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2881,13 +2881,13 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Business-Operations_JR2026519268</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
         </is>
       </c>
     </row>
@@ -2899,15 +2899,15 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Facilities Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2919,13 +2919,13 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Facilities-Engineering_JR2026521015</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
         </is>
       </c>
     </row>
@@ -2937,15 +2937,15 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Global Real Estate and Facilities &amp; Property Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2957,13 +2957,13 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Global-Real-Estate-and-Facilities---Property-Management_JR2026520992</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Methods Process Analyst</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -2983,7 +2983,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2995,13 +2995,13 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Methods-Process-Analyst_JR2026519532</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
         </is>
       </c>
     </row>
@@ -3013,15 +3013,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Program Management</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3033,13 +3033,13 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Program-Management_JR2026521026</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
         </is>
       </c>
     </row>
@@ -3051,15 +3051,15 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Quality Engineering Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
+          <t>USA - Everett, WA</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3071,13 +3071,13 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Engineering-Intern_JR2026520439</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
         </is>
       </c>
     </row>
@@ -3089,15 +3089,15 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Sales and Marketing</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
+          <t>USA - Arlington, VA</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3109,13 +3109,13 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Sales-and-Marketing_JR2026518830</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Supply Chain</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3135,7 +3135,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3147,13 +3147,13 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Supply-Chain_JR2026519410</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
         </is>
       </c>
     </row>
@@ -3165,15 +3165,15 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Communications Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
+          <t>USA - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3185,13 +3185,13 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Communications-Intern_JR2026518829-1</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Data Analytics Intern</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3211,7 +3211,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3223,13 +3223,13 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Data-Analytics-Intern_JR2026520976</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Engineering</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3249,7 +3249,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3261,13 +3261,13 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Engineering_JR2026505093</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Information Digital Technology &amp; Security (IDT&amp;S)</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3287,7 +3287,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3299,71 +3299,71 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Information-Digital-Technology---Security--IDT-S-_JR2026520791</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Quality Specialist</t>
+          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Boeing-Summer-2027-Internship-Program--Paid----Quality-Specialist_JR2026520392</t>
+          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Security &amp; Fire Operation (S&amp;FO)</t>
+          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3375,13 +3375,13 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Boeing-Summer-2027-Internship-Program--Paid----Security---Fire-Operation--S-FO-_JR2026521717</t>
+          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
         </is>
       </c>
     </row>
@@ -3393,33 +3393,33 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
+          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
+          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
+          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3439,7 +3439,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3451,13 +3451,13 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e6d87528-5da1-4970-9e42-7b224cfa63a9</t>
+          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
         </is>
       </c>
     </row>
@@ -3469,15 +3469,15 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
+          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3489,13 +3489,13 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6a953cbc-af69-452c-b357-1a0a3db80bbf</t>
+          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
         </is>
       </c>
     </row>
@@ -3507,15 +3507,15 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, Hardware</t>
+          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3527,13 +3527,13 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ccb0f99f-0cc7-4517-8d1c-faeca53b5e5c</t>
+          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
+          <t>Summer 2027 - Embedded Software Engineering Internship</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3553,7 +3553,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3565,13 +3565,13 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/8eb71502-4374-45aa-82fa-2b62a42cd8e9</t>
+          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Internship, RF</t>
+          <t>Summer 2027 - Embedded Software Engineering Internship</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3591,7 +3591,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3603,13 +3603,13 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e835c385-69b0-4faf-a82f-17bf61260286</t>
+          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
         </is>
       </c>
     </row>
@@ -3621,15 +3621,15 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Embedded Software Engineering Internship</t>
+          <t>Summer 2027 - Finance Internship</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3641,13 +3641,13 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/96e97f22-a5b2-4e95-af84-b4f765343663</t>
+          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
         </is>
       </c>
     </row>
@@ -3659,15 +3659,15 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Embedded Software Engineering Internship</t>
+          <t>Summer 2027 - GNC Internship</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3679,13 +3679,13 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/d25bf640-2b2b-48d6-ab79-8a06b246caaa</t>
+          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Finance Internship</t>
+          <t>Summer 2027 - Manufacturing Internship</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3705,7 +3705,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3717,13 +3717,13 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e0525e31-2d45-441e-bf3e-36be4b67d8ef</t>
+          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
         </is>
       </c>
     </row>
@@ -3735,15 +3735,15 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - GNC Internship</t>
+          <t>Summer 2027 - Mechanical Engineering Internship</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3755,13 +3755,13 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e18ce6a5-32ed-468e-a39e-28de9eb16872</t>
+          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
         </is>
       </c>
     </row>
@@ -3773,15 +3773,15 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Manufacturing Internship</t>
+          <t>Summer 2027 - Mechanical Engineering Internship</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3793,13 +3793,13 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/79d56d02-19bb-42fa-a7c6-ae19659120d6</t>
+          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
         </is>
       </c>
     </row>
@@ -3811,15 +3811,15 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Internship</t>
+          <t>Summer 2027 - Supply Chain Internship</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3831,13 +3831,13 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/042f3a1d-5fc1-44ef-8f12-57044eaa4db2</t>
+          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Internship</t>
+          <t>Summer 2027 - Systems Engineering Internship</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3857,7 +3857,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3869,13 +3869,13 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/c7217acc-8eb4-4431-9e90-f426ccca8d1f</t>
+          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
         </is>
       </c>
     </row>
@@ -3887,15 +3887,15 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Supply Chain Internship</t>
+          <t>Summer 2027 - Systems Engineering Internship</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3907,13 +3907,13 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/6c354949-9e6b-4716-9381-f8aa071e3465</t>
+          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
         </is>
       </c>
     </row>
@@ -3925,33 +3925,33 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Systems Engineering Internship</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/a3b0f097-9d62-4a67-9800-de5dfe416da2</t>
+          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
         </is>
       </c>
     </row>
@@ -3963,15 +3963,15 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Systems Engineering Internship</t>
+          <t>Summer 2027 – Test Engineering Internship</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -3983,71 +3983,67 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ecb287e0-376b-49fd-baef-fe08c0c0234c</t>
+          <t>https://jobs.lever.co/CesiumAstro/ab7dd1c4-7196-4cae-8fbd-cddec993b9b8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>E-Space</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>E-Space 2027 Summer Internship, Arlington TX</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
+          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Test Engineering Internship</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Westminster, CO</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
+          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4059,33 +4055,29 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr"/>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/ab7dd1c4-7196-4cae-8fbd-cddec993b9b8</t>
+          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>E-Space</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>E-Space 2027 Summer Internship, Arlington TX</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Arlington, TX</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
+          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr"/>
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4097,29 +4089,33 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/espace/296ec3b9-550d-440a-a2c4-1e8fc6dd648b</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Completions - Mechanical Engineering College Intern (Appleton, WI)</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="6" t="inlineStr">
+          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4131,29 +4127,33 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr"/>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Appleton-Summer-2027-Completions-Mechanical-Engineering-College-Intern-%28Appleton%2C-WI%29-WI-54911/1424361600/</t>
+          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Stress Engineering - Collegiate Associate Intern</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr"/>
-      <c r="D93" s="6" t="inlineStr">
+          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4165,13 +4165,13 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Stress-Engineering-Collegiate-Associate-Intern-GA-31401/1423689500/</t>
+          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
         </is>
       </c>
     </row>
@@ -4183,33 +4183,33 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Avionics Electrical Engineering Intern - Spring/Summer 2027</t>
+          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/b7babdb5-64ee-49ad-a193-918d6a31c462</t>
+          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Build Reliability Engineering Intern - Spring/Summer 2027</t>
+          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -4229,7 +4229,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4241,13 +4241,13 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/ee3a4109-b6e7-4ed5-8981-a483b3936e5a</t>
+          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Engineering Intern (Simulation/Hardware-In-The-Loop) - Spring &amp; Summer 2027</t>
+          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -4267,25 +4267,25 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/78008094-ca81-4a0c-9a18-93b30f932acd</t>
+          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>GNC &amp; Flight Software Intern - Spring/Summer 2027</t>
+          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4305,7 +4305,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4317,13 +4317,13 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/555263f6-c5ec-4489-ab07-1aea546b70e7</t>
+          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Loads &amp; Dynamics Engineering Intern - Summer 2027</t>
+          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -4343,25 +4343,25 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/29c10a11-aa02-4d64-83d0-00001cbd3ac0</t>
+          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Intern - Spring/Summer 2027</t>
+          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -4381,7 +4381,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4393,13 +4393,13 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bdf3754-5649-4a50-913e-b05140cb004f</t>
+          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
         </is>
       </c>
     </row>
@@ -4411,15 +4411,15 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern  - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4431,13 +4431,13 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/1bc5c858-1b04-4093-80a0-2ba3491afc60</t>
+          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Mission Systems Engineering Intern - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -4457,7 +4457,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4469,13 +4469,13 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/9229aa88-f54d-4ecd-85ee-b31f53b4207d</t>
+          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
         </is>
       </c>
     </row>
@@ -4487,15 +4487,15 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Command &amp; Control) - Spring/Summer 2027</t>
+          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4507,13 +4507,13 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/5b08e2df-c9db-4831-aece-67d89e744796</t>
+          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (HIL) - Spring/Summer 2027</t>
+          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -4533,7 +4533,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4545,13 +4545,13 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d87ed913-affc-475e-b721-c5b5f11c3c7b</t>
+          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
         </is>
       </c>
     </row>
@@ -4563,15 +4563,15 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Modeling &amp; Simulation) - Spring/Summer 2027</t>
+          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4583,13 +4583,13 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/445db430-6f81-41cf-847a-56a947afb936</t>
+          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Structures/Mechanical Engineering Intern - Spring/Summer 2027</t>
+          <t>Supply Chain Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4609,7 +4609,7 @@
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4621,13 +4621,13 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/60b5d40a-1065-4bd2-8c72-6b2fb69d4761</t>
+          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
         </is>
       </c>
     </row>
@@ -4639,15 +4639,15 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Subsystem Test Engineering Intern - Spring/Summer 2027</t>
+          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4659,33 +4659,33 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/643fd7b7-9015-43a1-aa2b-a54f117b403c</t>
+          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Intern - Spring/Summer 2027</t>
+          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4697,25 +4697,25 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/17a0b249-c6c4-4361-ab9c-1aa7c4472591</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Test and Operations Engineering Intern - Spring/Summer 2027</t>
+          <t>Dynamics Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -4723,7 +4723,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4735,13 +4735,13 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/hermeus/d40446ee-40a9-4bb0-a3a8-a4a189b74630</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Avionics Systems/Test Engineering Intern – Summer 2027</t>
+          <t>Electrical Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -4761,7 +4761,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4773,13 +4773,13 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411921008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Dynamics Engineering Intern – Summer 2027</t>
+          <t>GNC Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -4799,7 +4799,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4811,13 +4811,13 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411916008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern – Summer 2027</t>
+          <t>Mechanical  Engineering Intern – Summer 2027</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -4837,7 +4837,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4849,13 +4849,13 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411918008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
         </is>
       </c>
     </row>
@@ -4867,33 +4867,33 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>GNC Engineering Intern – Summer 2027</t>
+          <t xml:space="preserve">Mission Operations Engineering Intern – Summer 2027 </t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411917008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5447292008</t>
         </is>
       </c>
     </row>
@@ -4905,33 +4905,33 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Mechanical  Engineering Intern – Summer 2027</t>
+          <t xml:space="preserve">Platform Engineering Intern – Summer 2027 </t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5411915008</t>
+          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5447206008</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
@@ -4989,7 +4989,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
@@ -5027,7 +5027,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
@@ -5065,7 +5065,7 @@
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
@@ -5103,7 +5103,7 @@
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr"/>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
@@ -5243,7 +5243,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
@@ -5281,7 +5281,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
@@ -5319,7 +5319,7 @@
           <t>Toronto, CAN</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
@@ -5357,7 +5357,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
+          <t>Toronto, CAN</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5407,13 +5407,13 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
+          <t>Pasadena, CA</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5483,13 +5483,13 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
           <t>Littleton, CO</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
@@ -5547,7 +5547,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
@@ -5585,7 +5585,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5635,13 +5635,13 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
@@ -5658,10 +5658,10 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
+          <t>Littleton, CO</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5673,13 +5673,13 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
@@ -5737,7 +5737,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
@@ -5813,7 +5813,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
@@ -5848,10 +5848,10 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
+          <t>Middle River, MD</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5863,13 +5863,13 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
         </is>
       </c>
     </row>
@@ -5886,10 +5886,10 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5901,13 +5901,13 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
         </is>
       </c>
     </row>
@@ -5924,10 +5924,10 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
+          <t>Silver Spring, MD</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5939,13 +5939,13 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -5962,10 +5962,10 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -5977,13 +5977,13 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -6000,10 +6000,10 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
+          <t>Toronto, CAN</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6015,13 +6015,13 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6041,7 @@
           <t>Tucson, AZ</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
@@ -6079,7 +6079,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
@@ -6117,7 +6117,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
@@ -6155,7 +6155,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
@@ -6193,7 +6193,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
@@ -6231,7 +6231,7 @@
           <t>Albuquerque, NM</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
@@ -6269,7 +6269,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
@@ -6304,10 +6304,10 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
+          <t>Middle River, MD</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6319,13 +6319,13 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
         </is>
       </c>
     </row>
@@ -6342,10 +6342,10 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6357,13 +6357,13 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
         </is>
       </c>
     </row>
@@ -6380,10 +6380,10 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
+          <t>Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6395,13 +6395,13 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
         </is>
       </c>
     </row>
@@ -6418,10 +6418,10 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
+          <t>Wallops Island, VA</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6433,13 +6433,13 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="D154" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
@@ -6497,7 +6497,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
           <t>Middle River, MD</t>
         </is>
       </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
+          <t>Chantilly, VA</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6585,13 +6585,13 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
         </is>
       </c>
     </row>
@@ -6608,10 +6608,10 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
+          <t>Pasadena, CA</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6623,13 +6623,13 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -6646,10 +6646,10 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6661,13 +6661,13 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
           <t>Tucson, AZ</t>
         </is>
       </c>
-      <c r="D160" s="6" t="inlineStr">
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
@@ -6725,7 +6725,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
@@ -6763,7 +6763,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
@@ -6801,7 +6801,7 @@
           <t>Stennis Space Center, MS</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
@@ -6839,7 +6839,7 @@
           <t>Wallops Island, VA</t>
         </is>
       </c>
-      <c r="D164" s="6" t="inlineStr">
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
@@ -6877,7 +6877,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D165" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
@@ -6915,7 +6915,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D166" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
@@ -6953,7 +6953,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D167" s="6" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
@@ -6991,7 +6991,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
@@ -7029,7 +7029,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
@@ -7067,7 +7067,7 @@
           <t>Seattle, Washington</t>
         </is>
       </c>
-      <c r="D170" s="6" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
@@ -7105,7 +7105,7 @@
           <t>San Diego, California</t>
         </is>
       </c>
-      <c r="D171" s="6" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
@@ -7143,7 +7143,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D173" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
@@ -7219,7 +7219,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
@@ -7257,7 +7257,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D175" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
@@ -7295,7 +7295,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D176" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
@@ -7333,7 +7333,7 @@
           <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
@@ -7371,7 +7371,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
@@ -7409,7 +7409,7 @@
           <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
@@ -7447,7 +7447,7 @@
           <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
         </is>
       </c>
-      <c r="D180" s="6" t="inlineStr">
+      <c r="D180" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
@@ -7485,7 +7485,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
@@ -7523,7 +7523,7 @@
           <t>Kent, Washington</t>
         </is>
       </c>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr"/>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr"/>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="D191" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
-      <c r="D192" s="6" t="inlineStr">
+      <c r="D192" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr"/>
-      <c r="D193" s="6" t="inlineStr">
+      <c r="D193" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
@@ -7935,7 +7935,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D194" s="6" t="inlineStr">
+      <c r="D194" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
@@ -7973,7 +7973,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D195" s="6" t="inlineStr">
+      <c r="D195" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
@@ -8011,7 +8011,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D196" s="6" t="inlineStr">
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr"/>
@@ -8049,7 +8049,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D197" s="6" t="inlineStr">
+      <c r="D197" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
@@ -8087,7 +8087,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D198" s="6" t="inlineStr">
+      <c r="D198" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
@@ -8125,7 +8125,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D199" s="6" t="inlineStr">
+      <c r="D199" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
@@ -8163,7 +8163,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D200" s="6" t="inlineStr">
+      <c r="D200" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr"/>
@@ -8201,7 +8201,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D201" s="6" t="inlineStr">
+      <c r="D201" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
@@ -8239,7 +8239,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D202" s="6" t="inlineStr">
+      <c r="D202" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr"/>
@@ -8277,7 +8277,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D203" s="6" t="inlineStr">
+      <c r="D203" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
@@ -8315,7 +8315,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D204" s="6" t="inlineStr">
+      <c r="D204" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
@@ -8353,7 +8353,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D205" s="6" t="inlineStr">
+      <c r="D205" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr"/>
@@ -8391,7 +8391,7 @@
           <t>El Segundo, California, United States</t>
         </is>
       </c>
-      <c r="D206" s="6" t="inlineStr">
+      <c r="D206" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr"/>
@@ -8429,7 +8429,7 @@
           <t>Ashville, Ohio, United States</t>
         </is>
       </c>
-      <c r="D207" s="7" t="inlineStr">
+      <c r="D207" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8467,7 +8467,7 @@
           <t>South Burlington, Vermont, United States</t>
         </is>
       </c>
-      <c r="D208" s="7" t="inlineStr">
+      <c r="D208" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8505,7 +8505,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D209" s="7" t="inlineStr">
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8543,7 +8543,7 @@
           <t>USA - Auburn, WA</t>
         </is>
       </c>
-      <c r="D210" s="7" t="inlineStr">
+      <c r="D210" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8581,7 +8581,7 @@
           <t>USA - Everett, WA</t>
         </is>
       </c>
-      <c r="D211" s="7" t="inlineStr">
+      <c r="D211" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8619,7 +8619,7 @@
           <t>USA - Seattle, WA</t>
         </is>
       </c>
-      <c r="D212" s="7" t="inlineStr">
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8657,7 +8657,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D213" s="7" t="inlineStr">
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8695,7 +8695,7 @@
           <t>Westminster, CO</t>
         </is>
       </c>
-      <c r="D214" s="7" t="inlineStr">
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8733,7 +8733,7 @@
           <t>Evendale</t>
         </is>
       </c>
-      <c r="D215" s="7" t="inlineStr">
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr"/>
-      <c r="D216" s="7" t="inlineStr">
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr"/>
-      <c r="D217" s="7" t="inlineStr">
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr"/>
-      <c r="D218" s="7" t="inlineStr">
+      <c r="D218" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr"/>
-      <c r="D219" s="7" t="inlineStr">
+      <c r="D219" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr"/>
-      <c r="D220" s="7" t="inlineStr">
+      <c r="D220" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8941,7 +8941,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D221" s="7" t="inlineStr">
+      <c r="D221" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -8975,7 +8975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9030,84 +9030,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>K2 Space</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mission Operations Engineering Intern – Summer 2027 </t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5447292008</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>K2 Space</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform Engineering Intern – Summer 2027 </t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/k2spacecorporation/jobs/5447206008</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9118,7 +9042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9191,7 +9115,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -9201,7 +9125,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9229,7 +9153,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -9239,7 +9163,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9265,7 +9189,7 @@
           <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9277,7 +9201,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9303,7 +9227,7 @@
           <t>Costa Mesa, California, United States</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9315,7 +9239,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9341,7 +9265,7 @@
           <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9353,7 +9277,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9379,7 +9303,7 @@
           <t>Long Beach, CA</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9391,7 +9315,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9417,7 +9341,7 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9429,7 +9353,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -9455,7 +9379,7 @@
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9467,7 +9391,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -9493,7 +9417,7 @@
           <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9505,7 +9429,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -9515,122 +9439,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Rocket Lab</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Government Operations Intern Summer 2027</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Littleton, CO</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Rocket Lab</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Government Operations Intern Summer 2027</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Washington, DC</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2027 Industrial Engineer Intern</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255593007?gh_jid=5255593007</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9712,7 +9522,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9724,7 +9534,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9750,7 +9560,7 @@
           <t>USA - Arlington, VA</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9762,7 +9572,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9788,7 +9598,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9800,7 +9610,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9826,7 +9636,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9838,7 +9648,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9864,7 +9674,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9876,7 +9686,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9902,7 +9712,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9914,7 +9724,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9940,7 +9750,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9952,7 +9762,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -9978,7 +9788,7 @@
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -9990,7 +9800,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -10016,7 +9826,7 @@
           <t>Arlington, TX</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10028,7 +9838,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -10054,7 +9864,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10066,7 +9876,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -10092,7 +9902,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10104,7 +9914,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -10130,7 +9940,7 @@
           <t>Dallas, Texas</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -10142,7 +9952,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -10285,7 +10095,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10295,7 +10105,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10315,7 +10125,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10325,7 +10135,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10345,7 +10155,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10355,7 +10165,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10375,7 +10185,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10385,7 +10195,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10405,7 +10215,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10415,7 +10225,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10435,7 +10245,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10445,7 +10255,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10465,7 +10275,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10475,7 +10285,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10495,7 +10305,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10505,7 +10315,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -10525,7 +10335,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10535,7 +10345,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10555,7 +10365,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10565,7 +10375,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10585,7 +10395,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10595,7 +10405,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10615,7 +10425,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10625,7 +10435,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10645,7 +10455,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10655,7 +10465,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10675,7 +10485,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10685,7 +10495,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -10705,7 +10515,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10715,7 +10525,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10735,7 +10545,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10745,7 +10555,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10765,7 +10575,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10775,7 +10585,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10795,7 +10605,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10805,7 +10615,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -10825,7 +10635,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10835,7 +10645,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -10855,7 +10665,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10865,7 +10675,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10885,7 +10695,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -10895,7 +10705,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10915,7 +10725,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -10925,7 +10735,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10945,7 +10755,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -10955,7 +10765,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -10975,7 +10785,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -10985,7 +10795,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -11005,7 +10815,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11015,7 +10825,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11035,7 +10845,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -11045,7 +10855,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -11065,7 +10875,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11075,7 +10885,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -11095,7 +10905,7 @@
           <t>lever</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11105,7 +10915,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -11125,7 +10935,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11135,7 +10945,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -11155,7 +10965,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11165,7 +10975,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11185,7 +10995,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11195,7 +11005,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11215,7 +11025,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11225,7 +11035,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11245,7 +11055,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11255,7 +11065,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11275,7 +11085,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11285,7 +11095,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -11305,7 +11115,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11315,7 +11125,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -11335,7 +11145,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11345,7 +11155,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -11365,7 +11175,7 @@
           <t>workday</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11375,7 +11185,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11395,7 +11205,7 @@
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11405,7 +11215,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11425,7 +11235,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11435,7 +11245,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -11455,7 +11265,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11465,7 +11275,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -11485,7 +11295,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
@@ -11495,7 +11305,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -11515,7 +11325,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11525,7 +11335,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -11545,7 +11355,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11555,7 +11365,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -11575,7 +11385,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11585,7 +11395,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -11605,7 +11415,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11615,7 +11425,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -11635,7 +11445,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11645,7 +11455,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -11665,7 +11475,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11675,7 +11485,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -11695,7 +11505,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11705,7 +11515,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11725,7 +11535,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11735,7 +11545,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -11755,7 +11565,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11765,7 +11575,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -11785,7 +11595,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11795,7 +11605,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -11815,7 +11625,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11825,7 +11635,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -11845,7 +11655,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11855,7 +11665,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -11875,7 +11685,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11885,7 +11695,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -11905,7 +11715,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11915,7 +11725,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -11935,7 +11745,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11945,7 +11755,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -11965,7 +11775,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -11975,7 +11785,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -11995,7 +11805,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12005,7 +11815,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -12025,7 +11835,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12035,7 +11845,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -12055,7 +11865,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12065,7 +11875,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -12085,7 +11895,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12095,7 +11905,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -12115,7 +11925,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12125,7 +11935,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -12145,7 +11955,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12155,7 +11965,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -12175,7 +11985,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12185,7 +11995,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -12205,7 +12015,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12215,7 +12025,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -12235,7 +12045,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12245,7 +12055,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -12265,7 +12075,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12275,7 +12085,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -12295,7 +12105,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12305,7 +12115,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -12325,7 +12135,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12335,7 +12145,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -12355,7 +12165,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12365,7 +12175,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -12385,7 +12195,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12395,7 +12205,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -12415,7 +12225,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12425,7 +12235,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -12445,7 +12255,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12455,7 +12265,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -12475,7 +12285,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12485,7 +12295,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -12505,7 +12315,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12515,7 +12325,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -12535,7 +12345,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12545,7 +12355,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -12565,7 +12375,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12575,7 +12385,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -12595,7 +12405,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12605,7 +12415,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -12625,7 +12435,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12635,7 +12445,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -12655,7 +12465,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12665,7 +12475,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -12685,7 +12495,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12695,7 +12505,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -12715,7 +12525,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12725,7 +12535,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -12745,7 +12555,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12755,7 +12565,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -12775,7 +12585,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12785,7 +12595,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -12805,7 +12615,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12815,7 +12625,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -12835,7 +12645,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12845,7 +12655,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -12865,7 +12675,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12875,7 +12685,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -12895,7 +12705,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12905,7 +12715,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -12925,7 +12735,7 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -12935,7 +12745,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SOURCE HEALTH'!$A$1:$F$90</definedName>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -715,7 +715,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr"/>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -5407,13 +5407,13 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Toronto, CAN</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -5483,13 +5483,13 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Littleton, CO</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -5635,13 +5635,13 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -5673,13 +5673,13 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
+          <t>Toronto, CAN</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
@@ -5939,13 +5939,13 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Silver Spring, MD</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -5977,13 +5977,13 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
@@ -6015,13 +6015,13 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -6319,13 +6319,13 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -6357,13 +6357,13 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -6395,13 +6395,13 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -6433,13 +6433,13 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -6509,13 +6509,13 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990063003</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -6547,13 +6547,13 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990063003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -6585,13 +6585,13 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Chantilly, VA</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
@@ -6623,13 +6623,13 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Tucson, AZ</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
@@ -6661,13 +6661,13 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987046003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
@@ -6699,13 +6699,13 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Stennis Space Center, MS</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
@@ -6813,13 +6813,13 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Stennis Space Center, MS</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
@@ -6851,13 +6851,13 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr"/>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr"/>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr"/>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr"/>
@@ -9042,7 +9042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9325,122 +9325,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>CesiumAstro</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/CesiumAstro/9d308f2f-7a8a-4f04-b24e-bc6353875cfa</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CesiumAstro</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Summer 2027 - Electrical Engineering Internship, FPGA</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/CesiumAstro/5ac10e3b-f9d7-4029-bf25-73a191ff2636</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2027 Supply Chain Intern</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Costa Mesa, California, United States; Fort Collins, Colorado, United States; Quincy, Massachusetts, United States; Santa Ana, California, United States; Waltham, Massachusetts, United States</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5255827007?gh_jid=5255827007</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9534,7 +9420,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9572,7 +9458,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9610,7 +9496,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9648,7 +9534,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9686,7 +9572,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9724,7 +9610,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9762,7 +9648,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -9800,7 +9686,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -9838,7 +9724,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -9876,7 +9762,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -9914,7 +9800,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -9952,7 +9838,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -10105,7 +9991,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10135,7 +10021,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10165,7 +10051,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10195,7 +10081,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10225,7 +10111,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10255,7 +10141,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10285,7 +10171,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10315,7 +10201,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -10345,7 +10231,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10375,7 +10261,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10405,7 +10291,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10435,7 +10321,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10465,7 +10351,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10495,7 +10381,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -10525,7 +10411,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10555,7 +10441,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10585,7 +10471,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10615,7 +10501,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -10645,7 +10531,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -10675,7 +10561,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10705,7 +10591,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10735,7 +10621,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10765,7 +10651,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -10795,7 +10681,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -10825,7 +10711,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -10855,7 +10741,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -10885,7 +10771,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -10915,7 +10801,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -10945,7 +10831,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -10975,7 +10861,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11005,7 +10891,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11035,7 +10921,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11065,7 +10951,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11095,7 +10981,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -11125,7 +11011,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -11155,7 +11041,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -11185,7 +11071,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11215,7 +11101,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11245,7 +11131,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -11257,7 +11143,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Sierra Space</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -11275,19 +11161,19 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>500 Server Error: Internal Server Error for url: https://standardaero.wd1.myworkdayjobs.com/External?q=intern</t>
+          <t>HTTPSConnectionPool(host='www.sierraspace.com', port=443): Max retries exceeded with url: /careers/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1016)')))</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Venturi Astrolab</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -11305,19 +11191,19 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.astrolab.space/careers</t>
+          <t>500 Server Error: Internal Server Error for url: https://standardaero.wd1.myworkdayjobs.com/External?q=intern</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Venturi Astrolab</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -11325,9 +11211,9 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
@@ -11335,19 +11221,19 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+          <t>404 Client Error: Not Found for url: https://www.astrolab.space/careers</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Airbus Americas</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -11365,7 +11251,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -11377,7 +11263,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Airbus Americas</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -11395,7 +11281,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -11407,7 +11293,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Archer Aviation</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -11425,7 +11311,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -11437,7 +11323,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Axiom Space</t>
+          <t>Archer Aviation</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -11455,7 +11341,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -11467,7 +11353,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Axiom Space</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -11485,7 +11371,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -11497,7 +11383,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Barrios Technology</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -11515,7 +11401,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11527,7 +11413,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Bell / Textron</t>
+          <t>Barrios Technology</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -11545,7 +11431,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -11557,7 +11443,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>BlackSky</t>
+          <t>Bell / Textron</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -11575,7 +11461,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -11587,7 +11473,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Bombardier</t>
+          <t>BlackSky</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -11605,7 +11491,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -11617,7 +11503,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>Bombardier</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -11635,7 +11521,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -11647,7 +11533,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Capella Space</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -11665,7 +11551,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -11677,7 +11563,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Curtiss-Wright</t>
+          <t>Capella Space</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -11695,7 +11581,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -11707,7 +11593,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Eaton Aerospace</t>
+          <t>Curtiss-Wright</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -11725,7 +11611,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -11737,7 +11623,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Eaton Aerospace</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -11755,7 +11641,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -11767,7 +11653,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Firefly Aerospace</t>
+          <t>Embraer</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -11785,7 +11671,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -11797,7 +11683,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>GKN Aerospace</t>
+          <t>Firefly Aerospace</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -11815,7 +11701,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -11827,7 +11713,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>General Atomics Aeronautical Systems</t>
+          <t>GKN Aerospace</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -11845,7 +11731,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -11857,7 +11743,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>General Dynamics Mission Systems</t>
+          <t>General Atomics Aeronautical Systems</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -11875,7 +11761,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -11887,7 +11773,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>General Dynamics Mission Systems</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -11905,7 +11791,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -11917,7 +11803,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -11935,7 +11821,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -11947,7 +11833,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Intuitive Machines</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -11965,7 +11851,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -11977,7 +11863,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Intuitive Machines</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -11995,7 +11881,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -12007,7 +11893,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Johns Hopkins APL</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -12025,7 +11911,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -12037,7 +11923,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Johns Hopkins APL</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -12055,7 +11941,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -12067,7 +11953,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -12085,7 +11971,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -12097,7 +11983,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -12115,7 +12001,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -12127,7 +12013,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Lunar Outpost</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -12145,7 +12031,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -12157,7 +12043,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Maxar Space Systems</t>
+          <t>Lunar Outpost</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -12175,7 +12061,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -12187,7 +12073,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Moog</t>
+          <t>Maxar Space Systems</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -12205,7 +12091,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -12217,7 +12103,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Muon Space</t>
+          <t>Moog</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -12235,7 +12121,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -12247,7 +12133,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NASA</t>
+          <t>Muon Space</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -12265,7 +12151,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -12277,7 +12163,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NASA / USAJobs Pathways</t>
+          <t>NASA</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -12295,7 +12181,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -12307,7 +12193,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>NASA / USAJobs Pathways</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -12325,7 +12211,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -12337,7 +12223,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Oceaneering</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -12355,7 +12241,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -12367,7 +12253,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Planet Labs</t>
+          <t>Oceaneering</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -12385,7 +12271,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -12397,7 +12283,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Redwire</t>
+          <t>Planet Labs</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -12415,7 +12301,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -12427,7 +12313,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Scaled Composites</t>
+          <t>Redwire</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -12445,7 +12331,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -12457,7 +12343,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Sierra Space</t>
+          <t>Scaled Composites</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -12475,7 +12361,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -12505,7 +12391,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -12535,7 +12421,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -12565,7 +12451,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -12595,7 +12481,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -12625,7 +12511,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -12655,7 +12541,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -12685,7 +12571,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -12715,7 +12601,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -12745,7 +12631,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -715,7 +715,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr"/>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Toronto, CAN</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -5407,13 +5407,13 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -5445,13 +5445,13 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -5483,13 +5483,13 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -5635,13 +5635,13 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Littleton, CO</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -5673,13 +5673,13 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -5863,13 +5863,13 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -5901,13 +5901,13 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -6319,13 +6319,13 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -6357,13 +6357,13 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -6395,13 +6395,13 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -6509,13 +6509,13 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990063003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -6547,13 +6547,13 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990063003</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
@@ -6623,13 +6623,13 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Chantilly, VA</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
@@ -6699,13 +6699,13 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Stennis Space Center, MS</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
@@ -6813,13 +6813,13 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Stennis Space Center, MS</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
@@ -6851,13 +6851,13 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990350003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr"/>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr"/>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr"/>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -10663,7 +10663,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Parker Aerospace</t>
+          <t>NASA</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -10681,19 +10681,19 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>403 Client Error: Forbidden for url: https://parkercareers.ttcportals.com/search/jobs?q=intern</t>
+          <t>429 Client Error: Too Many Requests for url: https://www.nasa.gov/learning-resources/internship-programs/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>Parker Aerospace</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -10711,19 +10711,19 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>403 Client Error: Forbidden for url: https://jobs.saic.com/search/intern/jobs</t>
+          <t>403 Client Error: Forbidden for url: https://parkercareers.ttcportals.com/search/jobs?q=intern</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Safran</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -10741,29 +10741,29 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>403 Client Error: Forbidden for url: https://www.safran-group.com/jobs?search=intern</t>
+          <t>403 Client Error: Forbidden for url: https://jobs.saic.com/search/intern/jobs</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Apex Space</t>
+          <t>Safran</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>careers_page</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
@@ -10771,24 +10771,24 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/apexspace/jobs?content=true</t>
+          <t>403 Client Error: Forbidden for url: https://www.safran-group.com/jobs?search=intern</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Boom Supersonic</t>
+          <t>Apex Space</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -10801,24 +10801,24 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://api.lever.co/v0/postings/boomsupersonic?mode=json</t>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/apexspace/jobs?content=true</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Crane Aerospace &amp; Electronics</t>
+          <t>Boom Supersonic</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>careers_page</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -10831,24 +10831,24 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>HTTPSConnectionPool(host='jobs.craneco.com', port=443): Max retries exceeded with url: /search/?q=intern (Caused by NameResolutionError("HTTPSConnection(host='jobs.craneco.com', port=443): Failed to resolve 'jobs.craneco.com' ([Errno -2] Name or service not known)"))</t>
+          <t>404 Client Error: Not Found for url: https://api.lever.co/v0/postings/boomsupersonic?mode=json</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Hadrian</t>
+          <t>Crane Aerospace &amp; Electronics</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>careers_page</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -10861,24 +10861,24 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/hadrian/jobs?content=true</t>
+          <t>HTTPSConnectionPool(host='jobs.craneco.com', port=443): Max retries exceeded with url: /search/?q=intern (Caused by NameResolutionError("HTTPSConnection(host='jobs.craneco.com', port=443): Failed to resolve 'jobs.craneco.com' ([Errno -2] Name or service not known)"))</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Hadrian</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>careers_page</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -10891,24 +10891,24 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>500 Server Error: Internal Server Error for url: https://howmet.wd5.myworkdayjobs.com/Howmet_Careers?q=intern</t>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/hadrian/jobs?content=true</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Impulse Space</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>careers_page</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -10921,24 +10921,24 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/impulsespace/jobs?content=true</t>
+          <t>500 Server Error: Internal Server Error for url: https://howmet.wd5.myworkdayjobs.com/Howmet_Careers?q=intern</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Kratos Defense</t>
+          <t>Impulse Space</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>careers_page</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -10951,19 +10951,19 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>HTTPSConnectionPool(host='careers.kratosdefense.com', port=443): Max retries exceeded with url: /search/jobs?q=intern (Caused by NameResolutionError("HTTPSConnection(host='careers.kratosdefense.com', port=443): Failed to resolve 'careers.kratosdefense.com' ([Errno -2] Name or service not known)"))</t>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/impulsespace/jobs?content=true</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>NASA JPL / Caltech</t>
+          <t>Kratos Defense</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -10981,19 +10981,19 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.jpl.jobs/internships</t>
+          <t>HTTPSConnectionPool(host='careers.kratosdefense.com', port=443): Max retries exceeded with url: /search/jobs?q=intern (Caused by NameResolutionError("HTTPSConnection(host='careers.kratosdefense.com', port=443): Failed to resolve 'careers.kratosdefense.com' ([Errno -2] Name or service not known)"))</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Parsons</t>
+          <t>NASA JPL / Caltech</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -11011,19 +11011,19 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://jobs.parsons.com/jobs/search?q=intern</t>
+          <t>404 Client Error: Not Found for url: https://www.jpl.jobs/internships</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Parsons</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -11041,24 +11041,24 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.careers.peraton.com/jobs/search?query=intern</t>
+          <t>404 Client Error: Not Found for url: https://jobs.parsons.com/jobs/search?q=intern</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>RTX / Raytheon / Collins / Pratt &amp; Whitney</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>careers_page</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -11071,24 +11071,24 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>422 Client Error: Unprocessable Entity for url: https://globalhr.wd5.myworkdayjobs.com/wday/cxs/RTX/REC_RTX_Ext_Gateway/jobs</t>
+          <t>404 Client Error: Not Found for url: https://www.careers.peraton.com/jobs/search?query=intern</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Relativity Space Internships</t>
+          <t>RTX / Raytheon / Collins / Pratt &amp; Whitney</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -11101,24 +11101,24 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/rsinternboard/jobs?content=true</t>
+          <t>422 Client Error: Unprocessable Entity for url: https://globalhr.wd5.myworkdayjobs.com/wday/cxs/RTX/REC_RTX_Ext_Gateway/jobs</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Sierra Nevada Corporation</t>
+          <t>Relativity Space Internships</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>careers_page</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -11131,19 +11131,19 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.sncorp.com/careers/open-positions</t>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/rsinternboard/jobs?content=true</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Sierra Space</t>
+          <t>Sierra Nevada Corporation</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -11161,19 +11161,19 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>HTTPSConnectionPool(host='www.sierraspace.com', port=443): Max retries exceeded with url: /careers/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1016)')))</t>
+          <t>404 Client Error: Not Found for url: https://www.sncorp.com/careers/open-positions</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Sierra Space</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -11191,19 +11191,19 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>500 Server Error: Internal Server Error for url: https://standardaero.wd1.myworkdayjobs.com/External?q=intern</t>
+          <t>HTTPSConnectionPool(host='www.sierraspace.com', port=443): Max retries exceeded with url: /careers/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1016)')))</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Venturi Astrolab</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -11221,19 +11221,19 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.astrolab.space/careers</t>
+          <t>500 Server Error: Internal Server Error for url: https://standardaero.wd1.myworkdayjobs.com/External?q=intern</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Venturi Astrolab</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -11241,9 +11241,9 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
@@ -11251,19 +11251,19 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
+          <t>404 Client Error: Not Found for url: https://www.astrolab.space/careers</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Airbus Americas</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -11293,7 +11293,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Airbus Americas</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -11323,7 +11323,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Archer Aviation</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -11353,7 +11353,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Axiom Space</t>
+          <t>Archer Aviation</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -11383,7 +11383,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Axiom Space</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11413,7 +11413,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Barrios Technology</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -11443,7 +11443,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Bell / Textron</t>
+          <t>Barrios Technology</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -11473,7 +11473,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>BlackSky</t>
+          <t>Bell / Textron</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Bombardier</t>
+          <t>BlackSky</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -11533,7 +11533,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>Bombardier</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -11563,7 +11563,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Capella Space</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -11593,7 +11593,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Curtiss-Wright</t>
+          <t>Capella Space</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Eaton Aerospace</t>
+          <t>Curtiss-Wright</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -11653,7 +11653,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Eaton Aerospace</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -11683,7 +11683,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Firefly Aerospace</t>
+          <t>Embraer</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -11713,7 +11713,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>GKN Aerospace</t>
+          <t>Firefly Aerospace</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -11743,7 +11743,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>General Atomics Aeronautical Systems</t>
+          <t>GKN Aerospace</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>General Dynamics Mission Systems</t>
+          <t>General Atomics Aeronautical Systems</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -11803,7 +11803,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>General Dynamics Mission Systems</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -11833,7 +11833,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -11863,7 +11863,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Intuitive Machines</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -11893,7 +11893,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Intuitive Machines</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -11923,7 +11923,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Johns Hopkins APL</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -11953,7 +11953,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Johns Hopkins APL</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -11983,7 +11983,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -12013,7 +12013,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Lunar Outpost</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -12073,7 +12073,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Maxar Space Systems</t>
+          <t>Lunar Outpost</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -12103,7 +12103,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Moog</t>
+          <t>Maxar Space Systems</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -12133,7 +12133,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Muon Space</t>
+          <t>Moog</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -12163,7 +12163,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NASA</t>
+          <t>Muon Space</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SOURCE HEALTH'!$A$1:$F$90</definedName>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -715,7 +715,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr"/>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -5407,13 +5407,13 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Toronto, CAN</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -5445,13 +5445,13 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -5825,13 +5825,13 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984564003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -5901,13 +5901,13 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7988835003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984564003</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -6357,13 +6357,13 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -6395,13 +6395,13 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -6433,13 +6433,13 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
+          <t>Chantilly, VA</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
@@ -6661,13 +6661,13 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
+          <t>Tucson, AZ</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
@@ -6699,13 +6699,13 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr"/>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr"/>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr"/>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr"/>
@@ -9042,7 +9042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9287,46 +9287,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Rocket Lab</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>RF Engineering Intern Summer 2027</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:H6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9420,7 +9382,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9458,7 +9420,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9496,7 +9458,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9534,7 +9496,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9572,7 +9534,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9610,7 +9572,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9648,7 +9610,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -9686,7 +9648,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -9724,7 +9686,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -9762,7 +9724,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -9800,7 +9762,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -9838,7 +9800,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -9991,7 +9953,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10021,7 +9983,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10051,7 +10013,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10081,7 +10043,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10111,7 +10073,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10141,7 +10103,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10171,7 +10133,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10201,7 +10163,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -10231,7 +10193,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10261,7 +10223,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10291,7 +10253,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10321,7 +10283,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10351,7 +10313,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10381,7 +10343,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -10411,7 +10373,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10441,7 +10403,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10471,7 +10433,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10501,7 +10463,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -10531,7 +10493,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -10561,7 +10523,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10591,7 +10553,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10621,7 +10583,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10651,7 +10613,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -10663,7 +10625,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>NASA</t>
+          <t>Parker Aerospace</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -10681,19 +10643,19 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.nasa.gov/learning-resources/internship-programs/</t>
+          <t>403 Client Error: Forbidden for url: https://parkercareers.ttcportals.com/search/jobs?q=intern</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Parker Aerospace</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -10711,19 +10673,19 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>403 Client Error: Forbidden for url: https://parkercareers.ttcportals.com/search/jobs?q=intern</t>
+          <t>403 Client Error: Forbidden for url: https://jobs.saic.com/search/intern/jobs</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>Safran</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -10741,29 +10703,29 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>403 Client Error: Forbidden for url: https://jobs.saic.com/search/intern/jobs</t>
+          <t>403 Client Error: Forbidden for url: https://www.safran-group.com/jobs?search=intern</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Safran</t>
+          <t>Apex Space</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>careers_page</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
@@ -10771,24 +10733,24 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>403 Client Error: Forbidden for url: https://www.safran-group.com/jobs?search=intern</t>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/apexspace/jobs?content=true</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Apex Space</t>
+          <t>Boom Supersonic</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -10801,24 +10763,24 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/apexspace/jobs?content=true</t>
+          <t>404 Client Error: Not Found for url: https://api.lever.co/v0/postings/boomsupersonic?mode=json</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Boom Supersonic</t>
+          <t>Crane Aerospace &amp; Electronics</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>careers_page</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -10831,24 +10793,24 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://api.lever.co/v0/postings/boomsupersonic?mode=json</t>
+          <t>HTTPSConnectionPool(host='jobs.craneco.com', port=443): Max retries exceeded with url: /search/?q=intern (Caused by NameResolutionError("HTTPSConnection(host='jobs.craneco.com', port=443): Failed to resolve 'jobs.craneco.com' ([Errno -2] Name or service not known)"))</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Crane Aerospace &amp; Electronics</t>
+          <t>Hadrian</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>careers_page</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -10861,24 +10823,24 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>HTTPSConnectionPool(host='jobs.craneco.com', port=443): Max retries exceeded with url: /search/?q=intern (Caused by NameResolutionError("HTTPSConnection(host='jobs.craneco.com', port=443): Failed to resolve 'jobs.craneco.com' ([Errno -2] Name or service not known)"))</t>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/hadrian/jobs?content=true</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Hadrian</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>careers_page</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -10891,24 +10853,24 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/hadrian/jobs?content=true</t>
+          <t>500 Server Error: Internal Server Error for url: https://howmet.wd5.myworkdayjobs.com/Howmet_Careers?q=intern</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Impulse Space</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>careers_page</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -10921,24 +10883,24 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>500 Server Error: Internal Server Error for url: https://howmet.wd5.myworkdayjobs.com/Howmet_Careers?q=intern</t>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/impulsespace/jobs?content=true</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Impulse Space</t>
+          <t>Kratos Defense</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>careers_page</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -10951,19 +10913,19 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/impulsespace/jobs?content=true</t>
+          <t>HTTPSConnectionPool(host='careers.kratosdefense.com', port=443): Max retries exceeded with url: /search/jobs?q=intern (Caused by NameResolutionError("HTTPSConnection(host='careers.kratosdefense.com', port=443): Failed to resolve 'careers.kratosdefense.com' ([Errno -2] Name or service not known)"))</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Kratos Defense</t>
+          <t>NASA JPL / Caltech</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -10981,19 +10943,19 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>HTTPSConnectionPool(host='careers.kratosdefense.com', port=443): Max retries exceeded with url: /search/jobs?q=intern (Caused by NameResolutionError("HTTPSConnection(host='careers.kratosdefense.com', port=443): Failed to resolve 'careers.kratosdefense.com' ([Errno -2] Name or service not known)"))</t>
+          <t>404 Client Error: Not Found for url: https://www.jpl.jobs/internships</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>NASA JPL / Caltech</t>
+          <t>Parsons</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -11011,19 +10973,19 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.jpl.jobs/internships</t>
+          <t>404 Client Error: Not Found for url: https://jobs.parsons.com/jobs/search?q=intern</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Parsons</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -11041,19 +11003,19 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://jobs.parsons.com/jobs/search?q=intern</t>
+          <t>404 Client Error: Not Found for url: https://www.careers.peraton.com/jobs/search?query=intern</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Planet Labs</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -11071,12 +11033,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.careers.peraton.com/jobs/search?query=intern</t>
+          <t>HTTPSConnectionPool(host='www.planet.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11063,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11131,7 +11093,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -11161,7 +11123,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -11173,7 +11135,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Sierra Space</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -11191,19 +11153,19 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>HTTPSConnectionPool(host='www.sierraspace.com', port=443): Max retries exceeded with url: /careers/ (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1016)')))</t>
+          <t>500 Server Error: Internal Server Error for url: https://standardaero.wd1.myworkdayjobs.com/External?q=intern</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Venturi Astrolab</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -11221,19 +11183,19 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>500 Server Error: Internal Server Error for url: https://standardaero.wd1.myworkdayjobs.com/External?q=intern</t>
+          <t>404 Client Error: Not Found for url: https://www.astrolab.space/careers</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Venturi Astrolab</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -11241,9 +11203,9 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
@@ -11251,19 +11213,19 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.astrolab.space/careers</t>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Airbus Americas</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -11281,7 +11243,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -11293,7 +11255,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Airbus Americas</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -11311,7 +11273,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -11323,7 +11285,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Archer Aviation</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -11341,7 +11303,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -11353,7 +11315,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Archer Aviation</t>
+          <t>Axiom Space</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -11371,7 +11333,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -11383,7 +11345,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Axiom Space</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -11401,7 +11363,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11413,7 +11375,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Barrios Technology</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -11431,7 +11393,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -11443,7 +11405,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Barrios Technology</t>
+          <t>Bell / Textron</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -11461,7 +11423,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -11473,7 +11435,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Bell / Textron</t>
+          <t>BlackSky</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -11491,7 +11453,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -11503,7 +11465,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>BlackSky</t>
+          <t>Bombardier</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -11521,7 +11483,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -11533,7 +11495,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Bombardier</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -11551,7 +11513,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -11563,7 +11525,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>Capella Space</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -11581,7 +11543,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -11593,7 +11555,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Capella Space</t>
+          <t>Curtiss-Wright</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -11611,7 +11573,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -11623,7 +11585,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Curtiss-Wright</t>
+          <t>Eaton Aerospace</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -11641,7 +11603,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -11653,7 +11615,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Eaton Aerospace</t>
+          <t>Embraer</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -11671,7 +11633,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -11683,7 +11645,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Firefly Aerospace</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -11701,7 +11663,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -11713,7 +11675,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Firefly Aerospace</t>
+          <t>GKN Aerospace</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -11731,7 +11693,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -11743,7 +11705,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>GKN Aerospace</t>
+          <t>General Atomics Aeronautical Systems</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -11761,7 +11723,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -11773,7 +11735,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>General Atomics Aeronautical Systems</t>
+          <t>General Dynamics Mission Systems</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -11791,7 +11753,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -11803,7 +11765,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>General Dynamics Mission Systems</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -11821,7 +11783,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -11833,7 +11795,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -11851,7 +11813,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -11863,7 +11825,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Intuitive Machines</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -11881,7 +11843,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -11893,7 +11855,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Intuitive Machines</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -11911,7 +11873,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -11923,7 +11885,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Johns Hopkins APL</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -11941,7 +11903,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -11953,7 +11915,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Johns Hopkins APL</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -11971,7 +11933,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -11983,7 +11945,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -12001,7 +11963,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -12013,7 +11975,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -12031,7 +11993,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -12043,7 +12005,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Lunar Outpost</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -12061,7 +12023,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -12073,7 +12035,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Lunar Outpost</t>
+          <t>Maxar Space Systems</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -12091,7 +12053,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -12103,7 +12065,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Maxar Space Systems</t>
+          <t>Moog</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -12121,7 +12083,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -12133,7 +12095,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Moog</t>
+          <t>Muon Space</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -12151,7 +12113,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -12163,7 +12125,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Muon Space</t>
+          <t>NASA</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -12181,7 +12143,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -12211,7 +12173,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -12241,7 +12203,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -12271,7 +12233,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -12283,7 +12245,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Planet Labs</t>
+          <t>Redwire</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -12301,7 +12263,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -12313,7 +12275,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Redwire</t>
+          <t>Scaled Composites</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -12331,7 +12293,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -12343,7 +12305,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Scaled Composites</t>
+          <t>Sierra Space</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -12361,7 +12323,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -12391,7 +12353,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -12421,7 +12383,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -12451,7 +12413,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -12481,7 +12443,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -12511,7 +12473,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -12541,7 +12503,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -12571,7 +12533,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -12601,7 +12563,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -12631,7 +12593,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SOURCE HEALTH'!$A$1:$F$90</definedName>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -715,7 +715,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr"/>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -5407,13 +5407,13 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -5445,13 +5445,13 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7998598003</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Toronto, CAN</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -5483,13 +5483,13 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990683003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990043003</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Littleton, CO</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -5635,13 +5635,13 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -5673,13 +5673,13 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8001401003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7992754003</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -5863,13 +5863,13 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984564003</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -5901,13 +5901,13 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984564003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996623003</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CAN</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
@@ -5939,13 +5939,13 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Silver Spring, MD</t>
+          <t>Toronto, CAN</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -5977,13 +5977,13 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991769003</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Silver Spring, MD</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
@@ -6015,13 +6015,13 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7991448003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7989904003</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Intern Summer 2027</t>
+          <t>R&amp;D Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
@@ -6205,13 +6205,13 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986792003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996576003</t>
         </is>
       </c>
     </row>
@@ -6223,12 +6223,12 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D Engineering Intern Summer 2027</t>
+          <t>RF Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
@@ -6238,18 +6238,18 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7996576003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6261,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>RF Engineering Intern Summer 2027</t>
+          <t>Security Analyst Intern Summer 2027</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -6276,18 +6276,18 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8013277003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -6319,13 +6319,13 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -6357,13 +6357,13 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986956003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -6395,13 +6395,13 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986961003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986963003</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Security Analyst Intern Summer 2027</t>
+          <t>Structural Analysis Intern Summer 2027</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -6433,13 +6433,13 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986874003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986690003</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Structural Analysis Intern Summer 2027</t>
+          <t>Supply Chain Intern Summer 2027</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -6471,13 +6471,13 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986690003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Middle River, MD</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -6509,13 +6509,13 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7984568003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990063003</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Supply Chain Intern Summer 2027</t>
+          <t>Systems Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Middle River, MD</t>
+          <t>Pasadena, CA</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -6547,13 +6547,13 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990063003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Pasadena, CA</t>
+          <t>Chantilly, VA</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
@@ -6623,13 +6623,13 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990138003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Chantilly, VA</t>
+          <t>Tucson, AZ</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
@@ -6661,13 +6661,13 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990272003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
         </is>
       </c>
     </row>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineering Intern Summer 2027</t>
+          <t>Talent Acquisition Intern Summer 2027</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
@@ -6699,13 +6699,13 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990270003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990319003</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern Summer 2027</t>
+          <t>Test Engineering Intern - Avionics Summer 2027</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -6737,13 +6737,13 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7990319003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987159003</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Test Engineering Intern - Avionics Summer 2027</t>
+          <t>Test Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Wallops Island, VA</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
@@ -6775,13 +6775,13 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987159003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
@@ -6831,12 +6831,12 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Test Engineering Intern Summer 2027</t>
+          <t>Thermal Engineering Intern Summer 2027</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Wallops Island, VA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
@@ -6851,13 +6851,13 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8003529003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8000958003</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Thermal Engineering Intern Summer 2027</t>
+          <t>Turbomachinery Intern Summer 2027</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -6889,30 +6889,30 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/8000958003</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987208003</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Shield AI</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Turbomachinery Intern Summer 2027</t>
+          <t>Summer 2027 - Advanced Manufacturing Engineering Intern</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Long Beach, CA</t>
+          <t>Dallas, Texas</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
@@ -6927,13 +6927,13 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7987208003</t>
+          <t>https://jobs.lever.co/shieldai/c41c41a2-83d8-41a0-8a3b-ff8b84dc1c8a</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Advanced Manufacturing Engineering Intern</t>
+          <t>Summer 2027 - Electrical Engineering Co-op (June 2027)</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -6965,13 +6965,13 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/c41c41a2-83d8-41a0-8a3b-ff8b84dc1c8a</t>
+          <t>https://jobs.lever.co/shieldai/8c6cfcee-c6da-4a73-9bdf-3ef098ff59e6</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Co-op (June 2027)</t>
+          <t>Summer 2027 - Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -7003,13 +7003,13 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/8c6cfcee-c6da-4a73-9bdf-3ef098ff59e6</t>
+          <t>https://jobs.lever.co/shieldai/200a293f-71ce-4982-a100-ac4b500c4cf7</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Electrical Engineering Intern</t>
+          <t>Summer 2027 - Mechanical Engineering Intern</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Dallas, Texas</t>
+          <t>Seattle, Washington</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
@@ -7041,13 +7041,13 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/200a293f-71ce-4982-a100-ac4b500c4cf7</t>
+          <t>https://jobs.lever.co/shieldai/da54c482-fe62-4f60-98b1-55ac0b82b3bc</t>
         </is>
       </c>
     </row>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Mechanical Engineering Intern</t>
+          <t>Summer 2027 - Software Engineer Intern</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Seattle, Washington</t>
+          <t>San Diego, California</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
@@ -7079,30 +7079,30 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/da54c482-fe62-4f60-98b1-55ac0b82b3bc</t>
+          <t>https://jobs.lever.co/shieldai/8c850c75-081d-4d09-bebf-096379a93010</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Shield AI</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - Software Engineer Intern</t>
+          <t>Summer 2027 Business Operations Internship/Co-op</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>San Diego, California</t>
+          <t>Flexible - Any SpaceX Site</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
@@ -7117,13 +7117,13 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/shieldai/8c850c75-081d-4d09-bebf-096379a93010</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621771002?gh_jid=8621771002</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Business Operations Internship/Co-op</t>
+          <t>Summer 2027 Civil Engineering Internship</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -7155,13 +7155,13 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621771002?gh_jid=8621771002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8636144002?gh_jid=8636144002</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Civil Engineering Internship</t>
+          <t>Summer 2027 Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -7193,13 +7193,13 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8636144002?gh_jid=8636144002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621740002?gh_jid=8621740002</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Engineering Internship/Co-op</t>
+          <t>Summer 2027 Graduate Engineer Internship/Co-op</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -7231,13 +7231,13 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621740002?gh_jid=8621740002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621753002?gh_jid=8621753002</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Graduate Engineer Internship/Co-op</t>
+          <t>Summer 2027 Silicon Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -7269,13 +7269,13 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621753002?gh_jid=8621753002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621763002?gh_jid=8621763002</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Silicon Engineering Internship/Co-op</t>
+          <t>Summer 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -7307,30 +7307,30 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621763002?gh_jid=8621763002</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8621757002?gh_jid=8621757002</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Star Catcher</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Software Engineering Internship/Co-op</t>
+          <t>Summer 2027 Engineering Internship</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Flexible - Any SpaceX Site</t>
+          <t>Jacksonville, Florida, United States</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
@@ -7345,13 +7345,13 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8621757002?gh_jid=8621757002</t>
+          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413079009</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Engineering Internship</t>
+          <t>Summer 2027 Marketing &amp; Communications Internship</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -7383,30 +7383,30 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413079009</t>
+          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413215009</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Star Catcher</t>
+          <t>Stoke Space</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Marketing &amp; Communications Internship</t>
+          <t>Summer 2027 Internship - Engineering</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Jacksonville, Florida, United States</t>
+          <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
@@ -7421,13 +7421,13 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/star-catcher/jobs/4413215009</t>
+          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6175828004</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Internship - Engineering</t>
+          <t>Summer 2027 Internship - Operations</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Cape Canaveral, Florida; Kent, Washington; Moses Lake, Washington</t>
+          <t>Kent, Washington</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
@@ -7459,13 +7459,13 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6175828004</t>
+          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176785004</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Internship - Operations</t>
+          <t>Summer 2027 Internship - Software</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -7497,32 +7497,28 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176785004</t>
+          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176786004</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Stoke Space</t>
+          <t>United Launch Alliance</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Internship - Software</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>Kent, Washington</t>
-        </is>
-      </c>
+          <t>Aerospace Engineering Internship Summer 2027</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr"/>
       <c r="D182" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -7535,13 +7531,13 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/stokespacetechnologies/jobs/6176786004</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Aerospace-Engineering-Internship-Summer-2027-CO-80112/1427399400/</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7549,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Aerospace Engineering Internship Summer 2027</t>
+          <t>Avionics &amp; Electrical Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
@@ -7569,13 +7565,13 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Aerospace-Engineering-Internship-Summer-2027-CO-80112/1427399400/</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Avionics-&amp;-Electrical-Engineering-Internship-Summer-2027-CO-80112/1427399200/</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7583,7 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Avionics &amp; Electrical Engineering Internship Summer 2027</t>
+          <t>Civil Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr"/>
@@ -7603,13 +7599,13 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Avionics-&amp;-Electrical-Engineering-Internship-Summer-2027-CO-80112/1427399200/</t>
+          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Civil%E2%80%AFEngineering-Internship-Summer-2027-FL-32925/1427396600/</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7617,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Civil Engineering Internship - Summer 2027</t>
+          <t>Composite Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
@@ -7637,13 +7633,13 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Civil%E2%80%AFEngineering-Internship-Summer-2027-FL-32925/1427396600/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Composite-Engineering-Internship-Summer-2027-AL-35601/1427397600/</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7651,7 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Composite Engineering Internship - Summer 2027</t>
+          <t>Industrial Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
@@ -7671,13 +7667,13 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Composite-Engineering-Internship-Summer-2027-AL-35601/1427397600/</t>
+          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Industrial-Engineering-Internship-Summer-2027-FL-32925/1427396900/</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7685,7 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Industrial Engineering Internship - Summer 2027</t>
+          <t>Material Requirements Planning Specialist (MRP) Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
@@ -7705,13 +7701,13 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Industrial-Engineering-Internship-Summer-2027-FL-32925/1427396900/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Material-Requirements-Planning-Specialist-%28MRP%29-Internship-Summer-2027-AL-35601/1427398800/</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7719,7 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Material Requirements Planning Specialist (MRP) Internship - Summer 2027</t>
+          <t>Material and Process Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
@@ -7739,13 +7735,13 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Material-Requirements-Planning-Specialist-%28MRP%29-Internship-Summer-2027-AL-35601/1427398800/</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Material-and-Process-Engineering-Internship-Summer-2027-CO-80112/1427398900/</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7753,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Material and Process Engineering Internship Summer 2027</t>
+          <t>Mechanical Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr"/>
@@ -7773,13 +7769,13 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Material-and-Process-Engineering-Internship-Summer-2027-CO-80112/1427398900/</t>
+          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Mechanical-Engineering-Internship-Summer-2027-FL-32925/1427396400/</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7787,7 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Internship - Summer 2027</t>
+          <t>Quality Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
@@ -7807,13 +7803,13 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Cape-Canaveral-Mechanical-Engineering-Internship-Summer-2027-FL-32925/1427396400/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Quality-Engineering-Internship-Summer-2027-AL-35601/1427398600/</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7821,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Quality Engineering Internship Summer 2027</t>
+          <t>Software Engineering Internship Summer 2027</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
@@ -7841,13 +7837,13 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Quality-Engineering-Internship-Summer-2027-AL-35601/1427398600/</t>
+          <t>https://jobs.ulalaunch.com/job/Centennial-Software-Engineering-Internship-Summer-2027-CO-80112/1427398300/</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7855,7 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Internship Summer 2027</t>
+          <t>Weld Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
@@ -7875,28 +7871,32 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Centennial-Software-Engineering-Internship-Summer-2027-CO-80112/1427398300/</t>
+          <t>https://jobs.ulalaunch.com/job/Decatur-Weld-Engineering-Internship-Summer-2027-AL-35601/1427397200/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>United Launch Alliance</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Weld Engineering Internship - Summer 2027</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr"/>
+          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>El Segundo, California, United States</t>
+        </is>
+      </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -7904,18 +7904,18 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ulalaunch.com/job/Decatur-Weld-Engineering-Internship-Summer-2027-AL-35601/1427397200/</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Aerodynamics &amp; Analysis Engineering Internship - Summer 2027</t>
+          <t>Avionics Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -7947,13 +7947,13 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010632003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Avionics Engineering Internship - Summer 2027</t>
+          <t>Cybersecurity Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -7985,13 +7985,13 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010158003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Internship - Summer 2027</t>
+          <t>Flight Software Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -8023,13 +8023,13 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr"/>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005821003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Flight Software Internship - Summer 2027</t>
+          <t>Formulation Science Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -8061,13 +8061,13 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010159003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Formulation Science Internship - Summer 2027</t>
+          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -8099,13 +8099,13 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8005846003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Guidance, Navigation &amp; Controls (GNC) Internship - Summer 2027</t>
+          <t>Manufacturing Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -8137,13 +8137,13 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/7865601003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Internship - Summer 2027</t>
+          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -8175,13 +8175,13 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr"/>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010166003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Mechanisms &amp; Payload Internship - Summer 2027</t>
+          <t>Mission Operations Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -8213,13 +8213,13 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010168003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Mission Operations Internship - Summer 2027</t>
+          <t>Propulsion Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -8251,13 +8251,13 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr"/>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010682003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Propulsion Engineering Internship - Summer 2027</t>
+          <t>Structures Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -8289,13 +8289,13 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010169003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Structures Engineering Internship - Summer 2027</t>
+          <t>Thermal Engineering Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -8327,13 +8327,13 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010167003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Thermal Engineering Internship - Summer 2027</t>
+          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -8365,68 +8365,68 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr"/>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010172003</t>
+          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Vehicle Integration &amp; Test Internship - Summer 2027</t>
+          <t>2027 Manufacturing Optimization Engineer Intern</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, California, United States</t>
-        </is>
-      </c>
-      <c r="D206" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Ashville, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr"/>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vardaspace/jobs/8010170003</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>BETA Technologies</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>2027 Manufacturing Optimization Engineer Intern</t>
+          <t>BETA Internship</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Ashville, Ohio, United States</t>
+          <t>South Burlington, Vermont, United States</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
@@ -8441,30 +8441,30 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr"/>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5236893007?gh_jid=5236893007</t>
+          <t>https://job-boards.greenhouse.io/betatechnologiesinc/jobs/4218580009</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>BETA Technologies</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>BETA Internship</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>South Burlington, Vermont, United States</t>
+          <t>USA - Arlington, VA</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
@@ -8479,13 +8479,13 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr"/>
       <c r="H208" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/betatechnologiesinc/jobs/4218580009</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) - Government Operations and Sustainability</t>
+          <t>Boeing Summer 2027 Internship Program (Paid) – Environment, Health, and Safety (EHS)</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>USA - Arlington, VA</t>
+          <t>USA - Auburn, WA</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
@@ -8517,13 +8517,13 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr"/>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Arlington-VA/Boeing-Summer-2027-Internship-Program--Paid----Government-Operations-and-Sustainability_JR2026519183</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Auburn-WA/Boeing-Summer-2027-Internship-Program--Paid----Environment--Health--and-Safety--EHS-_JR2026519561</t>
         </is>
       </c>
     </row>
@@ -8535,12 +8535,12 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Boeing Summer 2027 Internship Program (Paid) – Environment, Health, and Safety (EHS)</t>
+          <t>Intern to Entry Level Conversion – Business Functions (All) (Summer 2026 Intern Program)</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>USA - Auburn, WA</t>
+          <t>USA - Everett, WA</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
@@ -8561,7 +8561,7 @@
       <c r="G210" s="4" t="inlineStr"/>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Auburn-WA/Boeing-Summer-2027-Internship-Program--Paid----Environment--Health--and-Safety--EHS-_JR2026519561</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Intern-to-Entry-Level-Conversion---Business-Functions--All---Summer-2026-Intern-Program-_JR2026516335</t>
         </is>
       </c>
     </row>
@@ -8573,12 +8573,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Intern to Entry Level Conversion – Business Functions (All) (Summer 2026 Intern Program)</t>
+          <t>Intern to Intern Conversion - Engineering (Summer 2026 Intern Program)</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>USA - Everett, WA</t>
+          <t>USA - Seattle, WA</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
@@ -8588,35 +8588,35 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr"/>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Everett-WA/Intern-to-Entry-Level-Conversion---Business-Functions--All---Summer-2026-Intern-Program-_JR2026516335</t>
+          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Intern-to-Intern-Conversion---Engineering--Summer-2026-Intern-Program-_JR2026516288</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CesiumAstro</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Intern to Intern Conversion - Engineering (Summer 2026 Intern Program)</t>
+          <t>Summer 2027 – Power Electronics Internship</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>USA - Seattle, WA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
@@ -8626,18 +8626,18 @@
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr"/>
       <c r="H212" s="4" t="inlineStr">
         <is>
-          <t>https://boeing.wd1.myworkdayjobs.com/INTERN/job/USA---Seattle-WA/Intern-to-Intern-Conversion---Engineering--Summer-2026-Intern-Program-_JR2026516288</t>
+          <t>https://jobs.lever.co/CesiumAstro/18d2c72e-30cd-4145-8b12-7db3a492d541</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Westminster, CO</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
@@ -8675,24 +8675,24 @@
       <c r="G213" s="4" t="inlineStr"/>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/18d2c72e-30cd-4145-8b12-7db3a492d541</t>
+          <t>https://jobs.lever.co/CesiumAstro/e82f19e5-68f7-4d87-816f-cf405191952e</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>CesiumAstro</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 – Power Electronics Internship</t>
+          <t>Finance Intern – US – Summer 2027</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Westminster, CO</t>
+          <t>Evendale</t>
         </is>
       </c>
       <c r="D214" s="6" t="inlineStr">
@@ -8707,32 +8707,28 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr"/>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/CesiumAstro/e82f19e5-68f7-4d87-816f-cf405191952e</t>
+          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Finance Intern – US – Summer 2027</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>Evendale</t>
-        </is>
-      </c>
+          <t>Summer 2027 - IEF - Flight Operations Engineer Collegiate Associate Intern</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr"/>
       <c r="D215" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
@@ -8745,13 +8741,13 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr"/>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>https://geaerospace.wd5.myworkdayjobs.com/GE_ExternalSite/job/Evendale/Finance-Intern---US---Summer-2027_R5030147-1</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Operations-Engineer-Collegiate-Associate-Intern-GA-31401/1421926200/</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8759,7 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Flight Operations Engineer Collegiate Associate Intern</t>
+          <t>Summer 2027 - IEF - Flight Sciences Engineer Collegiate Associate Intern</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr"/>
@@ -8779,13 +8775,13 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr"/>
       <c r="H216" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Operations-Engineer-Collegiate-Associate-Intern-GA-31401/1421926200/</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Sciences-Engineer-Collegiate-Associate-Intern-GA-31401/1421898000/</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8793,7 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Flight Sciences Engineer Collegiate Associate Intern</t>
+          <t>Summer 2027 - IEF - Flight Test Engineer Collegiate Associate Intern</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr"/>
@@ -8813,13 +8809,13 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr"/>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Sciences-Engineer-Collegiate-Associate-Intern-GA-31401/1421898000/</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Test-Engineer-Collegiate-Associate-Intern-GA-31401/1421914300/</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8827,7 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Flight Test Engineer Collegiate Associate Intern</t>
+          <t>Summer 2027 - IEF - Flight/System Simulation Engineer Collegiate Associate Intern</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr"/>
@@ -8853,7 +8849,7 @@
       <c r="G218" s="4" t="inlineStr"/>
       <c r="H218" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-Flight-Test-Engineer-Collegiate-Associate-Intern-GA-31401/1421914300/</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-FlightSystem-Simulation-Engineer-Collegiate-Associate-Intern-GA-31401/1421866000/</t>
         </is>
       </c>
     </row>
@@ -8865,7 +8861,7 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Flight/System Simulation Engineer Collegiate Associate Intern</t>
+          <t>Summer 2027 - IEF - Powerplant/Propulsion Engineer Collegiate Associate Intern</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr"/>
@@ -8887,22 +8883,26 @@
       <c r="G219" s="4" t="inlineStr"/>
       <c r="H219" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-FlightSystem-Simulation-Engineer-Collegiate-Associate-Intern-GA-31401/1421866000/</t>
+          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-PowerplantPropulsion-Engineer-Collegiate-Associate-Intern-GA-31401/1421952200/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 - IEF - Powerplant/Propulsion Engineer Collegiate Associate Intern</t>
-        </is>
-      </c>
-      <c r="C220" s="4" t="inlineStr"/>
+          <t>Propulsion Intern Summer 2027</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
           <t>CLOSED</t>
@@ -8915,13 +8915,13 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr"/>
       <c r="H220" s="4" t="inlineStr">
         <is>
-          <t>https://careers.gulfstream.com/job/Savannah-Summer-2027-IEF-PowerplantPropulsion-Engineer-Collegiate-Associate-Intern-GA-31401/1421952200/</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7986792003</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9173,122 +9173,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2027 Systems Engineer Intern</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Boston, Massachusetts, United States; Costa Mesa, California, United States; Fort Collins, Colorado, United States; Reston, Virginia, United States; Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257690007?gh_jid=5257690007</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2027 Reliability Engineer Intern</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Costa Mesa, California, United States</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257682007?gh_jid=5257682007</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2027 Quality &amp; Test Engineer Intern</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Ashville, Ohio, United States; Costa Mesa, California, United States; Irvine, California, United States; Quonset, Rhode Island, United States; Santa Ana, California, United States</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5257674007?gh_jid=5257674007</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9382,7 +9268,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -9420,7 +9306,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9458,7 +9344,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -9496,7 +9382,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9534,7 +9420,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -9572,7 +9458,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -9610,7 +9496,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -9648,7 +9534,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -9686,7 +9572,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -9724,7 +9610,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -9762,7 +9648,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -9800,7 +9686,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -9953,7 +9839,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -9983,7 +9869,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10013,7 +9899,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10043,7 +9929,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10073,7 +9959,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10103,7 +9989,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10133,7 +10019,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10163,7 +10049,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -10193,7 +10079,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10223,7 +10109,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10253,7 +10139,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10283,7 +10169,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10309,11 +10195,11 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10343,7 +10229,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -10373,7 +10259,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10403,7 +10289,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10433,7 +10319,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10463,7 +10349,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -10493,7 +10379,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -10523,7 +10409,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10553,7 +10439,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10583,7 +10469,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10613,7 +10499,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -10643,7 +10529,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -10673,7 +10559,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -10703,7 +10589,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -10733,7 +10619,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -10763,7 +10649,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -10793,7 +10679,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -10823,7 +10709,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -10853,7 +10739,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -10883,7 +10769,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -10913,7 +10799,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -10943,7 +10829,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -10973,7 +10859,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -11003,7 +10889,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -11015,12 +10901,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Planet Labs</t>
+          <t>RTX / Raytheon / Collins / Pratt &amp; Whitney</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>careers_page</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -11033,24 +10919,24 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>HTTPSConnectionPool(host='www.planet.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>422 Client Error: Unprocessable Entity for url: https://globalhr.wd5.myworkdayjobs.com/wday/cxs/RTX/REC_RTX_Ext_Gateway/jobs</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>RTX / Raytheon / Collins / Pratt &amp; Whitney</t>
+          <t>Relativity Space Internships</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -11063,24 +10949,24 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>422 Client Error: Unprocessable Entity for url: https://globalhr.wd5.myworkdayjobs.com/wday/cxs/RTX/REC_RTX_Ext_Gateway/jobs</t>
+          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/rsinternboard/jobs?content=true</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Relativity Space Internships</t>
+          <t>Sierra Nevada Corporation</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>careers_page</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -11093,19 +10979,19 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://boards-api.greenhouse.io/v1/boards/rsinternboard/jobs?content=true</t>
+          <t>404 Client Error: Not Found for url: https://www.sncorp.com/careers/open-positions</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Sierra Nevada Corporation</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -11123,19 +11009,19 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.sncorp.com/careers/open-positions</t>
+          <t>500 Server Error: Internal Server Error for url: https://standardaero.wd1.myworkdayjobs.com/External?q=intern</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Venturi Astrolab</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -11153,19 +11039,19 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>500 Server Error: Internal Server Error for url: https://standardaero.wd1.myworkdayjobs.com/External?q=intern</t>
+          <t>404 Client Error: Not Found for url: https://www.astrolab.space/careers</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Venturi Astrolab</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -11173,9 +11059,9 @@
           <t>careers_page</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
@@ -11183,19 +11069,19 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.astrolab.space/careers</t>
+          <t>Page fetched, but no verifiable Summer 2027 engineering internships were parsed; zero is not treated as authoritative.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Airbus Americas</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -11213,7 +11099,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -11225,7 +11111,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Airbus Americas</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -11243,7 +11129,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -11255,7 +11141,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Archer Aviation</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -11273,7 +11159,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -11285,7 +11171,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Archer Aviation</t>
+          <t>Axiom Space</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -11303,7 +11189,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -11315,7 +11201,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Axiom Space</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -11333,7 +11219,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -11345,7 +11231,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Barrios Technology</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -11363,7 +11249,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11375,7 +11261,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Barrios Technology</t>
+          <t>Bell / Textron</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -11393,7 +11279,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -11405,7 +11291,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Bell / Textron</t>
+          <t>BlackSky</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -11423,7 +11309,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -11435,7 +11321,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>BlackSky</t>
+          <t>Bombardier</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -11453,7 +11339,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -11465,7 +11351,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Bombardier</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -11483,7 +11369,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -11495,7 +11381,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>Capella Space</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -11513,7 +11399,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -11525,7 +11411,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Capella Space</t>
+          <t>Curtiss-Wright</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -11543,7 +11429,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -11555,7 +11441,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Curtiss-Wright</t>
+          <t>Eaton Aerospace</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -11573,7 +11459,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -11585,7 +11471,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Eaton Aerospace</t>
+          <t>Embraer</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -11603,7 +11489,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -11615,7 +11501,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Firefly Aerospace</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -11633,7 +11519,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -11645,7 +11531,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Firefly Aerospace</t>
+          <t>GKN Aerospace</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -11663,7 +11549,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -11675,7 +11561,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>GKN Aerospace</t>
+          <t>General Atomics Aeronautical Systems</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -11693,7 +11579,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -11705,7 +11591,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>General Atomics Aeronautical Systems</t>
+          <t>General Dynamics Mission Systems</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -11723,7 +11609,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -11735,7 +11621,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>General Dynamics Mission Systems</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -11753,7 +11639,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -11765,7 +11651,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -11783,7 +11669,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -11795,7 +11681,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Intuitive Machines</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -11813,7 +11699,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -11825,7 +11711,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Intuitive Machines</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -11843,7 +11729,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -11855,7 +11741,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Johns Hopkins APL</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -11873,7 +11759,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -11885,7 +11771,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Johns Hopkins APL</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -11903,7 +11789,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -11915,7 +11801,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -11933,7 +11819,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -11945,7 +11831,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -11963,7 +11849,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -11975,7 +11861,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Lunar Outpost</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -11993,7 +11879,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -12005,7 +11891,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Lunar Outpost</t>
+          <t>Maxar Space Systems</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -12023,7 +11909,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -12035,7 +11921,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Maxar Space Systems</t>
+          <t>Moog</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -12053,7 +11939,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -12065,7 +11951,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Moog</t>
+          <t>Muon Space</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -12083,7 +11969,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -12095,7 +11981,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Muon Space</t>
+          <t>NASA</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -12113,7 +11999,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -12125,7 +12011,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NASA</t>
+          <t>NASA / USAJobs Pathways</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -12143,7 +12029,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -12155,7 +12041,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NASA / USAJobs Pathways</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -12173,7 +12059,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -12185,7 +12071,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>Oceaneering</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -12203,7 +12089,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -12215,7 +12101,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Oceaneering</t>
+          <t>Planet Labs</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -12233,7 +12119,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -12263,7 +12149,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -12293,7 +12179,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -12323,7 +12209,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -12353,7 +12239,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -12383,7 +12269,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -12413,7 +12299,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -12443,7 +12329,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -12473,7 +12359,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -12503,7 +12389,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -12533,7 +12419,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -12563,7 +12449,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -12593,7 +12479,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">

--- a/AIAA_UH_Summer_2027_Internships.xlsx
+++ b/AIAA_UH_Summer_2027_Internships.xlsx
@@ -16,9 +16,9 @@
     <sheet name="SOURCE HEALTH" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$224</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL INTERNSHIPS'!$A$1:$H$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NEW TODAY'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NEW THIS WEEK'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TEXAS - HOUSTON'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CLOSING SOON'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SOURCE HEALTH'!$A$1:$F$90</definedName>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H224"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -690,17 +690,17 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2027 Firmware Engineer Intern</t>
+          <t>Intern to Intern Conversion – Business Functions (All) (Summer 2026 Intern Program)</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
+          <t>USA - Everett, WA</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -710,18 +710,18 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r=